--- a/JS/liste_etudiants_v1.xlsx
+++ b/JS/liste_etudiants_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Stephano\Documents\TRAVAIL\Photo-univ\JS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22BF04B3-A0EE-4916-8AC3-1F94EBDE2514}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D53FAFB-63C5-49A8-A829-B13741D45208}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-78" yWindow="0" windowWidth="11676" windowHeight="12318" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3756" yWindow="1536" windowWidth="17280" windowHeight="10440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2770,11 +2770,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+  <numFmts count="3">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="d/mm/yyyy;@"/>
     <numFmt numFmtId="165" formatCode="dd/mm/yyyy;@"/>
-    <numFmt numFmtId="166" formatCode="#,##0_ ;\-#,##0\ "/>
+    <numFmt numFmtId="169" formatCode="[$-40C]d\ mmmm\ yyyy;@"/>
   </numFmts>
   <fonts count="24" x14ac:knownFonts="1">
     <font>
@@ -3133,7 +3132,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="160">
+  <cellXfs count="163">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -3168,29 +3167,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -3303,15 +3279,6 @@
     <xf numFmtId="14" fontId="5" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3327,30 +3294,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="2" borderId="4" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="165" fontId="6" fillId="3" borderId="4" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="165" fontId="17" fillId="4" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
@@ -3358,15 +3305,6 @@
     <xf numFmtId="165" fontId="17" fillId="4" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3444,9 +3382,6 @@
     <xf numFmtId="0" fontId="18" fillId="2" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="165" fontId="6" fillId="3" borderId="4" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3456,9 +3391,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="21" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="3"/>
     <xf numFmtId="0" fontId="22" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -3478,18 +3410,8 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="5" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3497,23 +3419,106 @@
     <xf numFmtId="14" fontId="2" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="5" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="5" borderId="4" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="14" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="5" borderId="4" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="5" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="21" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="1" fontId="0" fillId="5" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="5" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="5" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="2" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="169" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="7" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="7" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="169" fontId="3" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="6" fillId="5" borderId="4" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="17" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="17" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="6" fillId="2" borderId="4" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="17" fillId="4" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="6" fillId="5" borderId="4" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
@@ -3827,8 +3832,8 @@
     <col min="2" max="2" width="24.1015625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.3125" customWidth="1"/>
     <col min="4" max="4" width="15.1015625" customWidth="1"/>
-    <col min="5" max="5" width="15.5234375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.26171875" customWidth="1"/>
+    <col min="5" max="5" width="15.5234375" style="125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.26171875" style="143" customWidth="1"/>
     <col min="7" max="7" width="19.5234375" customWidth="1"/>
     <col min="8" max="8" width="15.47265625" customWidth="1"/>
     <col min="9" max="9" width="12.5234375" customWidth="1"/>
@@ -3851,10 +3856,10 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="125" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="143" t="s">
         <v>5</v>
       </c>
       <c r="G1" t="s">
@@ -3892,7 +3897,7 @@
       <c r="A2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="141" t="s">
+      <c r="B2" s="115" t="s">
         <v>700</v>
       </c>
       <c r="C2" s="3" t="s">
@@ -3901,10 +3906,10 @@
       <c r="D2" s="10">
         <v>38985</v>
       </c>
-      <c r="E2" s="15">
+      <c r="E2" s="126">
         <v>213012043395</v>
       </c>
-      <c r="F2" s="21">
+      <c r="F2" s="144">
         <v>45645</v>
       </c>
       <c r="G2" s="7" t="s">
@@ -3913,16 +3918,16 @@
       <c r="H2" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="I2" s="31" t="s">
+      <c r="I2" s="21" t="s">
         <v>105</v>
       </c>
-      <c r="J2" s="35" t="s">
+      <c r="J2" s="25" t="s">
         <v>149</v>
       </c>
-      <c r="K2" s="36" t="s">
+      <c r="K2" s="26" t="s">
         <v>150</v>
       </c>
-      <c r="L2" s="37" t="s">
+      <c r="L2" s="27" t="s">
         <v>151</v>
       </c>
       <c r="M2" t="s">
@@ -3932,7 +3937,7 @@
         <f t="shared" ref="N2:N33" si="0">"https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/" &amp; C2 &amp; ".png"</f>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0001-G.png</v>
       </c>
-      <c r="O2" s="136" t="str">
+      <c r="O2" s="110" t="str">
         <f t="shared" ref="O2:O33" si="1">"https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/" &amp; C2 &amp; ".png"</f>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0001-G.png</v>
       </c>
@@ -3944,7 +3949,7 @@
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="141" t="s">
+      <c r="B3" s="115" t="s">
         <v>699</v>
       </c>
       <c r="C3" s="3" t="s">
@@ -3953,10 +3958,10 @@
       <c r="D3" s="10">
         <v>38844</v>
       </c>
-      <c r="E3" s="15">
+      <c r="E3" s="126">
         <v>214011119080</v>
       </c>
-      <c r="F3" s="21">
+      <c r="F3" s="144">
         <v>45467</v>
       </c>
       <c r="G3" s="7" t="s">
@@ -3965,16 +3970,16 @@
       <c r="H3" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="I3" s="31" t="s">
+      <c r="I3" s="21" t="s">
         <v>106</v>
       </c>
-      <c r="J3" s="35" t="s">
+      <c r="J3" s="25" t="s">
         <v>149</v>
       </c>
-      <c r="K3" s="36" t="s">
+      <c r="K3" s="26" t="s">
         <v>150</v>
       </c>
-      <c r="L3" s="37" t="s">
+      <c r="L3" s="27" t="s">
         <v>152</v>
       </c>
       <c r="M3" t="s">
@@ -3984,7 +3989,7 @@
         <f t="shared" si="0"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0002-G.png</v>
       </c>
-      <c r="O3" s="136" t="str">
+      <c r="O3" s="110" t="str">
         <f t="shared" si="1"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0002-G.png</v>
       </c>
@@ -4005,10 +4010,10 @@
       <c r="D4" s="10">
         <v>38138</v>
       </c>
-      <c r="E4" s="15">
+      <c r="E4" s="126">
         <v>213011040696</v>
       </c>
-      <c r="F4" s="21">
+      <c r="F4" s="144">
         <v>45006</v>
       </c>
       <c r="G4" s="7" t="s">
@@ -4017,16 +4022,16 @@
       <c r="H4" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="I4" s="31" t="s">
+      <c r="I4" s="21" t="s">
         <v>107</v>
       </c>
-      <c r="J4" s="35" t="s">
+      <c r="J4" s="25" t="s">
         <v>149</v>
       </c>
-      <c r="K4" s="36" t="s">
+      <c r="K4" s="26" t="s">
         <v>150</v>
       </c>
-      <c r="L4" s="37" t="s">
+      <c r="L4" s="27" t="s">
         <v>153</v>
       </c>
       <c r="M4" t="s">
@@ -4036,7 +4041,7 @@
         <f t="shared" si="0"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0003-G.png</v>
       </c>
-      <c r="O4" s="136" t="str">
+      <c r="O4" s="110" t="str">
         <f t="shared" si="1"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0003-G.png</v>
       </c>
@@ -4057,10 +4062,10 @@
       <c r="D5" s="10">
         <v>39372</v>
       </c>
-      <c r="E5" s="15">
+      <c r="E5" s="126">
         <v>213571011006</v>
       </c>
-      <c r="F5" s="21">
+      <c r="F5" s="144">
         <v>45949</v>
       </c>
       <c r="G5" s="7" t="s">
@@ -4069,16 +4074,16 @@
       <c r="H5" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="I5" s="31" t="s">
+      <c r="I5" s="21" t="s">
         <v>108</v>
       </c>
-      <c r="J5" s="35" t="s">
+      <c r="J5" s="25" t="s">
         <v>149</v>
       </c>
-      <c r="K5" s="36" t="s">
+      <c r="K5" s="26" t="s">
         <v>150</v>
       </c>
-      <c r="L5" s="37" t="s">
+      <c r="L5" s="27" t="s">
         <v>154</v>
       </c>
       <c r="M5" t="s">
@@ -4088,7 +4093,7 @@
         <f t="shared" si="0"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0004-G.png</v>
       </c>
-      <c r="O5" s="136" t="str">
+      <c r="O5" s="110" t="str">
         <f t="shared" si="1"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0004-G.png</v>
       </c>
@@ -4109,10 +4114,10 @@
       <c r="D6" s="10">
         <v>40150</v>
       </c>
-      <c r="E6" s="135">
+      <c r="E6" s="127">
         <v>930</v>
       </c>
-      <c r="F6" s="21">
+      <c r="F6" s="144">
         <v>40150</v>
       </c>
       <c r="G6" s="7" t="s">
@@ -4121,16 +4126,16 @@
       <c r="H6" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="I6" s="31" t="s">
+      <c r="I6" s="21" t="s">
         <v>109</v>
       </c>
-      <c r="J6" s="35" t="s">
+      <c r="J6" s="25" t="s">
         <v>149</v>
       </c>
-      <c r="K6" s="36" t="s">
+      <c r="K6" s="26" t="s">
         <v>150</v>
       </c>
-      <c r="L6" s="37" t="s">
+      <c r="L6" s="27" t="s">
         <v>155</v>
       </c>
       <c r="M6" t="s">
@@ -4140,7 +4145,7 @@
         <f t="shared" si="0"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0005-G.png</v>
       </c>
-      <c r="O6" s="136" t="str">
+      <c r="O6" s="110" t="str">
         <f t="shared" si="1"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0005-G.png</v>
       </c>
@@ -4161,10 +4166,10 @@
       <c r="D7" s="10">
         <v>38901</v>
       </c>
-      <c r="E7" s="15">
+      <c r="E7" s="126">
         <v>213011043114</v>
       </c>
-      <c r="F7" s="21">
+      <c r="F7" s="144">
         <v>45560</v>
       </c>
       <c r="G7" s="7" t="s">
@@ -4173,16 +4178,16 @@
       <c r="H7" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="I7" s="31" t="s">
+      <c r="I7" s="21" t="s">
         <v>110</v>
       </c>
-      <c r="J7" s="35" t="s">
+      <c r="J7" s="25" t="s">
         <v>149</v>
       </c>
-      <c r="K7" s="36" t="s">
+      <c r="K7" s="26" t="s">
         <v>150</v>
       </c>
-      <c r="L7" s="37" t="s">
+      <c r="L7" s="27" t="s">
         <v>156</v>
       </c>
       <c r="M7" t="s">
@@ -4192,7 +4197,7 @@
         <f t="shared" si="0"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0006-G.png</v>
       </c>
-      <c r="O7" s="136" t="str">
+      <c r="O7" s="110" t="str">
         <f t="shared" si="1"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0006-G.png</v>
       </c>
@@ -4204,7 +4209,7 @@
       <c r="A8" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="142" t="s">
+      <c r="B8" s="116" t="s">
         <v>701</v>
       </c>
       <c r="C8" s="3" t="s">
@@ -4213,28 +4218,28 @@
       <c r="D8" s="11">
         <v>39364</v>
       </c>
-      <c r="E8" s="16">
+      <c r="E8" s="128">
         <v>213012045255</v>
       </c>
-      <c r="F8" s="22">
+      <c r="F8" s="145">
         <v>46059</v>
       </c>
       <c r="G8" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="H8" s="27" t="s">
+      <c r="H8" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="I8" s="32" t="s">
+      <c r="I8" s="22" t="s">
         <v>111</v>
       </c>
-      <c r="J8" s="35" t="s">
+      <c r="J8" s="25" t="s">
         <v>149</v>
       </c>
-      <c r="K8" s="36" t="s">
+      <c r="K8" s="26" t="s">
         <v>150</v>
       </c>
-      <c r="L8" s="38" t="s">
+      <c r="L8" s="28" t="s">
         <v>157</v>
       </c>
       <c r="M8" t="s">
@@ -4244,7 +4249,7 @@
         <f t="shared" si="0"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0007-G.png</v>
       </c>
-      <c r="O8" s="136" t="str">
+      <c r="O8" s="110" t="str">
         <f t="shared" si="1"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0007-G.png</v>
       </c>
@@ -4260,31 +4265,31 @@
       <c r="C9" s="3" t="s">
         <v>760</v>
       </c>
-      <c r="D9" s="144">
+      <c r="D9" s="118">
         <v>36892</v>
       </c>
-      <c r="E9" s="15">
+      <c r="E9" s="126">
         <v>217011017683</v>
       </c>
-      <c r="F9" s="21">
+      <c r="F9" s="144">
         <v>43867</v>
       </c>
       <c r="G9" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="H9" s="28" t="s">
+      <c r="H9" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="I9" s="33" t="s">
+      <c r="I9" s="23" t="s">
         <v>112</v>
       </c>
-      <c r="J9" s="35" t="s">
+      <c r="J9" s="25" t="s">
         <v>149</v>
       </c>
-      <c r="K9" s="36" t="s">
+      <c r="K9" s="26" t="s">
         <v>150</v>
       </c>
-      <c r="L9" s="39" t="s">
+      <c r="L9" s="29" t="s">
         <v>158</v>
       </c>
       <c r="M9" t="s">
@@ -4294,7 +4299,7 @@
         <f t="shared" si="0"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0008-G.png</v>
       </c>
-      <c r="O9" s="136" t="str">
+      <c r="O9" s="110" t="str">
         <f t="shared" si="1"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0008-G.png</v>
       </c>
@@ -4315,28 +4320,28 @@
       <c r="D10" s="12">
         <v>37942</v>
       </c>
-      <c r="E10" s="15">
+      <c r="E10" s="126">
         <v>213011038395</v>
       </c>
-      <c r="F10" s="21">
+      <c r="F10" s="144">
         <v>44735</v>
       </c>
       <c r="G10" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="H10" s="28" t="s">
+      <c r="H10" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="I10" s="33" t="s">
+      <c r="I10" s="23" t="s">
         <v>113</v>
       </c>
-      <c r="J10" s="35" t="s">
+      <c r="J10" s="25" t="s">
         <v>149</v>
       </c>
-      <c r="K10" s="36" t="s">
+      <c r="K10" s="26" t="s">
         <v>150</v>
       </c>
-      <c r="L10" s="40" t="s">
+      <c r="L10" s="30" t="s">
         <v>159</v>
       </c>
       <c r="M10" t="s">
@@ -4346,7 +4351,7 @@
         <f t="shared" si="0"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0009-G.png</v>
       </c>
-      <c r="O10" s="136" t="str">
+      <c r="O10" s="110" t="str">
         <f t="shared" si="1"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0009-G.png</v>
       </c>
@@ -4358,7 +4363,7 @@
       <c r="A11" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="B11" s="140" t="s">
+      <c r="B11" s="114" t="s">
         <v>702</v>
       </c>
       <c r="C11" s="3" t="s">
@@ -4367,28 +4372,28 @@
       <c r="D11" s="13">
         <v>37288</v>
       </c>
-      <c r="E11" s="16">
+      <c r="E11" s="128">
         <v>213011036487</v>
       </c>
-      <c r="F11" s="22">
+      <c r="F11" s="145">
         <v>44265</v>
       </c>
       <c r="G11" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="H11" s="29" t="s">
+      <c r="H11" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="I11" s="34" t="s">
+      <c r="I11" s="24" t="s">
         <v>114</v>
       </c>
-      <c r="J11" s="35" t="s">
+      <c r="J11" s="25" t="s">
         <v>149</v>
       </c>
-      <c r="K11" s="36" t="s">
+      <c r="K11" s="26" t="s">
         <v>150</v>
       </c>
-      <c r="L11" s="41" t="s">
+      <c r="L11" s="31" t="s">
         <v>160</v>
       </c>
       <c r="M11" t="s">
@@ -4398,7 +4403,7 @@
         <f t="shared" si="0"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0010-G.png</v>
       </c>
-      <c r="O11" s="136" t="str">
+      <c r="O11" s="110" t="str">
         <f t="shared" si="1"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0010-G.png</v>
       </c>
@@ -4419,28 +4424,28 @@
       <c r="D12" s="13">
         <v>38498</v>
       </c>
-      <c r="E12" s="15">
+      <c r="E12" s="126">
         <v>213571009975</v>
       </c>
-      <c r="F12" s="22">
+      <c r="F12" s="145">
         <v>45327</v>
       </c>
       <c r="G12" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="H12" s="30" t="s">
+      <c r="H12" s="20" t="s">
         <v>86</v>
       </c>
-      <c r="I12" s="34" t="s">
+      <c r="I12" s="24" t="s">
         <v>115</v>
       </c>
-      <c r="J12" s="35" t="s">
+      <c r="J12" s="25" t="s">
         <v>149</v>
       </c>
-      <c r="K12" s="36" t="s">
+      <c r="K12" s="26" t="s">
         <v>150</v>
       </c>
-      <c r="L12" s="42" t="s">
+      <c r="L12" s="32" t="s">
         <v>161</v>
       </c>
       <c r="M12" t="s">
@@ -4450,7 +4455,7 @@
         <f t="shared" si="0"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0011-G.png</v>
       </c>
-      <c r="O12" s="136" t="str">
+      <c r="O12" s="110" t="str">
         <f t="shared" si="1"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0011-G.png</v>
       </c>
@@ -4468,31 +4473,31 @@
       <c r="C13" s="3" t="s">
         <v>756</v>
       </c>
-      <c r="D13" s="143">
+      <c r="D13" s="117">
         <v>37257</v>
       </c>
-      <c r="E13" s="17">
+      <c r="E13" s="129">
         <v>213622000605</v>
       </c>
-      <c r="F13" s="22">
+      <c r="F13" s="145">
         <v>43865</v>
       </c>
       <c r="G13" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="H13" s="29" t="s">
+      <c r="H13" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="I13" s="34" t="s">
+      <c r="I13" s="24" t="s">
         <v>116</v>
       </c>
-      <c r="J13" s="35" t="s">
+      <c r="J13" s="25" t="s">
         <v>149</v>
       </c>
-      <c r="K13" s="36" t="s">
+      <c r="K13" s="26" t="s">
         <v>150</v>
       </c>
-      <c r="L13" s="43" t="s">
+      <c r="L13" s="33" t="s">
         <v>162</v>
       </c>
       <c r="M13" t="s">
@@ -4502,7 +4507,7 @@
         <f t="shared" si="0"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0012-G.png</v>
       </c>
-      <c r="O13" s="136" t="str">
+      <c r="O13" s="110" t="str">
         <f t="shared" si="1"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0012-G.png</v>
       </c>
@@ -4523,28 +4528,28 @@
       <c r="D14" s="13">
         <v>38136</v>
       </c>
-      <c r="E14" s="16">
+      <c r="E14" s="128">
         <v>213011040932</v>
       </c>
-      <c r="F14" s="22">
+      <c r="F14" s="145">
         <v>45065</v>
       </c>
       <c r="G14" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="H14" s="29" t="s">
+      <c r="H14" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="I14" s="34" t="s">
+      <c r="I14" s="24" t="s">
         <v>117</v>
       </c>
-      <c r="J14" s="35" t="s">
+      <c r="J14" s="25" t="s">
         <v>149</v>
       </c>
-      <c r="K14" s="36" t="s">
+      <c r="K14" s="26" t="s">
         <v>150</v>
       </c>
-      <c r="L14" s="41" t="s">
+      <c r="L14" s="31" t="s">
         <v>163</v>
       </c>
       <c r="M14" t="s">
@@ -4554,7 +4559,7 @@
         <f t="shared" si="0"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0013-G.png</v>
       </c>
-      <c r="O14" s="136" t="str">
+      <c r="O14" s="110" t="str">
         <f t="shared" si="1"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0013-G.png</v>
       </c>
@@ -4575,28 +4580,28 @@
       <c r="D15" s="12">
         <v>38570</v>
       </c>
-      <c r="E15" s="15">
+      <c r="E15" s="126">
         <v>214011117917</v>
       </c>
-      <c r="F15" s="21">
+      <c r="F15" s="144">
         <v>45154</v>
       </c>
       <c r="G15" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="H15" s="28" t="s">
+      <c r="H15" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="I15" s="33" t="s">
+      <c r="I15" s="23" t="s">
         <v>118</v>
       </c>
-      <c r="J15" s="35" t="s">
+      <c r="J15" s="25" t="s">
         <v>149</v>
       </c>
-      <c r="K15" s="36" t="s">
+      <c r="K15" s="26" t="s">
         <v>150</v>
       </c>
-      <c r="L15" s="40" t="s">
+      <c r="L15" s="30" t="s">
         <v>164</v>
       </c>
       <c r="M15" t="s">
@@ -4606,7 +4611,7 @@
         <f t="shared" si="0"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0014-G.png</v>
       </c>
-      <c r="O15" s="136" t="str">
+      <c r="O15" s="110" t="str">
         <f t="shared" si="1"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0014-G.png</v>
       </c>
@@ -4627,28 +4632,28 @@
       <c r="D16" s="13">
         <v>36234</v>
       </c>
-      <c r="E16" s="17">
+      <c r="E16" s="129">
         <v>213051008903</v>
       </c>
-      <c r="F16" s="22">
+      <c r="F16" s="145">
         <v>44355</v>
       </c>
       <c r="G16" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="H16" s="29" t="s">
+      <c r="H16" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="I16" s="34" t="s">
+      <c r="I16" s="24" t="s">
         <v>119</v>
       </c>
-      <c r="J16" s="35" t="s">
+      <c r="J16" s="25" t="s">
         <v>149</v>
       </c>
-      <c r="K16" s="36" t="s">
+      <c r="K16" s="26" t="s">
         <v>150</v>
       </c>
-      <c r="L16" s="43" t="s">
+      <c r="L16" s="33" t="s">
         <v>165</v>
       </c>
       <c r="M16" t="s">
@@ -4658,7 +4663,7 @@
         <f t="shared" si="0"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0015-G.png</v>
       </c>
-      <c r="O16" s="136" t="str">
+      <c r="O16" s="110" t="str">
         <f t="shared" si="1"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0015-G.png</v>
       </c>
@@ -4679,28 +4684,28 @@
       <c r="D17" s="13">
         <v>39459</v>
       </c>
-      <c r="E17" s="146">
+      <c r="E17" s="130">
         <v>213272009416</v>
       </c>
-      <c r="F17" s="147">
+      <c r="F17" s="146">
         <v>46036</v>
       </c>
       <c r="G17" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="H17" s="29" t="s">
+      <c r="H17" s="19" t="s">
         <v>95</v>
       </c>
-      <c r="I17" s="34" t="s">
+      <c r="I17" s="24" t="s">
         <v>120</v>
       </c>
-      <c r="J17" s="35" t="s">
+      <c r="J17" s="25" t="s">
         <v>149</v>
       </c>
-      <c r="K17" s="36" t="s">
+      <c r="K17" s="26" t="s">
         <v>150</v>
       </c>
-      <c r="L17" s="41" t="s">
+      <c r="L17" s="31" t="s">
         <v>166</v>
       </c>
       <c r="M17" t="s">
@@ -4710,7 +4715,7 @@
         <f t="shared" si="0"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0016-G.png</v>
       </c>
-      <c r="O17" s="136" t="str">
+      <c r="O17" s="110" t="str">
         <f t="shared" si="1"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0016-G.png</v>
       </c>
@@ -4731,28 +4736,28 @@
       <c r="D18" s="12">
         <v>38530</v>
       </c>
-      <c r="E18" s="15">
+      <c r="E18" s="126">
         <v>213391018590</v>
       </c>
-      <c r="F18" s="21">
+      <c r="F18" s="144">
         <v>45247</v>
       </c>
       <c r="G18" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="H18" s="28" t="s">
+      <c r="H18" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="I18" s="33" t="s">
+      <c r="I18" s="23" t="s">
         <v>121</v>
       </c>
-      <c r="J18" s="35" t="s">
+      <c r="J18" s="25" t="s">
         <v>149</v>
       </c>
-      <c r="K18" s="36" t="s">
+      <c r="K18" s="26" t="s">
         <v>150</v>
       </c>
-      <c r="L18" s="40" t="s">
+      <c r="L18" s="30" t="s">
         <v>167</v>
       </c>
       <c r="M18" t="s">
@@ -4762,7 +4767,7 @@
         <f t="shared" si="0"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0017-G.png</v>
       </c>
-      <c r="O18" s="136" t="str">
+      <c r="O18" s="110" t="str">
         <f t="shared" si="1"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0017-G.png</v>
       </c>
@@ -4783,28 +4788,28 @@
       <c r="D19" s="12">
         <v>37934</v>
       </c>
-      <c r="E19" s="15">
+      <c r="E19" s="126">
         <v>213011039640</v>
       </c>
-      <c r="F19" s="21">
+      <c r="F19" s="144">
         <v>44881</v>
       </c>
       <c r="G19" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="H19" s="28" t="s">
+      <c r="H19" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="I19" s="33" t="s">
+      <c r="I19" s="23" t="s">
         <v>122</v>
       </c>
-      <c r="J19" s="35" t="s">
+      <c r="J19" s="25" t="s">
         <v>149</v>
       </c>
-      <c r="K19" s="36" t="s">
+      <c r="K19" s="26" t="s">
         <v>150</v>
       </c>
-      <c r="L19" s="40" t="s">
+      <c r="L19" s="30" t="s">
         <v>168</v>
       </c>
       <c r="M19" t="s">
@@ -4814,7 +4819,7 @@
         <f t="shared" si="0"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0018-G.png</v>
       </c>
-      <c r="O19" s="136" t="str">
+      <c r="O19" s="110" t="str">
         <f t="shared" si="1"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0018-G.png</v>
       </c>
@@ -4835,28 +4840,28 @@
       <c r="D20" s="12">
         <v>38618</v>
       </c>
-      <c r="E20" s="15">
+      <c r="E20" s="126">
         <v>213011041537</v>
       </c>
-      <c r="F20" s="21">
+      <c r="F20" s="144">
         <v>45209</v>
       </c>
       <c r="G20" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="H20" s="28" t="s">
+      <c r="H20" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="I20" s="33" t="s">
+      <c r="I20" s="23" t="s">
         <v>123</v>
       </c>
-      <c r="J20" s="35" t="s">
+      <c r="J20" s="25" t="s">
         <v>149</v>
       </c>
-      <c r="K20" s="36" t="s">
+      <c r="K20" s="26" t="s">
         <v>150</v>
       </c>
-      <c r="L20" s="39" t="s">
+      <c r="L20" s="29" t="s">
         <v>169</v>
       </c>
       <c r="M20" t="s">
@@ -4866,7 +4871,7 @@
         <f t="shared" si="0"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0019-G.png</v>
       </c>
-      <c r="O20" s="136" t="str">
+      <c r="O20" s="110" t="str">
         <f t="shared" si="1"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0019-G.png</v>
       </c>
@@ -4887,28 +4892,28 @@
       <c r="D21" s="13">
         <v>33968</v>
       </c>
-      <c r="E21" s="17">
+      <c r="E21" s="129">
         <v>217011009886</v>
       </c>
-      <c r="F21" s="22">
+      <c r="F21" s="145">
         <v>41519</v>
       </c>
       <c r="G21" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="H21" s="29" t="s">
+      <c r="H21" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="I21" s="34" t="s">
+      <c r="I21" s="24" t="s">
         <v>124</v>
       </c>
-      <c r="J21" s="35" t="s">
+      <c r="J21" s="25" t="s">
         <v>149</v>
       </c>
-      <c r="K21" s="36" t="s">
+      <c r="K21" s="26" t="s">
         <v>150</v>
       </c>
-      <c r="L21" s="43" t="s">
+      <c r="L21" s="33" t="s">
         <v>170</v>
       </c>
       <c r="M21" t="s">
@@ -4918,7 +4923,7 @@
         <f t="shared" si="0"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0020-G.png</v>
       </c>
-      <c r="O21" s="136" t="str">
+      <c r="O21" s="110" t="str">
         <f t="shared" si="1"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0020-G.png</v>
       </c>
@@ -4939,28 +4944,28 @@
       <c r="D22" s="12">
         <v>37691</v>
       </c>
-      <c r="E22" s="15">
+      <c r="E22" s="126">
         <v>213012037306</v>
       </c>
-      <c r="F22" s="23">
+      <c r="F22" s="147">
         <v>44494</v>
       </c>
-      <c r="G22" s="25" t="s">
+      <c r="G22" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="H22" s="28" t="s">
+      <c r="H22" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="I22" s="33" t="s">
+      <c r="I22" s="23" t="s">
         <v>125</v>
       </c>
-      <c r="J22" s="35" t="s">
+      <c r="J22" s="25" t="s">
         <v>149</v>
       </c>
-      <c r="K22" s="36" t="s">
+      <c r="K22" s="26" t="s">
         <v>150</v>
       </c>
-      <c r="L22" s="40" t="s">
+      <c r="L22" s="30" t="s">
         <v>171</v>
       </c>
       <c r="M22" t="s">
@@ -4970,7 +4975,7 @@
         <f t="shared" si="0"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0021-G.png</v>
       </c>
-      <c r="O22" s="136" t="str">
+      <c r="O22" s="110" t="str">
         <f t="shared" si="1"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0021-G.png</v>
       </c>
@@ -4988,31 +4993,31 @@
       <c r="C23" s="3" t="s">
         <v>746</v>
       </c>
-      <c r="D23" s="144">
+      <c r="D23" s="118">
         <v>38869</v>
       </c>
-      <c r="E23" s="15">
+      <c r="E23" s="126">
         <v>213112007904</v>
       </c>
-      <c r="F23" s="23">
+      <c r="F23" s="147">
         <v>45370</v>
       </c>
-      <c r="G23" s="25" t="s">
+      <c r="G23" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="H23" s="28" t="s">
+      <c r="H23" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="I23" s="33" t="s">
+      <c r="I23" s="23" t="s">
         <v>126</v>
       </c>
-      <c r="J23" s="35" t="s">
+      <c r="J23" s="25" t="s">
         <v>149</v>
       </c>
-      <c r="K23" s="36" t="s">
+      <c r="K23" s="26" t="s">
         <v>150</v>
       </c>
-      <c r="L23" s="39" t="s">
+      <c r="L23" s="29" t="s">
         <v>172</v>
       </c>
       <c r="M23" t="s">
@@ -5022,7 +5027,7 @@
         <f t="shared" si="0"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0022-G.png</v>
       </c>
-      <c r="O23" s="136" t="str">
+      <c r="O23" s="110" t="str">
         <f t="shared" si="1"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0022-G.png</v>
       </c>
@@ -5034,7 +5039,7 @@
       <c r="A24" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="B24" s="145" t="s">
+      <c r="B24" s="119" t="s">
         <v>703</v>
       </c>
       <c r="C24" s="3" t="s">
@@ -5043,28 +5048,28 @@
       <c r="D24" s="12">
         <v>38779</v>
       </c>
-      <c r="E24" s="15">
+      <c r="E24" s="126">
         <v>213592006673</v>
       </c>
-      <c r="F24" s="21">
+      <c r="F24" s="144">
         <v>45670</v>
       </c>
       <c r="G24" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="H24" s="28" t="s">
+      <c r="H24" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="I24" s="33" t="s">
+      <c r="I24" s="23" t="s">
         <v>127</v>
       </c>
-      <c r="J24" s="35" t="s">
+      <c r="J24" s="25" t="s">
         <v>149</v>
       </c>
-      <c r="K24" s="36" t="s">
+      <c r="K24" s="26" t="s">
         <v>150</v>
       </c>
-      <c r="L24" s="40" t="s">
+      <c r="L24" s="30" t="s">
         <v>173</v>
       </c>
       <c r="M24" t="s">
@@ -5074,7 +5079,7 @@
         <f t="shared" si="0"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0023-G.png</v>
       </c>
-      <c r="O24" s="136" t="str">
+      <c r="O24" s="110" t="str">
         <f t="shared" si="1"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0023-G.png</v>
       </c>
@@ -5092,31 +5097,31 @@
       <c r="C25" s="3" t="s">
         <v>744</v>
       </c>
-      <c r="D25" s="143">
+      <c r="D25" s="117">
         <v>36892</v>
       </c>
-      <c r="E25" s="15">
+      <c r="E25" s="126">
         <v>213111004494</v>
       </c>
-      <c r="F25" s="22">
+      <c r="F25" s="145">
         <v>44720</v>
       </c>
       <c r="G25" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="H25" s="29" t="s">
+      <c r="H25" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="I25" s="34" t="s">
+      <c r="I25" s="24" t="s">
         <v>128</v>
       </c>
-      <c r="J25" s="35" t="s">
+      <c r="J25" s="25" t="s">
         <v>149</v>
       </c>
-      <c r="K25" s="36" t="s">
+      <c r="K25" s="26" t="s">
         <v>150</v>
       </c>
-      <c r="L25" s="41" t="s">
+      <c r="L25" s="31" t="s">
         <v>174</v>
       </c>
       <c r="M25" t="s">
@@ -5126,7 +5131,7 @@
         <f t="shared" si="0"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0024-G.png</v>
       </c>
-      <c r="O25" s="136" t="str">
+      <c r="O25" s="110" t="str">
         <f t="shared" si="1"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0024-G.png</v>
       </c>
@@ -5147,28 +5152,28 @@
       <c r="D26" s="12">
         <v>37443</v>
       </c>
-      <c r="E26" s="15">
+      <c r="E26" s="126">
         <v>214051103166</v>
       </c>
-      <c r="F26" s="21">
+      <c r="F26" s="144">
         <v>44739</v>
       </c>
       <c r="G26" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="H26" s="28" t="s">
+      <c r="H26" s="18" t="s">
         <v>98</v>
       </c>
-      <c r="I26" s="33" t="s">
+      <c r="I26" s="23" t="s">
         <v>129</v>
       </c>
-      <c r="J26" s="35" t="s">
+      <c r="J26" s="25" t="s">
         <v>149</v>
       </c>
-      <c r="K26" s="36" t="s">
+      <c r="K26" s="26" t="s">
         <v>150</v>
       </c>
-      <c r="L26" s="40" t="s">
+      <c r="L26" s="30" t="s">
         <v>175</v>
       </c>
       <c r="M26" t="s">
@@ -5178,7 +5183,7 @@
         <f t="shared" si="0"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0025-G.png</v>
       </c>
-      <c r="O26" s="136" t="str">
+      <c r="O26" s="110" t="str">
         <f t="shared" si="1"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0025-G.png</v>
       </c>
@@ -5197,28 +5202,28 @@
       <c r="D27" s="12">
         <v>38272</v>
       </c>
-      <c r="E27" s="15">
+      <c r="E27" s="126">
         <v>213391019113</v>
       </c>
-      <c r="F27" s="21">
+      <c r="F27" s="144">
         <v>45677</v>
       </c>
       <c r="G27" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="H27" s="28" t="s">
+      <c r="H27" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="I27" s="33" t="s">
+      <c r="I27" s="23" t="s">
         <v>130</v>
       </c>
-      <c r="J27" s="35" t="s">
+      <c r="J27" s="25" t="s">
         <v>149</v>
       </c>
-      <c r="K27" s="36" t="s">
+      <c r="K27" s="26" t="s">
         <v>150</v>
       </c>
-      <c r="L27" s="40" t="s">
+      <c r="L27" s="30" t="s">
         <v>176</v>
       </c>
       <c r="M27" t="s">
@@ -5228,7 +5233,7 @@
         <f t="shared" si="0"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0026-G.png</v>
       </c>
-      <c r="O27" s="136" t="str">
+      <c r="O27" s="110" t="str">
         <f t="shared" si="1"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0026-G.png</v>
       </c>
@@ -5249,28 +5254,28 @@
       <c r="D28" s="12">
         <v>39040</v>
       </c>
-      <c r="E28" s="15">
+      <c r="E28" s="126">
         <v>214012119511</v>
       </c>
-      <c r="F28" s="21">
+      <c r="F28" s="144">
         <v>45663</v>
       </c>
       <c r="G28" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="H28" s="28" t="s">
+      <c r="H28" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="I28" s="33" t="s">
+      <c r="I28" s="23" t="s">
         <v>131</v>
       </c>
-      <c r="J28" s="35" t="s">
+      <c r="J28" s="25" t="s">
         <v>149</v>
       </c>
-      <c r="K28" s="36" t="s">
+      <c r="K28" s="26" t="s">
         <v>150</v>
       </c>
-      <c r="L28" s="40" t="s">
+      <c r="L28" s="30" t="s">
         <v>177</v>
       </c>
       <c r="M28" t="s">
@@ -5280,7 +5285,7 @@
         <f t="shared" si="0"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0027-G.png</v>
       </c>
-      <c r="O28" s="136" t="str">
+      <c r="O28" s="110" t="str">
         <f t="shared" si="1"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0027-G.png</v>
       </c>
@@ -5301,28 +5306,28 @@
       <c r="D29" s="12">
         <v>38416</v>
       </c>
-      <c r="E29" s="15">
+      <c r="E29" s="126">
         <v>213011042792</v>
       </c>
-      <c r="F29" s="21">
+      <c r="F29" s="144">
         <v>45491</v>
       </c>
       <c r="G29" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="H29" s="28" t="s">
+      <c r="H29" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="I29" s="33" t="s">
+      <c r="I29" s="23" t="s">
         <v>132</v>
       </c>
-      <c r="J29" s="35" t="s">
+      <c r="J29" s="25" t="s">
         <v>149</v>
       </c>
-      <c r="K29" s="36" t="s">
+      <c r="K29" s="26" t="s">
         <v>150</v>
       </c>
-      <c r="L29" s="40" t="s">
+      <c r="L29" s="30" t="s">
         <v>178</v>
       </c>
       <c r="M29" t="s">
@@ -5332,7 +5337,7 @@
         <f t="shared" si="0"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0028-G.png</v>
       </c>
-      <c r="O29" s="136" t="str">
+      <c r="O29" s="110" t="str">
         <f t="shared" si="1"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0028-G.png</v>
       </c>
@@ -5344,7 +5349,7 @@
       <c r="A30" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="B30" s="145" t="s">
+      <c r="B30" s="119" t="s">
         <v>704</v>
       </c>
       <c r="C30" s="3" t="s">
@@ -5353,28 +5358,28 @@
       <c r="D30" s="12">
         <v>38128</v>
       </c>
-      <c r="E30" s="15">
+      <c r="E30" s="126">
         <v>214011119521</v>
       </c>
-      <c r="F30" s="21">
+      <c r="F30" s="144">
         <v>45664</v>
       </c>
       <c r="G30" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="H30" s="28" t="s">
+      <c r="H30" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="I30" s="33" t="s">
+      <c r="I30" s="23" t="s">
         <v>133</v>
       </c>
-      <c r="J30" s="35" t="s">
+      <c r="J30" s="25" t="s">
         <v>149</v>
       </c>
-      <c r="K30" s="36" t="s">
+      <c r="K30" s="26" t="s">
         <v>150</v>
       </c>
-      <c r="L30" s="40" t="s">
+      <c r="L30" s="30" t="s">
         <v>179</v>
       </c>
       <c r="M30" t="s">
@@ -5384,7 +5389,7 @@
         <f t="shared" si="0"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0029-G.png</v>
       </c>
-      <c r="O30" s="136" t="str">
+      <c r="O30" s="110" t="str">
         <f t="shared" si="1"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0029-G.png</v>
       </c>
@@ -5396,7 +5401,7 @@
       <c r="A31" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="B31" s="145" t="s">
+      <c r="B31" s="119" t="s">
         <v>705</v>
       </c>
       <c r="C31" s="3" t="s">
@@ -5405,28 +5410,28 @@
       <c r="D31" s="12">
         <v>37653</v>
       </c>
-      <c r="E31" s="18">
+      <c r="E31" s="131">
         <v>243012138454</v>
       </c>
-      <c r="F31" s="21">
+      <c r="F31" s="144">
         <v>44740</v>
       </c>
       <c r="G31" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="H31" s="28" t="s">
+      <c r="H31" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="I31" s="33" t="s">
+      <c r="I31" s="23" t="s">
         <v>134</v>
       </c>
-      <c r="J31" s="35" t="s">
+      <c r="J31" s="25" t="s">
         <v>149</v>
       </c>
-      <c r="K31" s="36" t="s">
+      <c r="K31" s="26" t="s">
         <v>150</v>
       </c>
-      <c r="L31" s="44" t="s">
+      <c r="L31" s="34" t="s">
         <v>180</v>
       </c>
       <c r="M31" t="s">
@@ -5436,7 +5441,7 @@
         <f t="shared" si="0"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0030-G.png</v>
       </c>
-      <c r="O31" s="136" t="str">
+      <c r="O31" s="110" t="str">
         <f t="shared" si="1"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0030-G.png</v>
       </c>
@@ -5457,28 +5462,28 @@
       <c r="D32" s="13">
         <v>37800</v>
       </c>
-      <c r="E32" s="19">
+      <c r="E32" s="132">
         <v>214231105065</v>
       </c>
-      <c r="F32" s="22">
+      <c r="F32" s="145">
         <v>45447</v>
       </c>
       <c r="G32" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="H32" s="29" t="s">
+      <c r="H32" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="I32" s="34" t="s">
+      <c r="I32" s="24" t="s">
         <v>135</v>
       </c>
-      <c r="J32" s="35" t="s">
+      <c r="J32" s="25" t="s">
         <v>149</v>
       </c>
-      <c r="K32" s="36" t="s">
+      <c r="K32" s="26" t="s">
         <v>150</v>
       </c>
-      <c r="L32" s="41" t="s">
+      <c r="L32" s="31" t="s">
         <v>181</v>
       </c>
       <c r="M32" t="s">
@@ -5488,7 +5493,7 @@
         <f t="shared" si="0"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0031-G.png</v>
       </c>
-      <c r="O32" s="136" t="str">
+      <c r="O32" s="110" t="str">
         <f t="shared" si="1"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0031-G.png</v>
       </c>
@@ -5507,28 +5512,28 @@
       <c r="D33" s="12">
         <v>38717</v>
       </c>
-      <c r="E33" s="15">
+      <c r="E33" s="126">
         <v>213112007963</v>
       </c>
-      <c r="F33" s="23">
+      <c r="F33" s="147">
         <v>45322</v>
       </c>
-      <c r="G33" s="25" t="s">
+      <c r="G33" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="H33" s="28" t="s">
+      <c r="H33" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="I33" s="33" t="s">
+      <c r="I33" s="23" t="s">
         <v>136</v>
       </c>
-      <c r="J33" s="35" t="s">
+      <c r="J33" s="25" t="s">
         <v>149</v>
       </c>
-      <c r="K33" s="36" t="s">
+      <c r="K33" s="26" t="s">
         <v>150</v>
       </c>
-      <c r="L33" s="39" t="s">
+      <c r="L33" s="29" t="s">
         <v>182</v>
       </c>
       <c r="M33" t="s">
@@ -5538,7 +5543,7 @@
         <f t="shared" si="0"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0032-G.png</v>
       </c>
-      <c r="O33" s="136" t="str">
+      <c r="O33" s="110" t="str">
         <f t="shared" si="1"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0032-G.png</v>
       </c>
@@ -5557,28 +5562,28 @@
       <c r="D34" s="12">
         <v>37777</v>
       </c>
-      <c r="E34" s="15">
+      <c r="E34" s="126">
         <v>213011041069</v>
       </c>
-      <c r="F34" s="24">
+      <c r="F34" s="148">
         <v>45086</v>
       </c>
-      <c r="G34" s="26" t="s">
+      <c r="G34" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="H34" s="28" t="s">
+      <c r="H34" s="18" t="s">
         <v>93</v>
       </c>
-      <c r="I34" s="33" t="s">
+      <c r="I34" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="J34" s="35" t="s">
+      <c r="J34" s="25" t="s">
         <v>149</v>
       </c>
-      <c r="K34" s="36" t="s">
+      <c r="K34" s="26" t="s">
         <v>150</v>
       </c>
-      <c r="L34" s="39" t="s">
+      <c r="L34" s="29" t="s">
         <v>183</v>
       </c>
       <c r="M34" t="s">
@@ -5588,7 +5593,7 @@
         <f t="shared" ref="N34:N65" si="2">"https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/" &amp; C34 &amp; ".png"</f>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0033-G.png</v>
       </c>
-      <c r="O34" s="136" t="str">
+      <c r="O34" s="110" t="str">
         <f t="shared" ref="O34:O65" si="3">"https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/" &amp; C34 &amp; ".png"</f>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0033-G.png</v>
       </c>
@@ -5597,7 +5602,7 @@
       </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="148" t="s">
+      <c r="A35" s="120" t="s">
         <v>708</v>
       </c>
       <c r="B35" s="7" t="s">
@@ -5609,28 +5614,28 @@
       <c r="D35" s="12">
         <v>38293</v>
       </c>
-      <c r="E35" s="15">
+      <c r="E35" s="126">
         <v>213012041822</v>
       </c>
-      <c r="F35" s="21">
+      <c r="F35" s="144">
         <v>45287</v>
       </c>
       <c r="G35" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="H35" s="28" t="s">
+      <c r="H35" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="I35" s="33" t="s">
+      <c r="I35" s="23" t="s">
         <v>532</v>
       </c>
-      <c r="J35" s="35" t="s">
+      <c r="J35" s="25" t="s">
         <v>149</v>
       </c>
-      <c r="K35" s="36" t="s">
+      <c r="K35" s="26" t="s">
         <v>150</v>
       </c>
-      <c r="L35" s="40" t="s">
+      <c r="L35" s="30" t="s">
         <v>184</v>
       </c>
       <c r="M35" t="s">
@@ -5640,7 +5645,7 @@
         <f t="shared" si="2"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0034-G.png</v>
       </c>
-      <c r="O35" s="136" t="str">
+      <c r="O35" s="110" t="str">
         <f t="shared" si="3"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0034-G.png</v>
       </c>
@@ -5658,31 +5663,31 @@
       <c r="C36" s="3" t="s">
         <v>733</v>
       </c>
-      <c r="D36" s="143">
+      <c r="D36" s="117">
         <v>37987</v>
       </c>
-      <c r="E36" s="18">
+      <c r="E36" s="131">
         <v>214091102033</v>
       </c>
-      <c r="F36" s="22">
+      <c r="F36" s="145">
         <v>45362</v>
       </c>
       <c r="G36" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="H36" s="29" t="s">
+      <c r="H36" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="I36" s="34" t="s">
+      <c r="I36" s="24" t="s">
         <v>138</v>
       </c>
-      <c r="J36" s="35" t="s">
+      <c r="J36" s="25" t="s">
         <v>149</v>
       </c>
-      <c r="K36" s="36" t="s">
+      <c r="K36" s="26" t="s">
         <v>150</v>
       </c>
-      <c r="L36" s="41" t="s">
+      <c r="L36" s="31" t="s">
         <v>185</v>
       </c>
       <c r="M36" t="s">
@@ -5692,7 +5697,7 @@
         <f t="shared" si="2"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0035-G.png</v>
       </c>
-      <c r="O36" s="136" t="str">
+      <c r="O36" s="110" t="str">
         <f t="shared" si="3"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0035-G.png</v>
       </c>
@@ -5704,7 +5709,7 @@
       <c r="A37" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="B37" s="140" t="s">
+      <c r="B37" s="114" t="s">
         <v>706</v>
       </c>
       <c r="C37" s="3" t="s">
@@ -5713,28 +5718,28 @@
       <c r="D37" s="13">
         <v>39304</v>
       </c>
-      <c r="E37" s="19">
+      <c r="E37" s="132">
         <v>213011044882</v>
       </c>
-      <c r="F37" s="22">
+      <c r="F37" s="145">
         <v>45947</v>
       </c>
       <c r="G37" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="H37" s="29" t="s">
+      <c r="H37" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="I37" s="34" t="s">
+      <c r="I37" s="24" t="s">
         <v>139</v>
       </c>
-      <c r="J37" s="35" t="s">
+      <c r="J37" s="25" t="s">
         <v>149</v>
       </c>
-      <c r="K37" s="36" t="s">
+      <c r="K37" s="26" t="s">
         <v>150</v>
       </c>
-      <c r="L37" s="41" t="s">
+      <c r="L37" s="31" t="s">
         <v>186</v>
       </c>
       <c r="M37" t="s">
@@ -5744,7 +5749,7 @@
         <f t="shared" si="2"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0036-G.png</v>
       </c>
-      <c r="O37" s="136" t="str">
+      <c r="O37" s="110" t="str">
         <f t="shared" si="3"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0036-G.png</v>
       </c>
@@ -5756,7 +5761,7 @@
       <c r="A38" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="B38" s="140" t="s">
+      <c r="B38" s="114" t="s">
         <v>709</v>
       </c>
       <c r="C38" s="3" t="s">
@@ -5765,28 +5770,28 @@
       <c r="D38" s="13">
         <v>36220</v>
       </c>
-      <c r="E38" s="20">
+      <c r="E38" s="133">
         <v>213051007998</v>
       </c>
-      <c r="F38" s="147">
+      <c r="F38" s="146">
         <v>42810</v>
       </c>
       <c r="G38" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="H38" s="29" t="s">
+      <c r="H38" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="I38" s="34" t="s">
+      <c r="I38" s="24" t="s">
         <v>140</v>
       </c>
-      <c r="J38" s="35" t="s">
+      <c r="J38" s="25" t="s">
         <v>149</v>
       </c>
-      <c r="K38" s="36" t="s">
+      <c r="K38" s="26" t="s">
         <v>150</v>
       </c>
-      <c r="L38" s="43" t="s">
+      <c r="L38" s="33" t="s">
         <v>187</v>
       </c>
       <c r="M38" t="s">
@@ -5796,7 +5801,7 @@
         <f t="shared" si="2"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0037-G.png</v>
       </c>
-      <c r="O38" s="136" t="str">
+      <c r="O38" s="110" t="str">
         <f t="shared" si="3"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0037-G.png</v>
       </c>
@@ -5814,10 +5819,10 @@
       <c r="C39" s="3" t="s">
         <v>730</v>
       </c>
-      <c r="D39" s="144">
+      <c r="D39" s="118">
         <v>38353</v>
       </c>
-      <c r="E39" s="18">
+      <c r="E39" s="131">
         <v>213011044180</v>
       </c>
       <c r="F39" s="149">
@@ -5826,19 +5831,19 @@
       <c r="G39" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="H39" s="28" t="s">
+      <c r="H39" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="I39" s="33" t="s">
+      <c r="I39" s="23" t="s">
         <v>141</v>
       </c>
-      <c r="J39" s="35" t="s">
+      <c r="J39" s="25" t="s">
         <v>149</v>
       </c>
-      <c r="K39" s="36" t="s">
+      <c r="K39" s="26" t="s">
         <v>150</v>
       </c>
-      <c r="L39" s="39" t="s">
+      <c r="L39" s="29" t="s">
         <v>188</v>
       </c>
       <c r="M39" t="s">
@@ -5848,7 +5853,7 @@
         <f t="shared" si="2"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0038-G.png</v>
       </c>
-      <c r="O39" s="136" t="str">
+      <c r="O39" s="110" t="str">
         <f t="shared" si="3"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0038-G.png</v>
       </c>
@@ -5867,28 +5872,28 @@
       <c r="D40" s="12">
         <v>38189</v>
       </c>
-      <c r="E40" s="18">
+      <c r="E40" s="131">
         <v>213551008783</v>
       </c>
-      <c r="F40" s="21">
+      <c r="F40" s="144">
         <v>44951</v>
       </c>
       <c r="G40" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="H40" s="28" t="s">
+      <c r="H40" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="I40" s="33" t="s">
+      <c r="I40" s="23" t="s">
         <v>142</v>
       </c>
-      <c r="J40" s="35" t="s">
+      <c r="J40" s="25" t="s">
         <v>149</v>
       </c>
-      <c r="K40" s="36" t="s">
+      <c r="K40" s="26" t="s">
         <v>150</v>
       </c>
-      <c r="L40" s="39" t="s">
+      <c r="L40" s="29" t="s">
         <v>189</v>
       </c>
       <c r="M40" t="s">
@@ -5898,7 +5903,7 @@
         <f t="shared" si="2"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0039-G.png</v>
       </c>
-      <c r="O40" s="136" t="str">
+      <c r="O40" s="110" t="str">
         <f t="shared" si="3"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0039-G.png</v>
       </c>
@@ -5914,31 +5919,31 @@
       <c r="C41" s="3" t="s">
         <v>728</v>
       </c>
-      <c r="D41" s="143">
+      <c r="D41" s="117">
         <v>38353</v>
       </c>
-      <c r="E41" s="19">
+      <c r="E41" s="132">
         <v>213011042135</v>
       </c>
-      <c r="F41" s="22">
+      <c r="F41" s="145">
         <v>45351</v>
       </c>
       <c r="G41" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="H41" s="29" t="s">
+      <c r="H41" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="I41" s="34" t="s">
+      <c r="I41" s="24" t="s">
         <v>143</v>
       </c>
-      <c r="J41" s="35" t="s">
+      <c r="J41" s="25" t="s">
         <v>149</v>
       </c>
-      <c r="K41" s="36" t="s">
+      <c r="K41" s="26" t="s">
         <v>150</v>
       </c>
-      <c r="L41" s="41" t="s">
+      <c r="L41" s="31" t="s">
         <v>190</v>
       </c>
       <c r="M41" t="s">
@@ -5948,7 +5953,7 @@
         <f t="shared" si="2"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0040-G.png</v>
       </c>
-      <c r="O41" s="136" t="str">
+      <c r="O41" s="110" t="str">
         <f t="shared" si="3"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0040-G.png</v>
       </c>
@@ -5964,31 +5969,31 @@
       <c r="C42" s="3" t="s">
         <v>727</v>
       </c>
-      <c r="D42" s="144">
+      <c r="D42" s="118">
         <v>37880</v>
       </c>
-      <c r="E42" s="18">
+      <c r="E42" s="131">
         <v>214011115346</v>
       </c>
-      <c r="F42" s="21">
+      <c r="F42" s="144">
         <v>44708</v>
       </c>
       <c r="G42" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="H42" s="28" t="s">
+      <c r="H42" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="I42" s="33" t="s">
+      <c r="I42" s="23" t="s">
         <v>144</v>
       </c>
-      <c r="J42" s="35" t="s">
+      <c r="J42" s="25" t="s">
         <v>149</v>
       </c>
-      <c r="K42" s="36" t="s">
+      <c r="K42" s="26" t="s">
         <v>150</v>
       </c>
-      <c r="L42" s="45" t="s">
+      <c r="L42" s="35" t="s">
         <v>191</v>
       </c>
       <c r="M42" t="s">
@@ -5998,7 +6003,7 @@
         <f t="shared" si="2"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0041-G.png</v>
       </c>
-      <c r="O42" s="136" t="str">
+      <c r="O42" s="110" t="str">
         <f t="shared" si="3"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0041-G.png</v>
       </c>
@@ -6019,28 +6024,28 @@
       <c r="D43" s="13">
         <v>37624</v>
       </c>
-      <c r="E43" s="20">
+      <c r="E43" s="133">
         <v>213012036387</v>
       </c>
-      <c r="F43" s="22">
+      <c r="F43" s="145">
         <v>44249</v>
       </c>
       <c r="G43" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="H43" s="29" t="s">
+      <c r="H43" s="19" t="s">
         <v>97</v>
       </c>
-      <c r="I43" s="34" t="s">
+      <c r="I43" s="24" t="s">
         <v>145</v>
       </c>
-      <c r="J43" s="35" t="s">
+      <c r="J43" s="25" t="s">
         <v>149</v>
       </c>
-      <c r="K43" s="36" t="s">
+      <c r="K43" s="26" t="s">
         <v>150</v>
       </c>
-      <c r="L43" s="43" t="s">
+      <c r="L43" s="33" t="s">
         <v>192</v>
       </c>
       <c r="M43" t="s">
@@ -6050,7 +6055,7 @@
         <f t="shared" si="2"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0042-G.png</v>
       </c>
-      <c r="O43" s="136" t="str">
+      <c r="O43" s="110" t="str">
         <f t="shared" si="3"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0042-G.png</v>
       </c>
@@ -6068,31 +6073,31 @@
       <c r="C44" s="3" t="s">
         <v>725</v>
       </c>
-      <c r="D44" s="144">
+      <c r="D44" s="118">
         <v>38718</v>
       </c>
-      <c r="E44" s="18">
+      <c r="E44" s="131">
         <v>213152003984</v>
       </c>
-      <c r="F44" s="21">
+      <c r="F44" s="144">
         <v>45503</v>
       </c>
       <c r="G44" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="H44" s="28" t="s">
+      <c r="H44" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="I44" s="33" t="s">
+      <c r="I44" s="23" t="s">
         <v>146</v>
       </c>
-      <c r="J44" s="35" t="s">
+      <c r="J44" s="25" t="s">
         <v>149</v>
       </c>
-      <c r="K44" s="36" t="s">
+      <c r="K44" s="26" t="s">
         <v>150</v>
       </c>
-      <c r="L44" s="46" t="s">
+      <c r="L44" s="36" t="s">
         <v>193</v>
       </c>
       <c r="M44" t="s">
@@ -6102,7 +6107,7 @@
         <f t="shared" si="2"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0043-G.png</v>
       </c>
-      <c r="O44" s="136" t="str">
+      <c r="O44" s="110" t="str">
         <f t="shared" si="3"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0043-G.png</v>
       </c>
@@ -6121,28 +6126,28 @@
       <c r="D45" s="12">
         <v>38479</v>
       </c>
-      <c r="E45" s="18">
+      <c r="E45" s="131">
         <v>213391019169</v>
       </c>
-      <c r="F45" s="21">
+      <c r="F45" s="144">
         <v>45728</v>
       </c>
       <c r="G45" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="H45" s="28" t="s">
+      <c r="H45" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="I45" s="33" t="s">
+      <c r="I45" s="23" t="s">
         <v>147</v>
       </c>
-      <c r="J45" s="35" t="s">
+      <c r="J45" s="25" t="s">
         <v>149</v>
       </c>
-      <c r="K45" s="36" t="s">
+      <c r="K45" s="26" t="s">
         <v>150</v>
       </c>
-      <c r="L45" s="47" t="s">
+      <c r="L45" s="37" t="s">
         <v>194</v>
       </c>
       <c r="M45" t="s">
@@ -6152,7 +6157,7 @@
         <f t="shared" si="2"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0044-G.png</v>
       </c>
-      <c r="O45" s="136" t="str">
+      <c r="O45" s="110" t="str">
         <f t="shared" si="3"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0044-G.png</v>
       </c>
@@ -6168,31 +6173,31 @@
       <c r="C46" s="3" t="s">
         <v>723</v>
       </c>
-      <c r="D46" s="143">
+      <c r="D46" s="117">
         <v>38353</v>
       </c>
-      <c r="E46" s="19">
+      <c r="E46" s="132">
         <v>213091005037</v>
       </c>
-      <c r="F46" s="22">
+      <c r="F46" s="145">
         <v>44986</v>
       </c>
       <c r="G46" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="H46" s="29" t="s">
+      <c r="H46" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="I46" s="34" t="s">
+      <c r="I46" s="24" t="s">
         <v>148</v>
       </c>
-      <c r="J46" s="35" t="s">
+      <c r="J46" s="25" t="s">
         <v>149</v>
       </c>
-      <c r="K46" s="36" t="s">
+      <c r="K46" s="26" t="s">
         <v>150</v>
       </c>
-      <c r="L46" s="48" t="s">
+      <c r="L46" s="38" t="s">
         <v>195</v>
       </c>
       <c r="M46" t="s">
@@ -6202,7 +6207,7 @@
         <f t="shared" si="2"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0045-G.png</v>
       </c>
-      <c r="O46" s="136" t="str">
+      <c r="O46" s="110" t="str">
         <f t="shared" si="3"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0045-G.png</v>
       </c>
@@ -6223,28 +6228,28 @@
       <c r="D47" s="11">
         <v>37987</v>
       </c>
-      <c r="E47" s="71">
+      <c r="E47" s="134">
         <v>217011018800</v>
       </c>
-      <c r="F47" s="72">
+      <c r="F47" s="145">
         <v>44753</v>
       </c>
       <c r="G47" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="H47" s="57" t="s">
+      <c r="H47" s="47" t="s">
         <v>394</v>
       </c>
-      <c r="I47" s="94" t="s">
+      <c r="I47" s="70" t="s">
         <v>395</v>
       </c>
-      <c r="J47" s="128" t="s">
+      <c r="J47" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K47" s="29" t="s">
+      <c r="K47" s="19" t="s">
         <v>150</v>
       </c>
-      <c r="L47" s="106" t="s">
+      <c r="L47" s="82" t="s">
         <v>533</v>
       </c>
       <c r="M47" t="s">
@@ -6254,7 +6259,7 @@
         <f t="shared" si="2"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0001-SHS.png</v>
       </c>
-      <c r="O47" s="136" t="str">
+      <c r="O47" s="110" t="str">
         <f t="shared" si="3"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0001-SHS.png</v>
       </c>
@@ -6275,28 +6280,28 @@
       <c r="D48" s="11">
         <v>38482</v>
       </c>
-      <c r="E48" s="71">
+      <c r="E48" s="134">
         <v>214011119602</v>
       </c>
-      <c r="F48" s="72">
+      <c r="F48" s="145">
         <v>45686</v>
       </c>
       <c r="G48" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="H48" s="57" t="s">
+      <c r="H48" s="47" t="s">
         <v>87</v>
       </c>
-      <c r="I48" s="94" t="s">
+      <c r="I48" s="70" t="s">
         <v>396</v>
       </c>
-      <c r="J48" s="128" t="s">
+      <c r="J48" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K48" s="107" t="s">
+      <c r="K48" s="83" t="s">
         <v>150</v>
       </c>
-      <c r="L48" s="106" t="s">
+      <c r="L48" s="82" t="s">
         <v>534</v>
       </c>
       <c r="M48" t="s">
@@ -6306,7 +6311,7 @@
         <f t="shared" si="2"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0002-SHS.png</v>
       </c>
-      <c r="O48" s="136" t="str">
+      <c r="O48" s="110" t="str">
         <f t="shared" si="3"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0002-SHS.png</v>
       </c>
@@ -6327,28 +6332,28 @@
       <c r="D49" s="11">
         <v>38261</v>
       </c>
-      <c r="E49" s="71">
+      <c r="E49" s="134">
         <v>509012019360</v>
       </c>
-      <c r="F49" s="72">
+      <c r="F49" s="145">
         <v>44963</v>
       </c>
       <c r="G49" s="9" t="s">
         <v>896</v>
       </c>
-      <c r="H49" s="57" t="s">
+      <c r="H49" s="47" t="s">
         <v>103</v>
       </c>
-      <c r="I49" s="94" t="s">
+      <c r="I49" s="70" t="s">
         <v>397</v>
       </c>
-      <c r="J49" s="128" t="s">
+      <c r="J49" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K49" s="107" t="s">
+      <c r="K49" s="83" t="s">
         <v>150</v>
       </c>
-      <c r="L49" s="106" t="s">
+      <c r="L49" s="82" t="s">
         <v>535</v>
       </c>
       <c r="M49" t="s">
@@ -6358,7 +6363,7 @@
         <f t="shared" si="2"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0003-SHS.png</v>
       </c>
-      <c r="O49" s="136" t="str">
+      <c r="O49" s="110" t="str">
         <f t="shared" si="3"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0003-SHS.png</v>
       </c>
@@ -6370,7 +6375,7 @@
       <c r="A50" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="B50" s="142" t="s">
+      <c r="B50" s="116" t="s">
         <v>710</v>
       </c>
       <c r="C50" s="3" t="s">
@@ -6379,28 +6384,28 @@
       <c r="D50" s="11">
         <v>38658</v>
       </c>
-      <c r="E50" s="71">
+      <c r="E50" s="134">
         <v>213011041873</v>
       </c>
-      <c r="F50" s="150">
+      <c r="F50" s="146">
         <v>45301</v>
       </c>
       <c r="G50" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="H50" s="57" t="s">
+      <c r="H50" s="47" t="s">
         <v>394</v>
       </c>
-      <c r="I50" s="94" t="s">
+      <c r="I50" s="70" t="s">
         <v>398</v>
       </c>
-      <c r="J50" s="128" t="s">
+      <c r="J50" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K50" s="107" t="s">
+      <c r="K50" s="83" t="s">
         <v>150</v>
       </c>
-      <c r="L50" s="106" t="s">
+      <c r="L50" s="82" t="s">
         <v>536</v>
       </c>
       <c r="M50" t="s">
@@ -6410,7 +6415,7 @@
         <f t="shared" si="2"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0004-SHS.png</v>
       </c>
-      <c r="O50" s="136" t="str">
+      <c r="O50" s="110" t="str">
         <f t="shared" si="3"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0004-SHS.png</v>
       </c>
@@ -6431,28 +6436,28 @@
       <c r="D51" s="11">
         <v>39350</v>
       </c>
-      <c r="E51" s="71">
+      <c r="E51" s="134">
         <v>201031068071</v>
       </c>
-      <c r="F51" s="72">
+      <c r="F51" s="145">
         <v>45982</v>
       </c>
       <c r="G51" s="9" t="s">
         <v>391</v>
       </c>
-      <c r="H51" s="57" t="s">
+      <c r="H51" s="47" t="s">
         <v>87</v>
       </c>
-      <c r="I51" s="94" t="s">
+      <c r="I51" s="70" t="s">
         <v>399</v>
       </c>
-      <c r="J51" s="128" t="s">
+      <c r="J51" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K51" s="107" t="s">
+      <c r="K51" s="83" t="s">
         <v>150</v>
       </c>
-      <c r="L51" s="106" t="s">
+      <c r="L51" s="82" t="s">
         <v>537</v>
       </c>
       <c r="M51" t="s">
@@ -6462,7 +6467,7 @@
         <f t="shared" si="2"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0005-SHS.png</v>
       </c>
-      <c r="O51" s="136" t="str">
+      <c r="O51" s="110" t="str">
         <f t="shared" si="3"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0005-SHS.png</v>
       </c>
@@ -6481,28 +6486,28 @@
       <c r="D52" s="11">
         <v>38426</v>
       </c>
-      <c r="E52" s="71">
+      <c r="E52" s="134">
         <v>213271009192</v>
       </c>
-      <c r="F52" s="72">
+      <c r="F52" s="145">
         <v>45793</v>
       </c>
       <c r="G52" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="H52" s="57" t="s">
+      <c r="H52" s="47" t="s">
         <v>89</v>
       </c>
-      <c r="I52" s="94" t="s">
+      <c r="I52" s="70" t="s">
         <v>400</v>
       </c>
-      <c r="J52" s="128" t="s">
+      <c r="J52" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K52" s="107" t="s">
+      <c r="K52" s="83" t="s">
         <v>150</v>
       </c>
-      <c r="L52" s="106" t="s">
+      <c r="L52" s="82" t="s">
         <v>538</v>
       </c>
       <c r="M52" t="s">
@@ -6512,7 +6517,7 @@
         <f t="shared" si="2"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0006-SHS.png</v>
       </c>
-      <c r="O52" s="136" t="str">
+      <c r="O52" s="110" t="str">
         <f t="shared" si="3"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0006-SHS.png</v>
       </c>
@@ -6533,28 +6538,28 @@
       <c r="D53" s="11">
         <v>37022</v>
       </c>
-      <c r="E53" s="71">
+      <c r="E53" s="134">
         <v>213572008382</v>
       </c>
-      <c r="F53" s="72">
+      <c r="F53" s="145">
         <v>44630</v>
       </c>
       <c r="G53" s="9" t="s">
         <v>897</v>
       </c>
-      <c r="H53" s="57" t="s">
+      <c r="H53" s="47" t="s">
         <v>99</v>
       </c>
-      <c r="I53" s="94" t="s">
+      <c r="I53" s="70" t="s">
         <v>401</v>
       </c>
-      <c r="J53" s="128" t="s">
+      <c r="J53" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K53" s="107" t="s">
+      <c r="K53" s="83" t="s">
         <v>150</v>
       </c>
-      <c r="L53" s="106" t="s">
+      <c r="L53" s="82" t="s">
         <v>539</v>
       </c>
       <c r="M53" t="s">
@@ -6564,7 +6569,7 @@
         <f t="shared" si="2"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0007-SHS.png</v>
       </c>
-      <c r="O53" s="136" t="str">
+      <c r="O53" s="110" t="str">
         <f t="shared" si="3"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0007-SHS.png</v>
       </c>
@@ -6585,28 +6590,28 @@
       <c r="D54" s="11">
         <v>38179</v>
       </c>
-      <c r="E54" s="71">
+      <c r="E54" s="134">
         <v>213011043643</v>
       </c>
-      <c r="F54" s="72">
+      <c r="F54" s="145">
         <v>45693</v>
       </c>
       <c r="G54" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="H54" s="95" t="s">
+      <c r="H54" s="71" t="s">
         <v>102</v>
       </c>
-      <c r="I54" s="94" t="s">
+      <c r="I54" s="70" t="s">
         <v>402</v>
       </c>
-      <c r="J54" s="128" t="s">
+      <c r="J54" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K54" s="107" t="s">
+      <c r="K54" s="83" t="s">
         <v>150</v>
       </c>
-      <c r="L54" s="108" t="s">
+      <c r="L54" s="84" t="s">
         <v>540</v>
       </c>
       <c r="M54" t="s">
@@ -6616,7 +6621,7 @@
         <f t="shared" si="2"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0008-SHS.png</v>
       </c>
-      <c r="O54" s="136" t="str">
+      <c r="O54" s="110" t="str">
         <f t="shared" si="3"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0008-SHS.png</v>
       </c>
@@ -6632,31 +6637,31 @@
       <c r="C55" s="3" t="s">
         <v>876</v>
       </c>
-      <c r="D55" s="151">
+      <c r="D55" s="121">
         <v>39448</v>
       </c>
-      <c r="E55" s="71">
+      <c r="E55" s="134">
         <v>213011045119</v>
       </c>
-      <c r="F55" s="72">
+      <c r="F55" s="145">
         <v>46034</v>
       </c>
       <c r="G55" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="H55" s="57" t="s">
+      <c r="H55" s="47" t="s">
         <v>102</v>
       </c>
-      <c r="I55" s="94" t="s">
+      <c r="I55" s="70" t="s">
         <v>403</v>
       </c>
-      <c r="J55" s="128" t="s">
+      <c r="J55" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K55" s="107" t="s">
+      <c r="K55" s="83" t="s">
         <v>150</v>
       </c>
-      <c r="L55" s="108" t="s">
+      <c r="L55" s="84" t="s">
         <v>541</v>
       </c>
       <c r="M55" t="s">
@@ -6666,7 +6671,7 @@
         <f t="shared" si="2"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0009-SHS.png</v>
       </c>
-      <c r="O55" s="136" t="str">
+      <c r="O55" s="110" t="str">
         <f t="shared" si="3"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0009-SHS.png</v>
       </c>
@@ -6684,31 +6689,31 @@
       <c r="C56" s="3" t="s">
         <v>875</v>
       </c>
-      <c r="D56" s="151">
+      <c r="D56" s="121">
         <v>38353</v>
       </c>
-      <c r="E56" s="71">
+      <c r="E56" s="134">
         <v>213012042077</v>
       </c>
-      <c r="F56" s="72">
+      <c r="F56" s="145">
         <v>45343</v>
       </c>
       <c r="G56" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="H56" s="57" t="s">
+      <c r="H56" s="47" t="s">
         <v>95</v>
       </c>
-      <c r="I56" s="94" t="s">
+      <c r="I56" s="70" t="s">
         <v>404</v>
       </c>
-      <c r="J56" s="128" t="s">
+      <c r="J56" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K56" s="107" t="s">
+      <c r="K56" s="83" t="s">
         <v>150</v>
       </c>
-      <c r="L56" s="106" t="s">
+      <c r="L56" s="82" t="s">
         <v>542</v>
       </c>
       <c r="M56" t="s">
@@ -6718,7 +6723,7 @@
         <f t="shared" si="2"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0010-SHS.png</v>
       </c>
-      <c r="O56" s="136" t="str">
+      <c r="O56" s="110" t="str">
         <f t="shared" si="3"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0010-SHS.png</v>
       </c>
@@ -6739,28 +6744,28 @@
       <c r="D57" s="11">
         <v>37763</v>
       </c>
-      <c r="E57" s="71">
+      <c r="E57" s="134">
         <v>213111004475</v>
       </c>
-      <c r="F57" s="72">
+      <c r="F57" s="145">
         <v>44678</v>
       </c>
       <c r="G57" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="H57" s="57" t="s">
+      <c r="H57" s="47" t="s">
         <v>92</v>
       </c>
-      <c r="I57" s="94" t="s">
+      <c r="I57" s="70" t="s">
         <v>531</v>
       </c>
-      <c r="J57" s="128" t="s">
+      <c r="J57" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K57" s="107" t="s">
+      <c r="K57" s="83" t="s">
         <v>150</v>
       </c>
-      <c r="L57" s="106" t="s">
+      <c r="L57" s="82" t="s">
         <v>543</v>
       </c>
       <c r="M57" t="s">
@@ -6770,7 +6775,7 @@
         <f t="shared" si="2"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0011-SHS.png</v>
       </c>
-      <c r="O57" s="136" t="str">
+      <c r="O57" s="110" t="str">
         <f t="shared" si="3"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0011-SHS.png</v>
       </c>
@@ -6791,28 +6796,28 @@
       <c r="D58" s="11">
         <v>39002</v>
       </c>
-      <c r="E58" s="71">
+      <c r="E58" s="134">
         <v>213012044106</v>
       </c>
-      <c r="F58" s="72">
+      <c r="F58" s="145">
         <v>45782</v>
       </c>
       <c r="G58" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="H58" s="57" t="s">
+      <c r="H58" s="47" t="s">
         <v>98</v>
       </c>
-      <c r="I58" s="94" t="s">
+      <c r="I58" s="70" t="s">
         <v>405</v>
       </c>
-      <c r="J58" s="128" t="s">
+      <c r="J58" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K58" s="107" t="s">
+      <c r="K58" s="83" t="s">
         <v>150</v>
       </c>
-      <c r="L58" s="106" t="s">
+      <c r="L58" s="82" t="s">
         <v>544</v>
       </c>
       <c r="M58" t="s">
@@ -6822,7 +6827,7 @@
         <f t="shared" si="2"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0012-SHS.png</v>
       </c>
-      <c r="O58" s="136" t="str">
+      <c r="O58" s="110" t="str">
         <f t="shared" si="3"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0012-SHS.png</v>
       </c>
@@ -6843,28 +6848,28 @@
       <c r="D59" s="11">
         <v>38886</v>
       </c>
-      <c r="E59" s="71">
+      <c r="E59" s="134">
         <v>215302022662</v>
       </c>
-      <c r="F59" s="72">
+      <c r="F59" s="145">
         <v>45684</v>
       </c>
       <c r="G59" s="9" t="s">
         <v>898</v>
       </c>
-      <c r="H59" s="57" t="s">
+      <c r="H59" s="47" t="s">
         <v>87</v>
       </c>
-      <c r="I59" s="94" t="s">
+      <c r="I59" s="70" t="s">
         <v>406</v>
       </c>
-      <c r="J59" s="128" t="s">
+      <c r="J59" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K59" s="107" t="s">
+      <c r="K59" s="83" t="s">
         <v>150</v>
       </c>
-      <c r="L59" s="106" t="s">
+      <c r="L59" s="82" t="s">
         <v>545</v>
       </c>
       <c r="M59" t="s">
@@ -6874,7 +6879,7 @@
         <f t="shared" si="2"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0013-SHS.png</v>
       </c>
-      <c r="O59" s="136" t="str">
+      <c r="O59" s="110" t="str">
         <f t="shared" si="3"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0013-SHS.png</v>
       </c>
@@ -6895,10 +6900,10 @@
       <c r="D60" s="13">
         <v>38576</v>
       </c>
-      <c r="E60" s="73">
+      <c r="E60" s="135">
         <v>213171007839</v>
       </c>
-      <c r="F60" s="150">
+      <c r="F60" s="146">
         <v>44890</v>
       </c>
       <c r="G60" s="9" t="s">
@@ -6907,16 +6912,16 @@
       <c r="H60" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="I60" s="96" t="s">
+      <c r="I60" s="72" t="s">
         <v>407</v>
       </c>
-      <c r="J60" s="128" t="s">
+      <c r="J60" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K60" s="107" t="s">
+      <c r="K60" s="83" t="s">
         <v>150</v>
       </c>
-      <c r="L60" s="109" t="s">
+      <c r="L60" s="85" t="s">
         <v>546</v>
       </c>
       <c r="M60" t="s">
@@ -6926,7 +6931,7 @@
         <f t="shared" si="2"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0014-SHS.png</v>
       </c>
-      <c r="O60" s="136" t="str">
+      <c r="O60" s="110" t="str">
         <f t="shared" si="3"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0014-SHS.png</v>
       </c>
@@ -6942,13 +6947,13 @@
       <c r="C61" s="3" t="s">
         <v>870</v>
       </c>
-      <c r="D61" s="143">
+      <c r="D61" s="117">
         <v>37622</v>
       </c>
-      <c r="E61" s="73">
+      <c r="E61" s="135">
         <v>213012040593</v>
       </c>
-      <c r="F61" s="72">
+      <c r="F61" s="145">
         <v>44988</v>
       </c>
       <c r="G61" s="9" t="s">
@@ -6957,16 +6962,16 @@
       <c r="H61" s="14" t="s">
         <v>408</v>
       </c>
-      <c r="I61" s="96" t="s">
+      <c r="I61" s="72" t="s">
         <v>409</v>
       </c>
-      <c r="J61" s="128" t="s">
+      <c r="J61" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K61" s="107" t="s">
+      <c r="K61" s="83" t="s">
         <v>150</v>
       </c>
-      <c r="L61" s="109" t="s">
+      <c r="L61" s="85" t="s">
         <v>547</v>
       </c>
       <c r="M61" t="s">
@@ -6976,7 +6981,7 @@
         <f t="shared" si="2"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0015-SHS.png</v>
       </c>
-      <c r="O61" s="136" t="str">
+      <c r="O61" s="110" t="str">
         <f t="shared" si="3"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0015-SHS.png</v>
       </c>
@@ -6985,7 +6990,7 @@
       </c>
     </row>
     <row r="62" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A62" s="49" t="s">
+      <c r="A62" s="39" t="s">
         <v>222</v>
       </c>
       <c r="B62" s="9"/>
@@ -6995,10 +7000,10 @@
       <c r="D62" s="13">
         <v>38983</v>
       </c>
-      <c r="E62" s="73">
+      <c r="E62" s="135">
         <v>213012043414</v>
       </c>
-      <c r="F62" s="150">
+      <c r="F62" s="146">
         <v>45649</v>
       </c>
       <c r="G62" s="9" t="s">
@@ -7007,16 +7012,16 @@
       <c r="H62" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="I62" s="96" t="s">
+      <c r="I62" s="72" t="s">
         <v>410</v>
       </c>
-      <c r="J62" s="128" t="s">
+      <c r="J62" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K62" s="107" t="s">
+      <c r="K62" s="83" t="s">
         <v>150</v>
       </c>
-      <c r="L62" s="109" t="s">
+      <c r="L62" s="85" t="s">
         <v>548</v>
       </c>
       <c r="M62" t="s">
@@ -7026,7 +7031,7 @@
         <f t="shared" si="2"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0016-SHS.png</v>
       </c>
-      <c r="O62" s="136" t="str">
+      <c r="O62" s="110" t="str">
         <f t="shared" si="3"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0016-SHS.png</v>
       </c>
@@ -7035,7 +7040,7 @@
       </c>
     </row>
     <row r="63" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A63" s="49" t="s">
+      <c r="A63" s="39" t="s">
         <v>223</v>
       </c>
       <c r="B63" s="9" t="s">
@@ -7044,31 +7049,31 @@
       <c r="C63" s="3" t="s">
         <v>868</v>
       </c>
-      <c r="D63" s="152">
+      <c r="D63" s="122">
         <v>37257</v>
       </c>
-      <c r="E63" s="73">
+      <c r="E63" s="135">
         <v>213152003987</v>
       </c>
-      <c r="F63" s="74">
+      <c r="F63" s="150">
         <v>45509</v>
       </c>
-      <c r="G63" s="75" t="s">
+      <c r="G63" s="62" t="s">
         <v>82</v>
       </c>
-      <c r="H63" s="58" t="s">
+      <c r="H63" s="48" t="s">
         <v>87</v>
       </c>
-      <c r="I63" s="96" t="s">
+      <c r="I63" s="72" t="s">
         <v>411</v>
       </c>
-      <c r="J63" s="128" t="s">
+      <c r="J63" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K63" s="107" t="s">
+      <c r="K63" s="83" t="s">
         <v>150</v>
       </c>
-      <c r="L63" s="109" t="s">
+      <c r="L63" s="85" t="s">
         <v>549</v>
       </c>
       <c r="M63" t="s">
@@ -7078,7 +7083,7 @@
         <f t="shared" si="2"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0017-SHS.png</v>
       </c>
-      <c r="O63" s="136" t="str">
+      <c r="O63" s="110" t="str">
         <f t="shared" si="3"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0017-SHS.png</v>
       </c>
@@ -7087,7 +7092,7 @@
       </c>
     </row>
     <row r="64" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A64" s="49" t="s">
+      <c r="A64" s="39" t="s">
         <v>225</v>
       </c>
       <c r="B64" s="9"/>
@@ -7097,10 +7102,10 @@
       <c r="D64" s="13">
         <v>36526</v>
       </c>
-      <c r="E64" s="73">
+      <c r="E64" s="135">
         <v>214032100280</v>
       </c>
-      <c r="F64" s="72">
+      <c r="F64" s="145">
         <v>43544</v>
       </c>
       <c r="G64" s="9" t="s">
@@ -7109,16 +7114,16 @@
       <c r="H64" s="14" t="s">
         <v>412</v>
       </c>
-      <c r="I64" s="96" t="s">
+      <c r="I64" s="72" t="s">
         <v>413</v>
       </c>
-      <c r="J64" s="128" t="s">
+      <c r="J64" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K64" s="107" t="s">
+      <c r="K64" s="83" t="s">
         <v>150</v>
       </c>
-      <c r="L64" s="109" t="s">
+      <c r="L64" s="85" t="s">
         <v>550</v>
       </c>
       <c r="M64" t="s">
@@ -7128,7 +7133,7 @@
         <f t="shared" si="2"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0018-SHS.png</v>
       </c>
-      <c r="O64" s="136" t="str">
+      <c r="O64" s="110" t="str">
         <f t="shared" si="3"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0018-SHS.png</v>
       </c>
@@ -7137,7 +7142,7 @@
       </c>
     </row>
     <row r="65" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A65" s="49" t="s">
+      <c r="A65" s="39" t="s">
         <v>226</v>
       </c>
       <c r="B65" s="9" t="s">
@@ -7146,31 +7151,31 @@
       <c r="C65" s="3" t="s">
         <v>866</v>
       </c>
-      <c r="D65" s="59">
+      <c r="D65" s="49">
         <v>38347</v>
       </c>
-      <c r="E65" s="73">
+      <c r="E65" s="135">
         <v>215302022096</v>
       </c>
-      <c r="F65" s="74">
+      <c r="F65" s="150">
         <v>45322</v>
       </c>
-      <c r="G65" s="75" t="s">
+      <c r="G65" s="62" t="s">
         <v>898</v>
       </c>
-      <c r="H65" s="58" t="s">
+      <c r="H65" s="48" t="s">
         <v>102</v>
       </c>
-      <c r="I65" s="96" t="s">
+      <c r="I65" s="72" t="s">
         <v>414</v>
       </c>
-      <c r="J65" s="128" t="s">
+      <c r="J65" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K65" s="107" t="s">
+      <c r="K65" s="83" t="s">
         <v>150</v>
       </c>
-      <c r="L65" s="109" t="s">
+      <c r="L65" s="85" t="s">
         <v>551</v>
       </c>
       <c r="M65" t="s">
@@ -7180,7 +7185,7 @@
         <f t="shared" si="2"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0019-SHS.png</v>
       </c>
-      <c r="O65" s="136" t="str">
+      <c r="O65" s="110" t="str">
         <f t="shared" si="3"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0019-SHS.png</v>
       </c>
@@ -7201,10 +7206,10 @@
       <c r="D66" s="13">
         <v>35995</v>
       </c>
-      <c r="E66" s="73">
+      <c r="E66" s="135">
         <v>217012011964</v>
       </c>
-      <c r="F66" s="72">
+      <c r="F66" s="145">
         <v>42794</v>
       </c>
       <c r="G66" s="9" t="s">
@@ -7213,16 +7218,16 @@
       <c r="H66" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="I66" s="96" t="s">
+      <c r="I66" s="72" t="s">
         <v>415</v>
       </c>
-      <c r="J66" s="128" t="s">
+      <c r="J66" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K66" s="107" t="s">
+      <c r="K66" s="83" t="s">
         <v>150</v>
       </c>
-      <c r="L66" s="48" t="s">
+      <c r="L66" s="38" t="s">
         <v>552</v>
       </c>
       <c r="M66" t="s">
@@ -7232,7 +7237,7 @@
         <f t="shared" ref="N66:N97" si="4">"https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/" &amp; C66 &amp; ".png"</f>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0020-SHS.png</v>
       </c>
-      <c r="O66" s="136" t="str">
+      <c r="O66" s="110" t="str">
         <f t="shared" ref="O66:O97" si="5">"https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/" &amp; C66 &amp; ".png"</f>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0020-SHS.png</v>
       </c>
@@ -7251,10 +7256,10 @@
       <c r="D67" s="13">
         <v>38614</v>
       </c>
-      <c r="E67" s="73">
+      <c r="E67" s="135">
         <v>213011043526</v>
       </c>
-      <c r="F67" s="72">
+      <c r="F67" s="145">
         <v>45672</v>
       </c>
       <c r="G67" s="9" t="s">
@@ -7263,16 +7268,16 @@
       <c r="H67" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="I67" s="96" t="s">
+      <c r="I67" s="72" t="s">
         <v>416</v>
       </c>
-      <c r="J67" s="128" t="s">
+      <c r="J67" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K67" s="107" t="s">
+      <c r="K67" s="83" t="s">
         <v>150</v>
       </c>
-      <c r="L67" s="109" t="s">
+      <c r="L67" s="85" t="s">
         <v>553</v>
       </c>
       <c r="M67" t="s">
@@ -7282,7 +7287,7 @@
         <f t="shared" si="4"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0021-SHS.png</v>
       </c>
-      <c r="O67" s="136" t="str">
+      <c r="O67" s="110" t="str">
         <f t="shared" si="5"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0021-SHS.png</v>
       </c>
@@ -7294,7 +7299,7 @@
       <c r="A68" s="8" t="s">
         <v>231</v>
       </c>
-      <c r="B68" s="140" t="s">
+      <c r="B68" s="114" t="s">
         <v>711</v>
       </c>
       <c r="C68" s="3" t="s">
@@ -7303,28 +7308,28 @@
       <c r="D68" s="13">
         <v>38235</v>
       </c>
-      <c r="E68" s="73">
+      <c r="E68" s="135">
         <v>213612002210</v>
       </c>
-      <c r="F68" s="72">
+      <c r="F68" s="145">
         <v>45062</v>
       </c>
       <c r="G68" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="H68" s="58" t="s">
+      <c r="H68" s="48" t="s">
         <v>417</v>
       </c>
-      <c r="I68" s="96" t="s">
+      <c r="I68" s="72" t="s">
         <v>418</v>
       </c>
-      <c r="J68" s="128" t="s">
+      <c r="J68" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K68" s="107" t="s">
+      <c r="K68" s="83" t="s">
         <v>150</v>
       </c>
-      <c r="L68" s="109" t="s">
+      <c r="L68" s="85" t="s">
         <v>554</v>
       </c>
       <c r="M68" t="s">
@@ -7334,7 +7339,7 @@
         <f t="shared" si="4"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0022-SHS.png</v>
       </c>
-      <c r="O68" s="136" t="str">
+      <c r="O68" s="110" t="str">
         <f t="shared" si="5"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0022-SHS.png</v>
       </c>
@@ -7355,10 +7360,10 @@
       <c r="D69" s="13">
         <v>38916</v>
       </c>
-      <c r="E69" s="73">
+      <c r="E69" s="135">
         <v>213012043407</v>
       </c>
-      <c r="F69" s="72">
+      <c r="F69" s="145">
         <v>45649</v>
       </c>
       <c r="G69" s="9" t="s">
@@ -7367,16 +7372,16 @@
       <c r="H69" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="I69" s="96" t="s">
+      <c r="I69" s="72" t="s">
         <v>419</v>
       </c>
-      <c r="J69" s="128" t="s">
+      <c r="J69" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K69" s="107" t="s">
+      <c r="K69" s="83" t="s">
         <v>150</v>
       </c>
-      <c r="L69" s="109" t="s">
+      <c r="L69" s="85" t="s">
         <v>555</v>
       </c>
       <c r="M69" t="s">
@@ -7386,7 +7391,7 @@
         <f t="shared" si="4"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0023-SHS.png</v>
       </c>
-      <c r="O69" s="136" t="str">
+      <c r="O69" s="110" t="str">
         <f t="shared" si="5"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0023-SHS.png</v>
       </c>
@@ -7404,13 +7409,13 @@
       <c r="C70" s="3" t="s">
         <v>861</v>
       </c>
-      <c r="D70" s="143">
+      <c r="D70" s="117">
         <v>37622</v>
       </c>
-      <c r="E70" s="73">
+      <c r="E70" s="135">
         <v>213011038011</v>
       </c>
-      <c r="F70" s="72">
+      <c r="F70" s="145">
         <v>44673</v>
       </c>
       <c r="G70" s="9" t="s">
@@ -7419,16 +7424,16 @@
       <c r="H70" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="I70" s="96" t="s">
+      <c r="I70" s="72" t="s">
         <v>420</v>
       </c>
-      <c r="J70" s="128" t="s">
+      <c r="J70" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K70" s="107" t="s">
+      <c r="K70" s="83" t="s">
         <v>150</v>
       </c>
-      <c r="L70" s="109" t="s">
+      <c r="L70" s="85" t="s">
         <v>556</v>
       </c>
       <c r="M70" t="s">
@@ -7438,7 +7443,7 @@
         <f t="shared" si="4"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0024-SHS.png</v>
       </c>
-      <c r="O70" s="136" t="str">
+      <c r="O70" s="110" t="str">
         <f t="shared" si="5"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0024-SHS.png</v>
       </c>
@@ -7456,13 +7461,13 @@
       <c r="C71" s="3" t="s">
         <v>860</v>
       </c>
-      <c r="D71" s="143">
+      <c r="D71" s="117">
         <v>38773</v>
       </c>
-      <c r="E71" s="73">
+      <c r="E71" s="135">
         <v>213012043890</v>
       </c>
-      <c r="F71" s="72">
+      <c r="F71" s="145">
         <v>45734</v>
       </c>
       <c r="G71" s="9" t="s">
@@ -7471,16 +7476,16 @@
       <c r="H71" s="14" t="s">
         <v>421</v>
       </c>
-      <c r="I71" s="96" t="s">
+      <c r="I71" s="72" t="s">
         <v>422</v>
       </c>
-      <c r="J71" s="128" t="s">
+      <c r="J71" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K71" s="107" t="s">
+      <c r="K71" s="83" t="s">
         <v>150</v>
       </c>
-      <c r="L71" s="110" t="s">
+      <c r="L71" s="86" t="s">
         <v>557</v>
       </c>
       <c r="M71" t="s">
@@ -7490,7 +7495,7 @@
         <f t="shared" si="4"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0025-SHS.png</v>
       </c>
-      <c r="O71" s="136" t="str">
+      <c r="O71" s="110" t="str">
         <f t="shared" si="5"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0025-SHS.png</v>
       </c>
@@ -7511,10 +7516,10 @@
       <c r="D72" s="13">
         <v>37707</v>
       </c>
-      <c r="E72" s="73">
+      <c r="E72" s="135">
         <v>213151003626</v>
       </c>
-      <c r="F72" s="72">
+      <c r="F72" s="145">
         <v>45126</v>
       </c>
       <c r="G72" s="9" t="s">
@@ -7523,16 +7528,16 @@
       <c r="H72" s="14" t="s">
         <v>423</v>
       </c>
-      <c r="I72" s="96" t="s">
+      <c r="I72" s="72" t="s">
         <v>424</v>
       </c>
-      <c r="J72" s="128" t="s">
+      <c r="J72" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K72" s="107" t="s">
+      <c r="K72" s="83" t="s">
         <v>150</v>
       </c>
-      <c r="L72" s="109"/>
+      <c r="L72" s="85"/>
       <c r="M72" t="s">
         <v>693</v>
       </c>
@@ -7540,7 +7545,7 @@
         <f t="shared" si="4"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0026-SHS.png</v>
       </c>
-      <c r="O72" s="136" t="str">
+      <c r="O72" s="110" t="str">
         <f t="shared" si="5"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0026-SHS.png</v>
       </c>
@@ -7558,13 +7563,13 @@
       <c r="C73" s="3" t="s">
         <v>858</v>
       </c>
-      <c r="D73" s="143">
+      <c r="D73" s="117">
         <v>37622</v>
       </c>
-      <c r="E73" s="71">
+      <c r="E73" s="134">
         <v>213331006786</v>
       </c>
-      <c r="F73" s="72">
+      <c r="F73" s="145">
         <v>45320</v>
       </c>
       <c r="G73" s="9" t="s">
@@ -7573,16 +7578,16 @@
       <c r="H73" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="I73" s="96" t="s">
+      <c r="I73" s="72" t="s">
         <v>425</v>
       </c>
-      <c r="J73" s="128" t="s">
+      <c r="J73" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K73" s="107" t="s">
+      <c r="K73" s="83" t="s">
         <v>150</v>
       </c>
-      <c r="L73" s="109" t="s">
+      <c r="L73" s="85" t="s">
         <v>558</v>
       </c>
       <c r="M73" t="s">
@@ -7592,7 +7597,7 @@
         <f t="shared" si="4"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0027-SHS.png</v>
       </c>
-      <c r="O73" s="136" t="str">
+      <c r="O73" s="110" t="str">
         <f t="shared" si="5"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0027-SHS.png</v>
       </c>
@@ -7613,10 +7618,10 @@
       <c r="D74" s="13">
         <v>38403</v>
       </c>
-      <c r="E74" s="73">
+      <c r="E74" s="135">
         <v>213011041613</v>
       </c>
-      <c r="F74" s="72">
+      <c r="F74" s="145">
         <v>45224</v>
       </c>
       <c r="G74" s="9" t="s">
@@ -7625,16 +7630,16 @@
       <c r="H74" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="I74" s="96" t="s">
+      <c r="I74" s="72" t="s">
         <v>426</v>
       </c>
-      <c r="J74" s="128" t="s">
+      <c r="J74" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K74" s="107" t="s">
+      <c r="K74" s="83" t="s">
         <v>150</v>
       </c>
-      <c r="L74" s="109" t="s">
+      <c r="L74" s="85" t="s">
         <v>559</v>
       </c>
       <c r="M74" t="s">
@@ -7644,7 +7649,7 @@
         <f t="shared" si="4"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0028-SHS.png</v>
       </c>
-      <c r="O74" s="136" t="str">
+      <c r="O74" s="110" t="str">
         <f t="shared" si="5"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0028-SHS.png</v>
       </c>
@@ -7665,10 +7670,10 @@
       <c r="D75" s="13">
         <v>38042</v>
       </c>
-      <c r="E75" s="73">
+      <c r="E75" s="135">
         <v>213571008897</v>
       </c>
-      <c r="F75" s="72">
+      <c r="F75" s="145">
         <v>44861</v>
       </c>
       <c r="G75" s="9" t="s">
@@ -7677,16 +7682,16 @@
       <c r="H75" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="I75" s="96" t="s">
+      <c r="I75" s="72" t="s">
         <v>427</v>
       </c>
-      <c r="J75" s="128" t="s">
+      <c r="J75" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K75" s="107" t="s">
+      <c r="K75" s="83" t="s">
         <v>150</v>
       </c>
-      <c r="L75" s="109" t="s">
+      <c r="L75" s="85" t="s">
         <v>560</v>
       </c>
       <c r="M75" t="s">
@@ -7696,7 +7701,7 @@
         <f t="shared" si="4"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0029-SHS.png</v>
       </c>
-      <c r="O75" s="136" t="str">
+      <c r="O75" s="110" t="str">
         <f t="shared" si="5"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0029-SHS.png</v>
       </c>
@@ -7714,31 +7719,31 @@
       <c r="C76" s="3" t="s">
         <v>855</v>
       </c>
-      <c r="D76" s="59">
+      <c r="D76" s="49">
         <v>38678</v>
       </c>
-      <c r="E76" s="71">
+      <c r="E76" s="134">
         <v>214012120631</v>
       </c>
-      <c r="F76" s="155">
+      <c r="F76" s="151">
         <v>46013</v>
       </c>
-      <c r="G76" s="75" t="s">
+      <c r="G76" s="62" t="s">
         <v>83</v>
       </c>
-      <c r="H76" s="58" t="s">
+      <c r="H76" s="48" t="s">
         <v>87</v>
       </c>
-      <c r="I76" s="96" t="s">
+      <c r="I76" s="72" t="s">
         <v>428</v>
       </c>
-      <c r="J76" s="128" t="s">
+      <c r="J76" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K76" s="107" t="s">
+      <c r="K76" s="83" t="s">
         <v>150</v>
       </c>
-      <c r="L76" s="78" t="s">
+      <c r="L76" s="65" t="s">
         <v>561</v>
       </c>
       <c r="M76" t="s">
@@ -7748,7 +7753,7 @@
         <f t="shared" si="4"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0030-SHS.png</v>
       </c>
-      <c r="O76" s="136" t="str">
+      <c r="O76" s="110" t="str">
         <f t="shared" si="5"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0030-SHS.png</v>
       </c>
@@ -7769,8 +7774,8 @@
       <c r="D77" s="13">
         <v>38873</v>
       </c>
-      <c r="E77" s="73"/>
-      <c r="F77" s="72">
+      <c r="E77" s="135"/>
+      <c r="F77" s="145">
         <v>45813</v>
       </c>
       <c r="G77" s="9" t="s">
@@ -7779,16 +7784,16 @@
       <c r="H77" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="I77" s="96" t="s">
+      <c r="I77" s="72" t="s">
         <v>429</v>
       </c>
-      <c r="J77" s="128" t="s">
+      <c r="J77" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K77" s="107" t="s">
+      <c r="K77" s="83" t="s">
         <v>150</v>
       </c>
-      <c r="L77" s="109" t="s">
+      <c r="L77" s="85" t="s">
         <v>562</v>
       </c>
       <c r="M77" t="s">
@@ -7798,7 +7803,7 @@
         <f t="shared" si="4"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0031-SHS.png</v>
       </c>
-      <c r="O77" s="136" t="str">
+      <c r="O77" s="110" t="str">
         <f t="shared" si="5"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0031-SHS.png</v>
       </c>
@@ -7819,10 +7824,10 @@
       <c r="D78" s="13">
         <v>39223</v>
       </c>
-      <c r="E78" s="73">
+      <c r="E78" s="135">
         <v>214012120506</v>
       </c>
-      <c r="F78" s="72">
+      <c r="F78" s="145">
         <v>45954</v>
       </c>
       <c r="G78" s="9" t="s">
@@ -7831,16 +7836,16 @@
       <c r="H78" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="I78" s="96" t="s">
+      <c r="I78" s="72" t="s">
         <v>430</v>
       </c>
-      <c r="J78" s="128" t="s">
+      <c r="J78" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K78" s="107" t="s">
+      <c r="K78" s="83" t="s">
         <v>150</v>
       </c>
-      <c r="L78" s="109" t="s">
+      <c r="L78" s="85" t="s">
         <v>563</v>
       </c>
       <c r="M78" t="s">
@@ -7850,7 +7855,7 @@
         <f t="shared" si="4"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0032-SHS.png</v>
       </c>
-      <c r="O78" s="136" t="str">
+      <c r="O78" s="110" t="str">
         <f t="shared" si="5"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0032-SHS.png</v>
       </c>
@@ -7871,10 +7876,10 @@
       <c r="D79" s="13">
         <v>37659</v>
       </c>
-      <c r="E79" s="73">
+      <c r="E79" s="135">
         <v>213551008923</v>
       </c>
-      <c r="F79" s="72">
+      <c r="F79" s="145">
         <v>44951</v>
       </c>
       <c r="G79" s="9" t="s">
@@ -7883,16 +7888,16 @@
       <c r="H79" s="14" t="s">
         <v>431</v>
       </c>
-      <c r="I79" s="96" t="s">
+      <c r="I79" s="72" t="s">
         <v>432</v>
       </c>
-      <c r="J79" s="128" t="s">
+      <c r="J79" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K79" s="107" t="s">
+      <c r="K79" s="83" t="s">
         <v>150</v>
       </c>
-      <c r="L79" s="109" t="s">
+      <c r="L79" s="85" t="s">
         <v>564</v>
       </c>
       <c r="M79" t="s">
@@ -7902,7 +7907,7 @@
         <f t="shared" si="4"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0033-SHS.png</v>
       </c>
-      <c r="O79" s="136" t="str">
+      <c r="O79" s="110" t="str">
         <f t="shared" si="5"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0033-SHS.png</v>
       </c>
@@ -7914,19 +7919,19 @@
       <c r="A80" s="8" t="s">
         <v>253</v>
       </c>
-      <c r="B80" s="140" t="s">
+      <c r="B80" s="114" t="s">
         <v>712</v>
       </c>
       <c r="C80" s="3" t="s">
         <v>851</v>
       </c>
-      <c r="D80" s="143">
+      <c r="D80" s="117">
         <v>38377</v>
       </c>
-      <c r="E80" s="73">
+      <c r="E80" s="135">
         <v>217011024301</v>
       </c>
-      <c r="F80" s="72">
+      <c r="F80" s="145">
         <v>45805</v>
       </c>
       <c r="G80" s="9" t="s">
@@ -7935,16 +7940,16 @@
       <c r="H80" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="I80" s="96" t="s">
+      <c r="I80" s="72" t="s">
         <v>433</v>
       </c>
-      <c r="J80" s="128" t="s">
+      <c r="J80" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K80" s="107" t="s">
+      <c r="K80" s="83" t="s">
         <v>150</v>
       </c>
-      <c r="L80" s="109" t="s">
+      <c r="L80" s="85" t="s">
         <v>565</v>
       </c>
       <c r="M80" t="s">
@@ -7954,7 +7959,7 @@
         <f t="shared" si="4"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0034-SHS.png</v>
       </c>
-      <c r="O80" s="136" t="str">
+      <c r="O80" s="110" t="str">
         <f t="shared" si="5"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0034-SHS.png</v>
       </c>
@@ -7972,13 +7977,13 @@
       <c r="C81" s="3" t="s">
         <v>850</v>
       </c>
-      <c r="D81" s="143">
+      <c r="D81" s="117">
         <v>37987</v>
       </c>
-      <c r="E81" s="73">
+      <c r="E81" s="135">
         <v>213011041392</v>
       </c>
-      <c r="F81" s="72">
+      <c r="F81" s="145">
         <v>45180</v>
       </c>
       <c r="G81" s="9" t="s">
@@ -7987,16 +7992,16 @@
       <c r="H81" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="I81" s="96" t="s">
+      <c r="I81" s="72" t="s">
         <v>434</v>
       </c>
-      <c r="J81" s="128" t="s">
+      <c r="J81" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K81" s="107" t="s">
+      <c r="K81" s="83" t="s">
         <v>150</v>
       </c>
-      <c r="L81" s="109" t="s">
+      <c r="L81" s="85" t="s">
         <v>566</v>
       </c>
       <c r="M81" t="s">
@@ -8006,7 +8011,7 @@
         <f t="shared" si="4"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0035-SHS.png</v>
       </c>
-      <c r="O81" s="136" t="str">
+      <c r="O81" s="110" t="str">
         <f t="shared" si="5"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0035-SHS.png</v>
       </c>
@@ -8024,31 +8029,31 @@
       <c r="C82" s="3" t="s">
         <v>849</v>
       </c>
-      <c r="D82" s="59">
+      <c r="D82" s="49">
         <v>39627</v>
       </c>
-      <c r="E82" s="73">
+      <c r="E82" s="135">
         <v>196</v>
       </c>
-      <c r="F82" s="76">
+      <c r="F82" s="152">
         <v>39627</v>
       </c>
-      <c r="G82" s="77" t="s">
+      <c r="G82" s="64" t="s">
         <v>82</v>
       </c>
-      <c r="H82" s="58" t="s">
+      <c r="H82" s="48" t="s">
         <v>435</v>
       </c>
-      <c r="I82" s="96" t="s">
+      <c r="I82" s="72" t="s">
         <v>436</v>
       </c>
-      <c r="J82" s="128" t="s">
+      <c r="J82" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K82" s="107" t="s">
+      <c r="K82" s="83" t="s">
         <v>150</v>
       </c>
-      <c r="L82" s="110" t="s">
+      <c r="L82" s="86" t="s">
         <v>567</v>
       </c>
       <c r="M82" t="s">
@@ -8058,7 +8063,7 @@
         <f t="shared" si="4"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0036-SHS.png</v>
       </c>
-      <c r="O82" s="136" t="str">
+      <c r="O82" s="110" t="str">
         <f t="shared" si="5"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0036-SHS.png</v>
       </c>
@@ -8079,10 +8084,10 @@
       <c r="D83" s="13">
         <v>38845</v>
       </c>
-      <c r="E83" s="73">
+      <c r="E83" s="135">
         <v>213011043316</v>
       </c>
-      <c r="F83" s="72">
+      <c r="F83" s="145">
         <v>45618</v>
       </c>
       <c r="G83" s="9" t="s">
@@ -8091,16 +8096,16 @@
       <c r="H83" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="I83" s="96" t="s">
+      <c r="I83" s="72" t="s">
         <v>437</v>
       </c>
-      <c r="J83" s="128" t="s">
+      <c r="J83" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K83" s="107" t="s">
+      <c r="K83" s="83" t="s">
         <v>150</v>
       </c>
-      <c r="L83" s="109" t="s">
+      <c r="L83" s="85" t="s">
         <v>568</v>
       </c>
       <c r="M83" t="s">
@@ -8110,7 +8115,7 @@
         <f t="shared" si="4"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0037-SHS.png</v>
       </c>
-      <c r="O83" s="136" t="str">
+      <c r="O83" s="110" t="str">
         <f t="shared" si="5"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0037-SHS.png</v>
       </c>
@@ -8131,10 +8136,10 @@
       <c r="D84" s="13">
         <v>37561</v>
       </c>
-      <c r="E84" s="73">
+      <c r="E84" s="135">
         <v>208032006333</v>
       </c>
-      <c r="F84" s="72">
+      <c r="F84" s="145">
         <v>44354</v>
       </c>
       <c r="G84" s="9" t="s">
@@ -8143,16 +8148,16 @@
       <c r="H84" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="I84" s="96" t="s">
+      <c r="I84" s="72" t="s">
         <v>438</v>
       </c>
-      <c r="J84" s="128" t="s">
+      <c r="J84" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K84" s="107" t="s">
+      <c r="K84" s="83" t="s">
         <v>150</v>
       </c>
-      <c r="L84" s="109" t="s">
+      <c r="L84" s="85" t="s">
         <v>569</v>
       </c>
       <c r="M84" t="s">
@@ -8162,7 +8167,7 @@
         <f t="shared" si="4"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0038-SHS.png</v>
       </c>
-      <c r="O84" s="136" t="str">
+      <c r="O84" s="110" t="str">
         <f t="shared" si="5"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0038-SHS.png</v>
       </c>
@@ -8180,31 +8185,31 @@
       <c r="C85" s="3" t="s">
         <v>846</v>
       </c>
-      <c r="D85" s="59">
+      <c r="D85" s="49">
         <v>39448</v>
       </c>
-      <c r="E85" s="153">
+      <c r="E85" s="136">
         <v>213011045615</v>
       </c>
-      <c r="F85" s="150">
+      <c r="F85" s="146">
         <v>46139</v>
       </c>
       <c r="G85" s="9" t="s">
         <v>900</v>
       </c>
-      <c r="H85" s="58" t="s">
+      <c r="H85" s="48" t="s">
         <v>102</v>
       </c>
-      <c r="I85" s="96" t="s">
+      <c r="I85" s="72" t="s">
         <v>439</v>
       </c>
-      <c r="J85" s="128" t="s">
+      <c r="J85" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K85" s="107" t="s">
+      <c r="K85" s="83" t="s">
         <v>150</v>
       </c>
-      <c r="L85" s="109" t="s">
+      <c r="L85" s="85" t="s">
         <v>570</v>
       </c>
       <c r="M85" t="s">
@@ -8214,7 +8219,7 @@
         <f t="shared" si="4"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0039-SHS.png</v>
       </c>
-      <c r="O85" s="136" t="str">
+      <c r="O85" s="110" t="str">
         <f t="shared" si="5"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0039-SHS.png</v>
       </c>
@@ -8235,28 +8240,28 @@
       <c r="D86" s="13">
         <v>38163</v>
       </c>
-      <c r="E86" s="73">
+      <c r="E86" s="135">
         <v>212231007904</v>
       </c>
-      <c r="F86" s="72">
+      <c r="F86" s="145">
         <v>45282</v>
       </c>
       <c r="G86" s="9" t="s">
         <v>901</v>
       </c>
-      <c r="H86" s="58" t="s">
+      <c r="H86" s="48" t="s">
         <v>103</v>
       </c>
-      <c r="I86" s="96" t="s">
+      <c r="I86" s="72" t="s">
         <v>440</v>
       </c>
-      <c r="J86" s="128" t="s">
+      <c r="J86" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K86" s="107" t="s">
+      <c r="K86" s="83" t="s">
         <v>150</v>
       </c>
-      <c r="L86" s="110" t="s">
+      <c r="L86" s="86" t="s">
         <v>571</v>
       </c>
       <c r="M86" t="s">
@@ -8266,7 +8271,7 @@
         <f t="shared" si="4"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0040-SHS.png</v>
       </c>
-      <c r="O86" s="136" t="str">
+      <c r="O86" s="110" t="str">
         <f t="shared" si="5"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0040-SHS.png</v>
       </c>
@@ -8287,10 +8292,10 @@
       <c r="D87" s="13">
         <v>37897</v>
       </c>
-      <c r="E87" s="73">
+      <c r="E87" s="135">
         <v>213171007005</v>
       </c>
-      <c r="F87" s="150">
+      <c r="F87" s="146">
         <v>44791</v>
       </c>
       <c r="G87" s="9" t="s">
@@ -8299,16 +8304,16 @@
       <c r="H87" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="I87" s="96" t="s">
+      <c r="I87" s="72" t="s">
         <v>441</v>
       </c>
-      <c r="J87" s="128" t="s">
+      <c r="J87" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K87" s="107" t="s">
+      <c r="K87" s="83" t="s">
         <v>150</v>
       </c>
-      <c r="L87" s="109" t="s">
+      <c r="L87" s="85" t="s">
         <v>572</v>
       </c>
       <c r="M87" t="s">
@@ -8318,7 +8323,7 @@
         <f t="shared" si="4"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0041-SHS.png</v>
       </c>
-      <c r="O87" s="136" t="str">
+      <c r="O87" s="110" t="str">
         <f t="shared" si="5"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0041-SHS.png</v>
       </c>
@@ -8337,10 +8342,10 @@
       <c r="D88" s="13">
         <v>37985</v>
       </c>
-      <c r="E88" s="73">
+      <c r="E88" s="135">
         <v>213551008527</v>
       </c>
-      <c r="F88" s="78" t="s">
+      <c r="F88" s="145" t="s">
         <v>392</v>
       </c>
       <c r="G88" s="9" t="s">
@@ -8349,16 +8354,16 @@
       <c r="H88" s="14" t="s">
         <v>442</v>
       </c>
-      <c r="I88" s="96" t="s">
+      <c r="I88" s="72" t="s">
         <v>443</v>
       </c>
-      <c r="J88" s="128" t="s">
+      <c r="J88" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K88" s="107" t="s">
+      <c r="K88" s="83" t="s">
         <v>150</v>
       </c>
-      <c r="L88" s="109" t="s">
+      <c r="L88" s="85" t="s">
         <v>573</v>
       </c>
       <c r="M88" t="s">
@@ -8368,7 +8373,7 @@
         <f t="shared" si="4"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0042-SHS.png</v>
       </c>
-      <c r="O88" s="136" t="str">
+      <c r="O88" s="110" t="str">
         <f t="shared" si="5"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0042-SHS.png</v>
       </c>
@@ -8380,7 +8385,7 @@
       <c r="A89" s="8" t="s">
         <v>268</v>
       </c>
-      <c r="B89" s="140" t="s">
+      <c r="B89" s="114" t="s">
         <v>715</v>
       </c>
       <c r="C89" s="3" t="s">
@@ -8389,10 +8394,10 @@
       <c r="D89" s="13">
         <v>38933</v>
       </c>
-      <c r="E89" s="73">
+      <c r="E89" s="135">
         <v>213011043159</v>
       </c>
-      <c r="F89" s="72">
+      <c r="F89" s="145">
         <v>45932</v>
       </c>
       <c r="G89" s="9" t="s">
@@ -8401,16 +8406,16 @@
       <c r="H89" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="I89" s="96" t="s">
+      <c r="I89" s="72" t="s">
         <v>444</v>
       </c>
-      <c r="J89" s="128" t="s">
+      <c r="J89" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K89" s="107" t="s">
+      <c r="K89" s="83" t="s">
         <v>150</v>
       </c>
-      <c r="L89" s="109" t="s">
+      <c r="L89" s="85" t="s">
         <v>574</v>
       </c>
       <c r="M89" t="s">
@@ -8420,7 +8425,7 @@
         <f t="shared" si="4"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0043-SHS.png</v>
       </c>
-      <c r="O89" s="136" t="str">
+      <c r="O89" s="110" t="str">
         <f t="shared" si="5"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0043-SHS.png</v>
       </c>
@@ -8441,10 +8446,10 @@
       <c r="D90" s="13">
         <v>38687</v>
       </c>
-      <c r="E90" s="73">
+      <c r="E90" s="135">
         <v>213011043975</v>
       </c>
-      <c r="F90" s="72">
+      <c r="F90" s="145">
         <v>45744</v>
       </c>
       <c r="G90" s="9" t="s">
@@ -8453,16 +8458,16 @@
       <c r="H90" s="14" t="s">
         <v>431</v>
       </c>
-      <c r="I90" s="96" t="s">
+      <c r="I90" s="72" t="s">
         <v>445</v>
       </c>
-      <c r="J90" s="128" t="s">
+      <c r="J90" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K90" s="107" t="s">
+      <c r="K90" s="83" t="s">
         <v>150</v>
       </c>
-      <c r="L90" s="109" t="s">
+      <c r="L90" s="85" t="s">
         <v>575</v>
       </c>
       <c r="M90" t="s">
@@ -8472,7 +8477,7 @@
         <f t="shared" si="4"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0044-SHS.png</v>
       </c>
-      <c r="O90" s="136" t="str">
+      <c r="O90" s="110" t="str">
         <f t="shared" si="5"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0044-SHS.png</v>
       </c>
@@ -8484,7 +8489,7 @@
       <c r="A91" s="8" t="s">
         <v>271</v>
       </c>
-      <c r="B91" s="140" t="s">
+      <c r="B91" s="114" t="s">
         <v>714</v>
       </c>
       <c r="C91" s="3" t="s">
@@ -8493,10 +8498,10 @@
       <c r="D91" s="13">
         <v>36900</v>
       </c>
-      <c r="E91" s="73">
+      <c r="E91" s="135">
         <v>214152102001</v>
       </c>
-      <c r="F91" s="72">
+      <c r="F91" s="145">
         <v>44722</v>
       </c>
       <c r="G91" s="9" t="s">
@@ -8505,16 +8510,16 @@
       <c r="H91" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="I91" s="96" t="s">
+      <c r="I91" s="72" t="s">
         <v>446</v>
       </c>
-      <c r="J91" s="128" t="s">
+      <c r="J91" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K91" s="107" t="s">
+      <c r="K91" s="83" t="s">
         <v>150</v>
       </c>
-      <c r="L91" s="109" t="s">
+      <c r="L91" s="85" t="s">
         <v>576</v>
       </c>
       <c r="M91" t="s">
@@ -8524,7 +8529,7 @@
         <f t="shared" si="4"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0045-SHS.png</v>
       </c>
-      <c r="O91" s="136" t="str">
+      <c r="O91" s="110" t="str">
         <f t="shared" si="5"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0045-SHS.png</v>
       </c>
@@ -8545,10 +8550,10 @@
       <c r="D92" s="13">
         <v>38485</v>
       </c>
-      <c r="E92" s="73">
+      <c r="E92" s="135">
         <v>213012041689</v>
       </c>
-      <c r="F92" s="150">
+      <c r="F92" s="146">
         <v>45243</v>
       </c>
       <c r="G92" s="9" t="s">
@@ -8557,16 +8562,16 @@
       <c r="H92" s="14" t="s">
         <v>447</v>
       </c>
-      <c r="I92" s="96" t="s">
+      <c r="I92" s="72" t="s">
         <v>448</v>
       </c>
-      <c r="J92" s="128" t="s">
+      <c r="J92" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K92" s="107" t="s">
+      <c r="K92" s="83" t="s">
         <v>150</v>
       </c>
-      <c r="L92" s="109" t="s">
+      <c r="L92" s="85" t="s">
         <v>577</v>
       </c>
       <c r="M92" t="s">
@@ -8576,7 +8581,7 @@
         <f t="shared" si="4"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0046-SHS.png</v>
       </c>
-      <c r="O92" s="136" t="str">
+      <c r="O92" s="110" t="str">
         <f t="shared" si="5"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0046-SHS.png</v>
       </c>
@@ -8597,10 +8602,10 @@
       <c r="D93" s="13">
         <v>38115</v>
       </c>
-      <c r="E93" s="73">
+      <c r="E93" s="135">
         <v>213011038337</v>
       </c>
-      <c r="F93" s="72">
+      <c r="F93" s="145">
         <v>44726</v>
       </c>
       <c r="G93" s="9" t="s">
@@ -8609,16 +8614,16 @@
       <c r="H93" s="14" t="s">
         <v>394</v>
       </c>
-      <c r="I93" s="96" t="s">
+      <c r="I93" s="72" t="s">
         <v>449</v>
       </c>
-      <c r="J93" s="128" t="s">
+      <c r="J93" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K93" s="107" t="s">
+      <c r="K93" s="83" t="s">
         <v>150</v>
       </c>
-      <c r="L93" s="109" t="s">
+      <c r="L93" s="85" t="s">
         <v>578</v>
       </c>
       <c r="M93" t="s">
@@ -8628,7 +8633,7 @@
         <f t="shared" si="4"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0047-SHS.png</v>
       </c>
-      <c r="O93" s="136" t="str">
+      <c r="O93" s="110" t="str">
         <f t="shared" si="5"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0047-SHS.png</v>
       </c>
@@ -8649,10 +8654,10 @@
       <c r="D94" s="13">
         <v>37852</v>
       </c>
-      <c r="E94" s="73">
+      <c r="E94" s="135">
         <v>214151102686</v>
       </c>
-      <c r="F94" s="72">
+      <c r="F94" s="145">
         <v>44952</v>
       </c>
       <c r="G94" s="9" t="s">
@@ -8661,16 +8666,16 @@
       <c r="H94" s="14" t="s">
         <v>450</v>
       </c>
-      <c r="I94" s="96" t="s">
+      <c r="I94" s="72" t="s">
         <v>451</v>
       </c>
-      <c r="J94" s="128" t="s">
+      <c r="J94" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K94" s="107" t="s">
+      <c r="K94" s="83" t="s">
         <v>150</v>
       </c>
-      <c r="L94" s="109" t="s">
+      <c r="L94" s="85" t="s">
         <v>579</v>
       </c>
       <c r="M94" t="s">
@@ -8680,7 +8685,7 @@
         <f t="shared" si="4"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0048-SHS.png</v>
       </c>
-      <c r="O94" s="136" t="str">
+      <c r="O94" s="110" t="str">
         <f t="shared" si="5"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0048-SHS.png</v>
       </c>
@@ -8689,7 +8694,7 @@
       </c>
     </row>
     <row r="95" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A95" s="154" t="s">
+      <c r="A95" s="123" t="s">
         <v>713</v>
       </c>
       <c r="B95" s="9" t="s">
@@ -8701,10 +8706,10 @@
       <c r="D95" s="13">
         <v>37063</v>
       </c>
-      <c r="E95" s="73">
+      <c r="E95" s="135">
         <v>213551010207</v>
       </c>
-      <c r="F95" s="72">
+      <c r="F95" s="145">
         <v>45369</v>
       </c>
       <c r="G95" s="9" t="s">
@@ -8713,16 +8718,16 @@
       <c r="H95" s="14" t="s">
         <v>421</v>
       </c>
-      <c r="I95" s="96" t="s">
+      <c r="I95" s="72" t="s">
         <v>452</v>
       </c>
-      <c r="J95" s="128" t="s">
+      <c r="J95" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K95" s="107" t="s">
+      <c r="K95" s="83" t="s">
         <v>150</v>
       </c>
-      <c r="L95" s="109" t="s">
+      <c r="L95" s="85" t="s">
         <v>580</v>
       </c>
       <c r="M95" t="s">
@@ -8732,7 +8737,7 @@
         <f t="shared" si="4"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0049-SHS.png</v>
       </c>
-      <c r="O95" s="136" t="str">
+      <c r="O95" s="110" t="str">
         <f t="shared" si="5"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0049-SHS.png</v>
       </c>
@@ -8750,13 +8755,13 @@
       <c r="C96" s="3" t="s">
         <v>835</v>
       </c>
-      <c r="D96" s="143">
+      <c r="D96" s="117">
         <v>37622</v>
       </c>
-      <c r="E96" s="73">
+      <c r="E96" s="135">
         <v>213291004821</v>
       </c>
-      <c r="F96" s="72">
+      <c r="F96" s="145">
         <v>45523</v>
       </c>
       <c r="G96" s="9" t="s">
@@ -8765,16 +8770,16 @@
       <c r="H96" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="I96" s="96" t="s">
+      <c r="I96" s="72" t="s">
         <v>453</v>
       </c>
-      <c r="J96" s="128" t="s">
+      <c r="J96" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K96" s="107" t="s">
+      <c r="K96" s="83" t="s">
         <v>150</v>
       </c>
-      <c r="L96" s="109" t="s">
+      <c r="L96" s="85" t="s">
         <v>581</v>
       </c>
       <c r="M96" t="s">
@@ -8784,7 +8789,7 @@
         <f t="shared" si="4"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0050-SHS.png</v>
       </c>
-      <c r="O96" s="136" t="str">
+      <c r="O96" s="110" t="str">
         <f t="shared" si="5"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0050-SHS.png</v>
       </c>
@@ -8805,10 +8810,10 @@
       <c r="D97" s="13">
         <v>39460</v>
       </c>
-      <c r="E97" s="153">
+      <c r="E97" s="136">
         <v>213171014146</v>
       </c>
-      <c r="F97" s="150">
+      <c r="F97" s="146">
         <v>46087</v>
       </c>
       <c r="G97" s="9" t="s">
@@ -8817,16 +8822,16 @@
       <c r="H97" s="14" t="s">
         <v>454</v>
       </c>
-      <c r="I97" s="96" t="s">
+      <c r="I97" s="72" t="s">
         <v>455</v>
       </c>
-      <c r="J97" s="128" t="s">
+      <c r="J97" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K97" s="107" t="s">
+      <c r="K97" s="83" t="s">
         <v>150</v>
       </c>
-      <c r="L97" s="109" t="s">
+      <c r="L97" s="85" t="s">
         <v>582</v>
       </c>
       <c r="M97" t="s">
@@ -8836,7 +8841,7 @@
         <f t="shared" si="4"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0051-SHS.png</v>
       </c>
-      <c r="O97" s="136" t="str">
+      <c r="O97" s="110" t="str">
         <f t="shared" si="5"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0051-SHS.png</v>
       </c>
@@ -8857,10 +8862,10 @@
       <c r="D98" s="13">
         <v>37446</v>
       </c>
-      <c r="E98" s="73">
+      <c r="E98" s="135">
         <v>214012114078</v>
       </c>
-      <c r="F98" s="72">
+      <c r="F98" s="145">
         <v>44502</v>
       </c>
       <c r="G98" s="9" t="s">
@@ -8869,16 +8874,16 @@
       <c r="H98" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="I98" s="96" t="s">
+      <c r="I98" s="72" t="s">
         <v>456</v>
       </c>
-      <c r="J98" s="128" t="s">
+      <c r="J98" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K98" s="107" t="s">
+      <c r="K98" s="83" t="s">
         <v>150</v>
       </c>
-      <c r="L98" s="109" t="s">
+      <c r="L98" s="85" t="s">
         <v>583</v>
       </c>
       <c r="M98" t="s">
@@ -8888,7 +8893,7 @@
         <f t="shared" ref="N98:N106" si="6">"https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/" &amp; C98 &amp; ".png"</f>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0052-SHS.png</v>
       </c>
-      <c r="O98" s="136" t="str">
+      <c r="O98" s="110" t="str">
         <f t="shared" ref="O98:O106" si="7">"https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/" &amp; C98 &amp; ".png"</f>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0052-SHS.png</v>
       </c>
@@ -8897,40 +8902,40 @@
       </c>
     </row>
     <row r="99" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A99" s="50" t="s">
+      <c r="A99" s="40" t="s">
         <v>285</v>
       </c>
-      <c r="B99" s="51" t="s">
+      <c r="B99" s="41" t="s">
         <v>286</v>
       </c>
       <c r="C99" s="3" t="s">
         <v>832</v>
       </c>
-      <c r="D99" s="60">
+      <c r="D99" s="50">
         <v>38331</v>
       </c>
-      <c r="E99" s="79">
+      <c r="E99" s="137">
         <v>213151004045</v>
       </c>
-      <c r="F99" s="80">
+      <c r="F99" s="153">
         <v>45731</v>
       </c>
-      <c r="G99" s="51" t="s">
+      <c r="G99" s="41" t="s">
         <v>82</v>
       </c>
-      <c r="H99" s="97" t="s">
+      <c r="H99" s="73" t="s">
         <v>94</v>
       </c>
-      <c r="I99" s="98" t="s">
+      <c r="I99" s="74" t="s">
         <v>457</v>
       </c>
-      <c r="J99" s="128" t="s">
+      <c r="J99" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K99" s="111" t="s">
+      <c r="K99" s="87" t="s">
         <v>150</v>
       </c>
-      <c r="L99" s="112" t="s">
+      <c r="L99" s="88" t="s">
         <v>584</v>
       </c>
       <c r="M99" t="s">
@@ -8940,7 +8945,7 @@
         <f t="shared" si="6"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0053-SHS.png</v>
       </c>
-      <c r="O99" s="136" t="str">
+      <c r="O99" s="110" t="str">
         <f t="shared" si="7"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0053-SHS.png</v>
       </c>
@@ -8958,13 +8963,13 @@
       <c r="C100" s="3" t="s">
         <v>831</v>
       </c>
-      <c r="D100" s="143">
+      <c r="D100" s="117">
         <v>37622</v>
       </c>
-      <c r="E100" s="73">
+      <c r="E100" s="135">
         <v>213491009046</v>
       </c>
-      <c r="F100" s="72">
+      <c r="F100" s="145">
         <v>44874</v>
       </c>
       <c r="G100" s="9" t="s">
@@ -8973,16 +8978,16 @@
       <c r="H100" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="I100" s="96" t="s">
+      <c r="I100" s="72" t="s">
         <v>458</v>
       </c>
-      <c r="J100" s="128" t="s">
+      <c r="J100" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K100" s="107" t="s">
+      <c r="K100" s="83" t="s">
         <v>150</v>
       </c>
-      <c r="L100" s="109" t="s">
+      <c r="L100" s="85" t="s">
         <v>585</v>
       </c>
       <c r="M100" t="s">
@@ -8992,7 +8997,7 @@
         <f t="shared" si="6"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0054-SHS.png</v>
       </c>
-      <c r="O100" s="136" t="str">
+      <c r="O100" s="110" t="str">
         <f t="shared" si="7"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0054-SHS.png</v>
       </c>
@@ -9004,7 +9009,7 @@
       <c r="A101" s="8" t="s">
         <v>289</v>
       </c>
-      <c r="B101" s="140" t="s">
+      <c r="B101" s="114" t="s">
         <v>716</v>
       </c>
       <c r="C101" s="3" t="s">
@@ -9013,28 +9018,28 @@
       <c r="D101" s="13">
         <v>38459</v>
       </c>
-      <c r="E101" s="73">
+      <c r="E101" s="135">
         <v>213151004044</v>
       </c>
-      <c r="F101" s="72">
+      <c r="F101" s="145">
         <v>45728</v>
       </c>
       <c r="G101" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="H101" s="99" t="s">
+      <c r="H101" s="75" t="s">
         <v>87</v>
       </c>
-      <c r="I101" s="96" t="s">
+      <c r="I101" s="72" t="s">
         <v>459</v>
       </c>
-      <c r="J101" s="128" t="s">
+      <c r="J101" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K101" s="107" t="s">
+      <c r="K101" s="83" t="s">
         <v>150</v>
       </c>
-      <c r="L101" s="109" t="s">
+      <c r="L101" s="85" t="s">
         <v>586</v>
       </c>
       <c r="M101" t="s">
@@ -9044,7 +9049,7 @@
         <f t="shared" si="6"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0055-SHS.png</v>
       </c>
-      <c r="O101" s="136" t="str">
+      <c r="O101" s="110" t="str">
         <f t="shared" si="7"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0055-SHS.png</v>
       </c>
@@ -9065,10 +9070,10 @@
       <c r="D102" s="13">
         <v>39546</v>
       </c>
-      <c r="E102" s="153">
+      <c r="E102" s="136">
         <v>213012045616</v>
       </c>
-      <c r="F102" s="150">
+      <c r="F102" s="146">
         <v>46139</v>
       </c>
       <c r="G102" s="9" t="s">
@@ -9077,16 +9082,16 @@
       <c r="H102" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="I102" s="96" t="s">
+      <c r="I102" s="72" t="s">
         <v>460</v>
       </c>
-      <c r="J102" s="128" t="s">
+      <c r="J102" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K102" s="107" t="s">
+      <c r="K102" s="83" t="s">
         <v>150</v>
       </c>
-      <c r="L102" s="109" t="s">
+      <c r="L102" s="85" t="s">
         <v>587</v>
       </c>
       <c r="M102" t="s">
@@ -9096,7 +9101,7 @@
         <f t="shared" si="6"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0056-SHS.png</v>
       </c>
-      <c r="O102" s="136" t="str">
+      <c r="O102" s="110" t="str">
         <f t="shared" si="7"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0056-SHS.png</v>
       </c>
@@ -9117,10 +9122,10 @@
       <c r="D103" s="13">
         <v>38224</v>
       </c>
-      <c r="E103" s="73">
+      <c r="E103" s="135">
         <v>213011038881</v>
       </c>
-      <c r="F103" s="72">
+      <c r="F103" s="145">
         <v>44809</v>
       </c>
       <c r="G103" s="9" t="s">
@@ -9129,16 +9134,16 @@
       <c r="H103" s="14" t="s">
         <v>394</v>
       </c>
-      <c r="I103" s="96" t="s">
+      <c r="I103" s="72" t="s">
         <v>461</v>
       </c>
-      <c r="J103" s="128" t="s">
+      <c r="J103" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K103" s="107" t="s">
+      <c r="K103" s="83" t="s">
         <v>150</v>
       </c>
-      <c r="L103" s="109" t="s">
+      <c r="L103" s="85" t="s">
         <v>588</v>
       </c>
       <c r="M103" t="s">
@@ -9148,7 +9153,7 @@
         <f t="shared" si="6"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0057-SHS.png</v>
       </c>
-      <c r="O103" s="136" t="str">
+      <c r="O103" s="110" t="str">
         <f t="shared" si="7"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0057-SHS.png</v>
       </c>
@@ -9169,10 +9174,10 @@
       <c r="D104" s="13">
         <v>37987</v>
       </c>
-      <c r="E104" s="73">
+      <c r="E104" s="135">
         <v>214151102541</v>
       </c>
-      <c r="F104" s="72">
+      <c r="F104" s="145">
         <v>44931</v>
       </c>
       <c r="G104" s="9" t="s">
@@ -9181,16 +9186,16 @@
       <c r="H104" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="I104" s="96" t="s">
+      <c r="I104" s="72" t="s">
         <v>462</v>
       </c>
-      <c r="J104" s="128" t="s">
+      <c r="J104" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K104" s="107" t="s">
+      <c r="K104" s="83" t="s">
         <v>150</v>
       </c>
-      <c r="L104" s="109" t="s">
+      <c r="L104" s="85" t="s">
         <v>589</v>
       </c>
       <c r="M104" t="s">
@@ -9200,7 +9205,7 @@
         <f t="shared" si="6"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0058-SHS.png</v>
       </c>
-      <c r="O104" s="136" t="str">
+      <c r="O104" s="110" t="str">
         <f t="shared" si="7"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0058-SHS.png</v>
       </c>
@@ -9221,28 +9226,28 @@
       <c r="D105" s="13">
         <v>37723</v>
       </c>
-      <c r="E105" s="73">
+      <c r="E105" s="135">
         <v>214012116627</v>
       </c>
-      <c r="F105" s="72">
+      <c r="F105" s="145">
         <v>44897</v>
       </c>
       <c r="G105" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="H105" s="99" t="s">
+      <c r="H105" s="75" t="s">
         <v>463</v>
       </c>
-      <c r="I105" s="96" t="s">
+      <c r="I105" s="72" t="s">
         <v>464</v>
       </c>
-      <c r="J105" s="128" t="s">
+      <c r="J105" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K105" s="107" t="s">
+      <c r="K105" s="83" t="s">
         <v>150</v>
       </c>
-      <c r="L105" s="109" t="s">
+      <c r="L105" s="85" t="s">
         <v>590</v>
       </c>
       <c r="M105" t="s">
@@ -9252,7 +9257,7 @@
         <f t="shared" si="6"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0059-SHS.png</v>
       </c>
-      <c r="O105" s="136" t="str">
+      <c r="O105" s="110" t="str">
         <f t="shared" si="7"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0059-SHS.png</v>
       </c>
@@ -9273,10 +9278,10 @@
       <c r="D106" s="13">
         <v>37838</v>
       </c>
-      <c r="E106" s="73">
+      <c r="E106" s="135">
         <v>213011040674</v>
       </c>
-      <c r="F106" s="72">
+      <c r="F106" s="145">
         <v>45002</v>
       </c>
       <c r="G106" s="9" t="s">
@@ -9285,16 +9290,16 @@
       <c r="H106" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="I106" s="96" t="s">
+      <c r="I106" s="72" t="s">
         <v>465</v>
       </c>
-      <c r="J106" s="128" t="s">
+      <c r="J106" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K106" s="107" t="s">
+      <c r="K106" s="83" t="s">
         <v>150</v>
       </c>
-      <c r="L106" s="109" t="s">
+      <c r="L106" s="85" t="s">
         <v>591</v>
       </c>
       <c r="M106" t="s">
@@ -9304,7 +9309,7 @@
         <f t="shared" si="6"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0060-SHS.png</v>
       </c>
-      <c r="O106" s="136" t="str">
+      <c r="O106" s="110" t="str">
         <f t="shared" si="7"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0060-SHS.png</v>
       </c>
@@ -9313,40 +9318,40 @@
       </c>
     </row>
     <row r="107" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A107" s="52" t="s">
+      <c r="A107" s="42" t="s">
         <v>300</v>
       </c>
-      <c r="B107" s="53" t="s">
+      <c r="B107" s="43" t="s">
         <v>301</v>
       </c>
       <c r="C107" s="3" t="s">
         <v>824</v>
       </c>
-      <c r="D107" s="151">
+      <c r="D107" s="121">
         <v>37257</v>
       </c>
-      <c r="E107" s="81">
+      <c r="E107" s="138">
         <v>213151002796</v>
       </c>
-      <c r="F107" s="82">
+      <c r="F107" s="154">
         <v>44069</v>
       </c>
-      <c r="G107" s="83" t="s">
+      <c r="G107" s="66" t="s">
         <v>82</v>
       </c>
-      <c r="H107" s="66" t="s">
+      <c r="H107" s="56" t="s">
         <v>94</v>
       </c>
-      <c r="I107" s="100" t="s">
+      <c r="I107" s="76" t="s">
         <v>466</v>
       </c>
-      <c r="J107" s="128" t="s">
+      <c r="J107" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K107" s="113" t="s">
+      <c r="K107" s="89" t="s">
         <v>592</v>
       </c>
-      <c r="L107" s="114" t="s">
+      <c r="L107" s="90" t="s">
         <v>593</v>
       </c>
       <c r="M107" t="s">
@@ -9356,7 +9361,7 @@
         <f t="shared" ref="N107:N124" si="8">"https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/" &amp; C107 &amp; ".png"</f>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0061-SHS.png</v>
       </c>
-      <c r="O107" s="136" t="str">
+      <c r="O107" s="110" t="str">
         <f t="shared" ref="O107:O124" si="9">"https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/" &amp; C107 &amp; ".png"</f>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0061-SHS.png</v>
       </c>
@@ -9374,31 +9379,31 @@
       <c r="C108" s="3" t="s">
         <v>823</v>
       </c>
-      <c r="D108" s="62">
+      <c r="D108" s="52">
         <v>38751</v>
       </c>
-      <c r="E108" s="71">
+      <c r="E108" s="134">
         <v>213052010771</v>
       </c>
-      <c r="F108" s="75">
+      <c r="F108" s="155">
         <v>45363</v>
       </c>
-      <c r="G108" s="74" t="s">
+      <c r="G108" s="61" t="s">
         <v>82</v>
       </c>
-      <c r="H108" s="101" t="s">
+      <c r="H108" s="77" t="s">
         <v>89</v>
       </c>
-      <c r="I108" s="32" t="s">
+      <c r="I108" s="22" t="s">
         <v>467</v>
       </c>
-      <c r="J108" s="128" t="s">
+      <c r="J108" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K108" s="115" t="s">
+      <c r="K108" s="91" t="s">
         <v>592</v>
       </c>
-      <c r="L108" s="116" t="s">
+      <c r="L108" s="92" t="s">
         <v>594</v>
       </c>
       <c r="M108" t="s">
@@ -9408,7 +9413,7 @@
         <f t="shared" si="8"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0062-SHS.png</v>
       </c>
-      <c r="O108" s="136" t="str">
+      <c r="O108" s="110" t="str">
         <f t="shared" si="9"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0062-SHS.png</v>
       </c>
@@ -9427,28 +9432,28 @@
       <c r="D109" s="11">
         <v>36467</v>
       </c>
-      <c r="E109" s="71">
+      <c r="E109" s="134">
         <v>213211003777</v>
       </c>
-      <c r="F109" s="84">
+      <c r="F109" s="156">
         <v>43213</v>
       </c>
-      <c r="G109" s="78" t="s">
+      <c r="G109" s="65" t="s">
         <v>82</v>
       </c>
-      <c r="H109" s="57" t="s">
+      <c r="H109" s="47" t="s">
         <v>442</v>
       </c>
-      <c r="I109" s="32" t="s">
+      <c r="I109" s="22" t="s">
         <v>468</v>
       </c>
-      <c r="J109" s="128" t="s">
+      <c r="J109" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K109" s="115" t="s">
+      <c r="K109" s="91" t="s">
         <v>592</v>
       </c>
-      <c r="L109" s="116" t="s">
+      <c r="L109" s="92" t="s">
         <v>595</v>
       </c>
       <c r="M109" t="s">
@@ -9458,7 +9463,7 @@
         <f t="shared" si="8"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0063-SHS.png</v>
       </c>
-      <c r="O109" s="136" t="str">
+      <c r="O109" s="110" t="str">
         <f t="shared" si="9"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0063-SHS.png</v>
       </c>
@@ -9476,31 +9481,31 @@
       <c r="C110" s="3" t="s">
         <v>821</v>
       </c>
-      <c r="D110" s="157">
+      <c r="D110" s="124">
         <v>36161</v>
       </c>
-      <c r="E110" s="156">
+      <c r="E110" s="139">
         <v>420051006344</v>
       </c>
-      <c r="F110" s="75">
+      <c r="F110" s="155">
         <v>43622</v>
       </c>
-      <c r="G110" s="74" t="s">
+      <c r="G110" s="61" t="s">
         <v>902</v>
       </c>
-      <c r="H110" s="101" t="s">
+      <c r="H110" s="77" t="s">
         <v>469</v>
       </c>
-      <c r="I110" s="32" t="s">
+      <c r="I110" s="22" t="s">
         <v>470</v>
       </c>
-      <c r="J110" s="128" t="s">
+      <c r="J110" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K110" s="115" t="s">
+      <c r="K110" s="91" t="s">
         <v>592</v>
       </c>
-      <c r="L110" s="116" t="s">
+      <c r="L110" s="92" t="s">
         <v>596</v>
       </c>
       <c r="M110" t="s">
@@ -9510,7 +9515,7 @@
         <f t="shared" si="8"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0064-SHS.png</v>
       </c>
-      <c r="O110" s="136" t="str">
+      <c r="O110" s="110" t="str">
         <f t="shared" si="9"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0064-SHS.png</v>
       </c>
@@ -9526,31 +9531,31 @@
       <c r="C111" s="3" t="s">
         <v>820</v>
       </c>
-      <c r="D111" s="151">
+      <c r="D111" s="121">
         <v>37622</v>
       </c>
-      <c r="E111" s="71">
+      <c r="E111" s="134">
         <v>213291004302</v>
       </c>
-      <c r="F111" s="84">
+      <c r="F111" s="156">
         <v>45184</v>
       </c>
-      <c r="G111" s="78" t="s">
+      <c r="G111" s="65" t="s">
         <v>82</v>
       </c>
-      <c r="H111" s="57" t="s">
+      <c r="H111" s="47" t="s">
         <v>471</v>
       </c>
-      <c r="I111" s="32" t="s">
+      <c r="I111" s="22" t="s">
         <v>472</v>
       </c>
-      <c r="J111" s="128" t="s">
+      <c r="J111" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K111" s="115" t="s">
+      <c r="K111" s="91" t="s">
         <v>592</v>
       </c>
-      <c r="L111" s="116" t="s">
+      <c r="L111" s="92" t="s">
         <v>597</v>
       </c>
       <c r="M111" t="s">
@@ -9560,7 +9565,7 @@
         <f t="shared" si="8"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0065-SHS.png</v>
       </c>
-      <c r="O111" s="136" t="str">
+      <c r="O111" s="110" t="str">
         <f t="shared" si="9"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0065-SHS.png</v>
       </c>
@@ -9581,28 +9586,28 @@
       <c r="D112" s="11">
         <v>39112</v>
       </c>
-      <c r="E112" s="71">
+      <c r="E112" s="134">
         <v>217032010764</v>
       </c>
-      <c r="F112" s="84">
+      <c r="F112" s="156">
         <v>45618</v>
       </c>
-      <c r="G112" s="78" t="s">
+      <c r="G112" s="65" t="s">
         <v>84</v>
       </c>
-      <c r="H112" s="57" t="s">
+      <c r="H112" s="47" t="s">
         <v>86</v>
       </c>
-      <c r="I112" s="32" t="s">
+      <c r="I112" s="22" t="s">
         <v>473</v>
       </c>
-      <c r="J112" s="128" t="s">
+      <c r="J112" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K112" s="115" t="s">
+      <c r="K112" s="91" t="s">
         <v>592</v>
       </c>
-      <c r="L112" s="116" t="s">
+      <c r="L112" s="92" t="s">
         <v>598</v>
       </c>
       <c r="M112" t="s">
@@ -9612,7 +9617,7 @@
         <f t="shared" si="8"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0066-SHS.png</v>
       </c>
-      <c r="O112" s="136" t="str">
+      <c r="O112" s="110" t="str">
         <f t="shared" si="9"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0066-SHS.png</v>
       </c>
@@ -9633,28 +9638,28 @@
       <c r="D113" s="11">
         <v>38652</v>
       </c>
-      <c r="E113" s="71">
+      <c r="E113" s="134">
         <v>213331006794</v>
       </c>
-      <c r="F113" s="84">
+      <c r="F113" s="156">
         <v>45334</v>
       </c>
-      <c r="G113" s="78" t="s">
+      <c r="G113" s="65" t="s">
         <v>82</v>
       </c>
-      <c r="H113" s="101" t="s">
+      <c r="H113" s="77" t="s">
         <v>89</v>
       </c>
-      <c r="I113" s="32" t="s">
+      <c r="I113" s="22" t="s">
         <v>474</v>
       </c>
-      <c r="J113" s="128" t="s">
+      <c r="J113" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K113" s="115" t="s">
+      <c r="K113" s="91" t="s">
         <v>592</v>
       </c>
-      <c r="L113" s="116" t="s">
+      <c r="L113" s="92" t="s">
         <v>599</v>
       </c>
       <c r="M113" t="s">
@@ -9664,7 +9669,7 @@
         <f t="shared" si="8"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0067-SHS.png</v>
       </c>
-      <c r="O113" s="136" t="str">
+      <c r="O113" s="110" t="str">
         <f t="shared" si="9"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0067-SHS.png</v>
       </c>
@@ -9685,28 +9690,28 @@
       <c r="D114" s="11">
         <v>32758</v>
       </c>
-      <c r="E114" s="71">
+      <c r="E114" s="134">
         <v>213011020231</v>
       </c>
-      <c r="F114" s="84">
+      <c r="F114" s="156">
         <v>39720</v>
       </c>
-      <c r="G114" s="78" t="s">
+      <c r="G114" s="65" t="s">
         <v>82</v>
       </c>
-      <c r="H114" s="57" t="s">
+      <c r="H114" s="47" t="s">
         <v>91</v>
       </c>
-      <c r="I114" s="32" t="s">
+      <c r="I114" s="22" t="s">
         <v>475</v>
       </c>
-      <c r="J114" s="128" t="s">
+      <c r="J114" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K114" s="115" t="s">
+      <c r="K114" s="91" t="s">
         <v>592</v>
       </c>
-      <c r="L114" s="117" t="s">
+      <c r="L114" s="93" t="s">
         <v>600</v>
       </c>
       <c r="M114" t="s">
@@ -9716,7 +9721,7 @@
         <f t="shared" si="8"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0068-SHS.png</v>
       </c>
-      <c r="O114" s="136" t="str">
+      <c r="O114" s="110" t="str">
         <f t="shared" si="9"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0068-SHS.png</v>
       </c>
@@ -9734,31 +9739,31 @@
       <c r="C115" s="3" t="s">
         <v>816</v>
       </c>
-      <c r="D115" s="62">
+      <c r="D115" s="52">
         <v>38619</v>
       </c>
-      <c r="E115" s="71">
+      <c r="E115" s="134">
         <v>213011041969</v>
       </c>
-      <c r="F115" s="77">
+      <c r="F115" s="157">
         <v>45324</v>
       </c>
-      <c r="G115" s="76" t="s">
+      <c r="G115" s="63" t="s">
         <v>82</v>
       </c>
-      <c r="H115" s="101" t="s">
+      <c r="H115" s="77" t="s">
         <v>90</v>
       </c>
-      <c r="I115" s="32" t="s">
+      <c r="I115" s="22" t="s">
         <v>476</v>
       </c>
-      <c r="J115" s="128" t="s">
+      <c r="J115" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K115" s="115" t="s">
+      <c r="K115" s="91" t="s">
         <v>592</v>
       </c>
-      <c r="L115" s="116" t="s">
+      <c r="L115" s="92" t="s">
         <v>601</v>
       </c>
       <c r="M115" t="s">
@@ -9768,7 +9773,7 @@
         <f t="shared" si="8"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0069-SHS.png</v>
       </c>
-      <c r="O115" s="136" t="str">
+      <c r="O115" s="110" t="str">
         <f t="shared" si="9"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0069-SHS.png</v>
       </c>
@@ -9780,7 +9785,7 @@
       <c r="A116" s="4" t="s">
         <v>316</v>
       </c>
-      <c r="B116" s="142" t="s">
+      <c r="B116" s="116" t="s">
         <v>719</v>
       </c>
       <c r="C116" s="3" t="s">
@@ -9789,28 +9794,28 @@
       <c r="D116" s="11">
         <v>38523</v>
       </c>
-      <c r="E116" s="71">
+      <c r="E116" s="134">
         <v>213011041311</v>
       </c>
-      <c r="F116" s="84">
+      <c r="F116" s="156">
         <v>45161</v>
       </c>
-      <c r="G116" s="78" t="s">
+      <c r="G116" s="65" t="s">
         <v>82</v>
       </c>
-      <c r="H116" s="57" t="s">
+      <c r="H116" s="47" t="s">
         <v>86</v>
       </c>
-      <c r="I116" s="32" t="s">
+      <c r="I116" s="22" t="s">
         <v>477</v>
       </c>
-      <c r="J116" s="128" t="s">
+      <c r="J116" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K116" s="115" t="s">
+      <c r="K116" s="91" t="s">
         <v>592</v>
       </c>
-      <c r="L116" s="116" t="s">
+      <c r="L116" s="92" t="s">
         <v>602</v>
       </c>
       <c r="M116" t="s">
@@ -9820,7 +9825,7 @@
         <f t="shared" si="8"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0070-SHS.png</v>
       </c>
-      <c r="O116" s="136" t="str">
+      <c r="O116" s="110" t="str">
         <f t="shared" si="9"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0070-SHS.png</v>
       </c>
@@ -9841,28 +9846,28 @@
       <c r="D117" s="11">
         <v>38121</v>
       </c>
-      <c r="E117" s="71">
+      <c r="E117" s="134">
         <v>213011039957</v>
       </c>
-      <c r="F117" s="84">
+      <c r="F117" s="156">
         <v>44939</v>
       </c>
-      <c r="G117" s="78" t="s">
+      <c r="G117" s="65" t="s">
         <v>82</v>
       </c>
-      <c r="H117" s="57" t="s">
+      <c r="H117" s="47" t="s">
         <v>92</v>
       </c>
-      <c r="I117" s="32" t="s">
+      <c r="I117" s="22" t="s">
         <v>478</v>
       </c>
-      <c r="J117" s="128" t="s">
+      <c r="J117" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K117" s="115" t="s">
+      <c r="K117" s="91" t="s">
         <v>592</v>
       </c>
-      <c r="L117" s="116" t="s">
+      <c r="L117" s="92" t="s">
         <v>603</v>
       </c>
       <c r="M117" t="s">
@@ -9872,7 +9877,7 @@
         <f t="shared" si="8"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0071-SHS.png</v>
       </c>
-      <c r="O117" s="136" t="str">
+      <c r="O117" s="110" t="str">
         <f t="shared" si="9"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0071-SHS.png</v>
       </c>
@@ -9890,31 +9895,31 @@
       <c r="C118" s="3" t="s">
         <v>813</v>
       </c>
-      <c r="D118" s="62">
+      <c r="D118" s="52">
         <v>36900</v>
       </c>
-      <c r="E118" s="71">
+      <c r="E118" s="134">
         <v>213431000221</v>
       </c>
-      <c r="F118" s="84">
+      <c r="F118" s="156">
         <v>43551</v>
       </c>
-      <c r="G118" s="78" t="s">
+      <c r="G118" s="65" t="s">
         <v>82</v>
       </c>
-      <c r="H118" s="101" t="s">
+      <c r="H118" s="77" t="s">
         <v>103</v>
       </c>
-      <c r="I118" s="32" t="s">
+      <c r="I118" s="22" t="s">
         <v>479</v>
       </c>
-      <c r="J118" s="128" t="s">
+      <c r="J118" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K118" s="115" t="s">
+      <c r="K118" s="91" t="s">
         <v>592</v>
       </c>
-      <c r="L118" s="116" t="s">
+      <c r="L118" s="92" t="s">
         <v>604</v>
       </c>
       <c r="M118" t="s">
@@ -9924,7 +9929,7 @@
         <f t="shared" si="8"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0072-SHS.png</v>
       </c>
-      <c r="O118" s="136" t="str">
+      <c r="O118" s="110" t="str">
         <f t="shared" si="9"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0072-SHS.png</v>
       </c>
@@ -9942,31 +9947,31 @@
       <c r="C119" s="3" t="s">
         <v>812</v>
       </c>
-      <c r="D119" s="151">
+      <c r="D119" s="121">
         <v>37622</v>
       </c>
-      <c r="E119" s="71">
+      <c r="E119" s="134">
         <v>213371007057</v>
       </c>
-      <c r="F119" s="84">
+      <c r="F119" s="156">
         <v>44672</v>
       </c>
-      <c r="G119" s="78" t="s">
+      <c r="G119" s="65" t="s">
         <v>82</v>
       </c>
-      <c r="H119" s="57" t="s">
+      <c r="H119" s="47" t="s">
         <v>100</v>
       </c>
-      <c r="I119" s="32" t="s">
+      <c r="I119" s="22" t="s">
         <v>480</v>
       </c>
-      <c r="J119" s="128" t="s">
+      <c r="J119" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K119" s="115" t="s">
+      <c r="K119" s="91" t="s">
         <v>592</v>
       </c>
-      <c r="L119" s="118" t="s">
+      <c r="L119" s="94" t="s">
         <v>606</v>
       </c>
       <c r="M119" t="s">
@@ -9976,7 +9981,7 @@
         <f t="shared" si="8"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0073-SHS.png</v>
       </c>
-      <c r="O119" s="136" t="str">
+      <c r="O119" s="110" t="str">
         <f t="shared" si="9"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0073-SHS.png</v>
       </c>
@@ -9988,7 +9993,7 @@
       <c r="A120" s="4" t="s">
         <v>321</v>
       </c>
-      <c r="B120" s="142" t="s">
+      <c r="B120" s="116" t="s">
         <v>718</v>
       </c>
       <c r="C120" s="3" t="s">
@@ -9997,28 +10002,28 @@
       <c r="D120" s="11">
         <v>38101</v>
       </c>
-      <c r="E120" s="71">
+      <c r="E120" s="134">
         <v>213011040630</v>
       </c>
-      <c r="F120" s="84">
+      <c r="F120" s="156">
         <v>44998</v>
       </c>
-      <c r="G120" s="78" t="s">
+      <c r="G120" s="65" t="s">
         <v>82</v>
       </c>
-      <c r="H120" s="57" t="s">
+      <c r="H120" s="47" t="s">
         <v>86</v>
       </c>
-      <c r="I120" s="32" t="s">
+      <c r="I120" s="22" t="s">
         <v>481</v>
       </c>
-      <c r="J120" s="128" t="s">
+      <c r="J120" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K120" s="115" t="s">
+      <c r="K120" s="91" t="s">
         <v>592</v>
       </c>
-      <c r="L120" s="116" t="s">
+      <c r="L120" s="92" t="s">
         <v>607</v>
       </c>
       <c r="M120" t="s">
@@ -10028,7 +10033,7 @@
         <f t="shared" si="8"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0074-SHS.png</v>
       </c>
-      <c r="O120" s="136" t="str">
+      <c r="O120" s="110" t="str">
         <f t="shared" si="9"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0074-SHS.png</v>
       </c>
@@ -10049,28 +10054,28 @@
       <c r="D121" s="11">
         <v>37940</v>
       </c>
-      <c r="E121" s="71">
+      <c r="E121" s="134">
         <v>213071009273</v>
       </c>
-      <c r="F121" s="84">
+      <c r="F121" s="156">
         <v>44883</v>
       </c>
-      <c r="G121" s="78" t="s">
+      <c r="G121" s="65" t="s">
         <v>82</v>
       </c>
-      <c r="H121" s="57" t="s">
+      <c r="H121" s="47" t="s">
         <v>482</v>
       </c>
-      <c r="I121" s="32" t="s">
+      <c r="I121" s="22" t="s">
         <v>483</v>
       </c>
-      <c r="J121" s="128" t="s">
+      <c r="J121" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K121" s="115" t="s">
+      <c r="K121" s="91" t="s">
         <v>592</v>
       </c>
-      <c r="L121" s="116" t="s">
+      <c r="L121" s="92" t="s">
         <v>608</v>
       </c>
       <c r="M121" t="s">
@@ -10080,7 +10085,7 @@
         <f t="shared" si="8"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0075-SHS.png</v>
       </c>
-      <c r="O121" s="136" t="str">
+      <c r="O121" s="110" t="str">
         <f t="shared" si="9"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0075-SHS.png</v>
       </c>
@@ -10092,37 +10097,37 @@
       <c r="A122" s="8" t="s">
         <v>323</v>
       </c>
-      <c r="B122" s="140" t="s">
+      <c r="B122" s="114" t="s">
         <v>717</v>
       </c>
       <c r="C122" s="3" t="s">
         <v>809</v>
       </c>
-      <c r="D122" s="59">
+      <c r="D122" s="49">
         <v>38227</v>
       </c>
-      <c r="E122" s="71">
+      <c r="E122" s="134">
         <v>213591006418</v>
       </c>
-      <c r="F122" s="75">
+      <c r="F122" s="155">
         <v>45324</v>
       </c>
-      <c r="G122" s="74" t="s">
+      <c r="G122" s="61" t="s">
         <v>82</v>
       </c>
-      <c r="H122" s="58" t="s">
+      <c r="H122" s="48" t="s">
         <v>91</v>
       </c>
-      <c r="I122" s="34" t="s">
+      <c r="I122" s="24" t="s">
         <v>484</v>
       </c>
-      <c r="J122" s="128" t="s">
+      <c r="J122" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K122" s="115" t="s">
+      <c r="K122" s="91" t="s">
         <v>592</v>
       </c>
-      <c r="L122" s="119" t="s">
+      <c r="L122" s="95" t="s">
         <v>609</v>
       </c>
       <c r="M122" t="s">
@@ -10132,7 +10137,7 @@
         <f t="shared" si="8"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0076-SHS.png</v>
       </c>
-      <c r="O122" s="136" t="str">
+      <c r="O122" s="110" t="str">
         <f t="shared" si="9"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0076-SHS.png</v>
       </c>
@@ -10153,28 +10158,28 @@
       <c r="D123" s="13">
         <v>38014</v>
       </c>
-      <c r="E123" s="71">
+      <c r="E123" s="134">
         <v>213012042230</v>
       </c>
-      <c r="F123" s="84">
+      <c r="F123" s="156">
         <v>45366</v>
       </c>
-      <c r="G123" s="78" t="s">
+      <c r="G123" s="65" t="s">
         <v>82</v>
       </c>
       <c r="H123" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="I123" s="34" t="s">
+      <c r="I123" s="24" t="s">
         <v>485</v>
       </c>
-      <c r="J123" s="128" t="s">
+      <c r="J123" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K123" s="115" t="s">
+      <c r="K123" s="91" t="s">
         <v>592</v>
       </c>
-      <c r="L123" s="119" t="s">
+      <c r="L123" s="95" t="s">
         <v>610</v>
       </c>
       <c r="M123" t="s">
@@ -10184,7 +10189,7 @@
         <f t="shared" si="8"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0077-SHS.png</v>
       </c>
-      <c r="O123" s="136" t="str">
+      <c r="O123" s="110" t="str">
         <f t="shared" si="9"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0077-SHS.png</v>
       </c>
@@ -10193,7 +10198,7 @@
       </c>
     </row>
     <row r="124" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A124" s="49" t="s">
+      <c r="A124" s="39" t="s">
         <v>326</v>
       </c>
       <c r="B124" s="9"/>
@@ -10203,28 +10208,28 @@
       <c r="D124" s="13">
         <v>38630</v>
       </c>
-      <c r="E124" s="71">
+      <c r="E124" s="134">
         <v>213011042019</v>
       </c>
-      <c r="F124" s="84">
+      <c r="F124" s="156">
         <v>45334</v>
       </c>
-      <c r="G124" s="78" t="s">
+      <c r="G124" s="65" t="s">
         <v>82</v>
       </c>
-      <c r="H124" s="58" t="s">
+      <c r="H124" s="48" t="s">
         <v>95</v>
       </c>
-      <c r="I124" s="34" t="s">
+      <c r="I124" s="24" t="s">
         <v>486</v>
       </c>
-      <c r="J124" s="128" t="s">
+      <c r="J124" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K124" s="115" t="s">
+      <c r="K124" s="91" t="s">
         <v>592</v>
       </c>
-      <c r="L124" s="119" t="s">
+      <c r="L124" s="95" t="s">
         <v>611</v>
       </c>
       <c r="M124" t="s">
@@ -10234,7 +10239,7 @@
         <f t="shared" si="8"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0078-SHS.png</v>
       </c>
-      <c r="O124" s="136" t="str">
+      <c r="O124" s="110" t="str">
         <f t="shared" si="9"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0078-SHS.png</v>
       </c>
@@ -10246,47 +10251,47 @@
       <c r="A125" s="4" t="s">
         <v>327</v>
       </c>
-      <c r="B125" s="142" t="s">
+      <c r="B125" s="116" t="s">
         <v>720</v>
       </c>
       <c r="C125" s="3" t="s">
         <v>806</v>
       </c>
-      <c r="D125" s="61">
+      <c r="D125" s="51">
         <v>37350</v>
       </c>
-      <c r="E125" s="81">
+      <c r="E125" s="138">
         <v>213011035292</v>
       </c>
-      <c r="F125" s="85">
+      <c r="F125" s="158">
         <v>43928</v>
       </c>
-      <c r="G125" s="55" t="s">
+      <c r="G125" s="45" t="s">
         <v>82</v>
       </c>
-      <c r="H125" s="66" t="s">
+      <c r="H125" s="56" t="s">
         <v>104</v>
       </c>
-      <c r="I125" s="100" t="s">
+      <c r="I125" s="76" t="s">
         <v>487</v>
       </c>
-      <c r="J125" s="128" t="s">
+      <c r="J125" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K125" s="120" t="s">
+      <c r="K125" s="96" t="s">
         <v>605</v>
       </c>
-      <c r="L125" s="121" t="s">
+      <c r="L125" s="97" t="s">
         <v>612</v>
       </c>
-      <c r="M125" s="137" t="s">
+      <c r="M125" s="111" t="s">
         <v>693</v>
       </c>
       <c r="N125" t="str">
         <f t="shared" ref="N125:N163" si="10">"https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/" &amp; C125 &amp; ".png"</f>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0079-SHS.png</v>
       </c>
-      <c r="O125" s="136" t="str">
+      <c r="O125" s="110" t="str">
         <f t="shared" ref="O125:O163" si="11">"https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/" &amp; C125 &amp; ".png"</f>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0079-SHS.png</v>
       </c>
@@ -10298,37 +10303,37 @@
       <c r="A126" s="4" t="s">
         <v>328</v>
       </c>
-      <c r="B126" s="53" t="s">
+      <c r="B126" s="43" t="s">
         <v>329</v>
       </c>
       <c r="C126" s="3" t="s">
         <v>805</v>
       </c>
-      <c r="D126" s="61">
+      <c r="D126" s="51">
         <v>37050</v>
       </c>
-      <c r="E126" s="81">
+      <c r="E126" s="138">
         <v>213011036670</v>
       </c>
-      <c r="F126" s="85">
+      <c r="F126" s="158">
         <v>44302</v>
       </c>
-      <c r="G126" s="55" t="s">
+      <c r="G126" s="45" t="s">
         <v>82</v>
       </c>
-      <c r="H126" s="66" t="s">
+      <c r="H126" s="56" t="s">
         <v>469</v>
       </c>
-      <c r="I126" s="100" t="s">
+      <c r="I126" s="76" t="s">
         <v>488</v>
       </c>
-      <c r="J126" s="128" t="s">
+      <c r="J126" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K126" s="120" t="s">
+      <c r="K126" s="96" t="s">
         <v>605</v>
       </c>
-      <c r="L126" s="121" t="s">
+      <c r="L126" s="97" t="s">
         <v>613</v>
       </c>
       <c r="M126" t="s">
@@ -10338,7 +10343,7 @@
         <f t="shared" si="10"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0080-SHS.png</v>
       </c>
-      <c r="O126" s="136" t="str">
+      <c r="O126" s="110" t="str">
         <f t="shared" si="11"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0080-SHS.png</v>
       </c>
@@ -10347,38 +10352,38 @@
       </c>
     </row>
     <row r="127" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A127" s="139" t="s">
+      <c r="A127" s="113" t="s">
         <v>696</v>
       </c>
-      <c r="B127" s="53"/>
+      <c r="B127" s="43"/>
       <c r="C127" s="3" t="s">
         <v>804</v>
       </c>
-      <c r="D127" s="63">
+      <c r="D127" s="53">
         <v>36498</v>
       </c>
-      <c r="E127" s="81">
+      <c r="E127" s="138">
         <v>403031006361</v>
       </c>
-      <c r="F127" s="85">
+      <c r="F127" s="158">
         <v>43999</v>
       </c>
-      <c r="G127" s="55" t="s">
+      <c r="G127" s="45" t="s">
         <v>82</v>
       </c>
-      <c r="H127" s="66" t="s">
+      <c r="H127" s="56" t="s">
         <v>90</v>
       </c>
-      <c r="I127" s="100" t="s">
+      <c r="I127" s="76" t="s">
         <v>489</v>
       </c>
-      <c r="J127" s="128" t="s">
+      <c r="J127" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K127" s="120" t="s">
+      <c r="K127" s="96" t="s">
         <v>605</v>
       </c>
-      <c r="L127" s="121" t="s">
+      <c r="L127" s="97" t="s">
         <v>614</v>
       </c>
       <c r="M127" t="s">
@@ -10388,7 +10393,7 @@
         <f t="shared" si="10"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0081-SHS.png</v>
       </c>
-      <c r="O127" s="136" t="str">
+      <c r="O127" s="110" t="str">
         <f t="shared" si="11"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0081-SHS.png</v>
       </c>
@@ -10400,35 +10405,35 @@
       <c r="A128" s="4" t="s">
         <v>330</v>
       </c>
-      <c r="B128" s="53"/>
+      <c r="B128" s="43"/>
       <c r="C128" s="3" t="s">
         <v>803</v>
       </c>
-      <c r="D128" s="64">
+      <c r="D128" s="54">
         <v>37257</v>
       </c>
-      <c r="E128" s="81">
+      <c r="E128" s="138">
         <v>213611001592</v>
       </c>
-      <c r="F128" s="85">
+      <c r="F128" s="158">
         <v>44610</v>
       </c>
-      <c r="G128" s="55" t="s">
+      <c r="G128" s="45" t="s">
         <v>82</v>
       </c>
-      <c r="H128" s="65" t="s">
+      <c r="H128" s="55" t="s">
         <v>91</v>
       </c>
-      <c r="I128" s="100" t="s">
+      <c r="I128" s="76" t="s">
         <v>490</v>
       </c>
-      <c r="J128" s="128" t="s">
+      <c r="J128" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K128" s="120" t="s">
+      <c r="K128" s="96" t="s">
         <v>605</v>
       </c>
-      <c r="L128" s="121" t="s">
+      <c r="L128" s="97" t="s">
         <v>615</v>
       </c>
       <c r="M128" t="s">
@@ -10438,7 +10443,7 @@
         <f t="shared" si="10"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0082-SHS.png</v>
       </c>
-      <c r="O128" s="136" t="str">
+      <c r="O128" s="110" t="str">
         <f t="shared" si="11"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0082-SHS.png</v>
       </c>
@@ -10447,40 +10452,40 @@
       </c>
     </row>
     <row r="129" spans="1:16" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A129" s="54" t="s">
+      <c r="A129" s="44" t="s">
         <v>331</v>
       </c>
-      <c r="B129" s="53" t="s">
+      <c r="B129" s="43" t="s">
         <v>332</v>
       </c>
       <c r="C129" s="3" t="s">
         <v>802</v>
       </c>
-      <c r="D129" s="157">
+      <c r="D129" s="124">
         <v>36892</v>
       </c>
-      <c r="E129" s="81">
+      <c r="E129" s="138">
         <v>213071008530</v>
       </c>
-      <c r="F129" s="86">
+      <c r="F129" s="159">
         <v>44146</v>
       </c>
-      <c r="G129" s="87" t="s">
+      <c r="G129" s="67" t="s">
         <v>904</v>
       </c>
-      <c r="H129" s="65" t="s">
+      <c r="H129" s="55" t="s">
         <v>482</v>
       </c>
-      <c r="I129" s="100" t="s">
+      <c r="I129" s="76" t="s">
         <v>491</v>
       </c>
-      <c r="J129" s="128" t="s">
+      <c r="J129" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K129" s="120" t="s">
+      <c r="K129" s="96" t="s">
         <v>605</v>
       </c>
-      <c r="L129" s="121" t="s">
+      <c r="L129" s="97" t="s">
         <v>616</v>
       </c>
       <c r="M129" t="s">
@@ -10490,7 +10495,7 @@
         <f t="shared" si="10"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0083-SHS.png</v>
       </c>
-      <c r="O129" s="136" t="str">
+      <c r="O129" s="110" t="str">
         <f t="shared" si="11"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0083-SHS.png</v>
       </c>
@@ -10502,7 +10507,7 @@
       <c r="A130" s="4" t="s">
         <v>333</v>
       </c>
-      <c r="B130" s="53" t="s">
+      <c r="B130" s="43" t="s">
         <v>334</v>
       </c>
       <c r="C130" s="3" t="s">
@@ -10511,28 +10516,28 @@
       <c r="D130" s="11">
         <v>36719</v>
       </c>
-      <c r="E130" s="88">
+      <c r="E130" s="140">
         <v>214431100893</v>
       </c>
-      <c r="F130" s="72">
+      <c r="F130" s="145">
         <v>43542</v>
       </c>
-      <c r="G130" s="55" t="s">
+      <c r="G130" s="45" t="s">
         <v>83</v>
       </c>
-      <c r="H130" s="57" t="s">
+      <c r="H130" s="47" t="s">
         <v>86</v>
       </c>
-      <c r="I130" s="32" t="s">
+      <c r="I130" s="22" t="s">
         <v>492</v>
       </c>
-      <c r="J130" s="128" t="s">
+      <c r="J130" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K130" s="120" t="s">
+      <c r="K130" s="96" t="s">
         <v>605</v>
       </c>
-      <c r="L130" s="122" t="s">
+      <c r="L130" s="98" t="s">
         <v>617</v>
       </c>
       <c r="M130" t="s">
@@ -10542,7 +10547,7 @@
         <f t="shared" si="10"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0084-SHS.png</v>
       </c>
-      <c r="O130" s="136" t="str">
+      <c r="O130" s="110" t="str">
         <f t="shared" si="11"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0084-SHS.png</v>
       </c>
@@ -10554,37 +10559,37 @@
       <c r="A131" s="4" t="s">
         <v>335</v>
       </c>
-      <c r="B131" s="53" t="s">
+      <c r="B131" s="43" t="s">
         <v>336</v>
       </c>
       <c r="C131" s="3" t="s">
         <v>800</v>
       </c>
-      <c r="D131" s="61">
+      <c r="D131" s="51">
         <v>35727</v>
       </c>
-      <c r="E131" s="81">
+      <c r="E131" s="138">
         <v>213011030676</v>
       </c>
-      <c r="F131" s="85">
+      <c r="F131" s="158">
         <v>42859</v>
       </c>
-      <c r="G131" s="55" t="s">
+      <c r="G131" s="45" t="s">
         <v>82</v>
       </c>
-      <c r="H131" s="66" t="s">
+      <c r="H131" s="56" t="s">
         <v>97</v>
       </c>
-      <c r="I131" s="100" t="s">
+      <c r="I131" s="76" t="s">
         <v>493</v>
       </c>
-      <c r="J131" s="128" t="s">
+      <c r="J131" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K131" s="120" t="s">
+      <c r="K131" s="96" t="s">
         <v>605</v>
       </c>
-      <c r="L131" s="121" t="s">
+      <c r="L131" s="97" t="s">
         <v>618</v>
       </c>
       <c r="M131" t="s">
@@ -10594,7 +10599,7 @@
         <f t="shared" si="10"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0085-SHS.png</v>
       </c>
-      <c r="O131" s="136" t="str">
+      <c r="O131" s="110" t="str">
         <f t="shared" si="11"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0085-SHS.png</v>
       </c>
@@ -10606,37 +10611,37 @@
       <c r="A132" s="4" t="s">
         <v>337</v>
       </c>
-      <c r="B132" s="53" t="s">
+      <c r="B132" s="43" t="s">
         <v>338</v>
       </c>
       <c r="C132" s="3" t="s">
         <v>799</v>
       </c>
-      <c r="D132" s="151">
+      <c r="D132" s="121">
         <v>37257</v>
       </c>
-      <c r="E132" s="81">
+      <c r="E132" s="138">
         <v>210011054709</v>
       </c>
-      <c r="F132" s="85">
+      <c r="F132" s="158">
         <v>44946</v>
       </c>
-      <c r="G132" s="55" t="s">
+      <c r="G132" s="45" t="s">
         <v>903</v>
       </c>
-      <c r="H132" s="66" t="s">
+      <c r="H132" s="56" t="s">
         <v>97</v>
       </c>
-      <c r="I132" s="100" t="s">
+      <c r="I132" s="76" t="s">
         <v>494</v>
       </c>
-      <c r="J132" s="128" t="s">
+      <c r="J132" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K132" s="120" t="s">
+      <c r="K132" s="96" t="s">
         <v>605</v>
       </c>
-      <c r="L132" s="121" t="s">
+      <c r="L132" s="97" t="s">
         <v>619</v>
       </c>
       <c r="M132" t="s">
@@ -10646,7 +10651,7 @@
         <f t="shared" si="10"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0086-SHS.png</v>
       </c>
-      <c r="O132" s="136" t="str">
+      <c r="O132" s="110" t="str">
         <f t="shared" si="11"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0086-SHS.png</v>
       </c>
@@ -10658,35 +10663,35 @@
       <c r="A133" s="4" t="s">
         <v>339</v>
       </c>
-      <c r="B133" s="53"/>
+      <c r="B133" s="43"/>
       <c r="C133" s="3" t="s">
         <v>798</v>
       </c>
-      <c r="D133" s="151">
+      <c r="D133" s="121">
         <v>37622</v>
       </c>
-      <c r="E133" s="81">
+      <c r="E133" s="138">
         <v>213151003530</v>
       </c>
-      <c r="F133" s="85">
+      <c r="F133" s="158">
         <v>44978</v>
       </c>
-      <c r="G133" s="55" t="s">
+      <c r="G133" s="45" t="s">
         <v>82</v>
       </c>
-      <c r="H133" s="65" t="s">
+      <c r="H133" s="55" t="s">
         <v>87</v>
       </c>
-      <c r="I133" s="100" t="s">
+      <c r="I133" s="76" t="s">
         <v>495</v>
       </c>
-      <c r="J133" s="128" t="s">
+      <c r="J133" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K133" s="120" t="s">
+      <c r="K133" s="96" t="s">
         <v>605</v>
       </c>
-      <c r="L133" s="121" t="s">
+      <c r="L133" s="97" t="s">
         <v>620</v>
       </c>
       <c r="M133" t="s">
@@ -10696,7 +10701,7 @@
         <f t="shared" si="10"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0087-SHS.png</v>
       </c>
-      <c r="O133" s="136" t="str">
+      <c r="O133" s="110" t="str">
         <f t="shared" si="11"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0087-SHS.png</v>
       </c>
@@ -10708,37 +10713,37 @@
       <c r="A134" s="4" t="s">
         <v>340</v>
       </c>
-      <c r="B134" s="53" t="s">
+      <c r="B134" s="43" t="s">
         <v>341</v>
       </c>
       <c r="C134" s="3" t="s">
         <v>797</v>
       </c>
-      <c r="D134" s="61">
+      <c r="D134" s="51">
         <v>37779</v>
       </c>
-      <c r="E134" s="81">
+      <c r="E134" s="138">
         <v>213012037498</v>
       </c>
-      <c r="F134" s="85">
+      <c r="F134" s="158">
         <v>44552</v>
       </c>
-      <c r="G134" s="55" t="s">
+      <c r="G134" s="45" t="s">
         <v>82</v>
       </c>
-      <c r="H134" s="66" t="s">
+      <c r="H134" s="56" t="s">
         <v>93</v>
       </c>
-      <c r="I134" s="100" t="s">
+      <c r="I134" s="76" t="s">
         <v>496</v>
       </c>
-      <c r="J134" s="128" t="s">
+      <c r="J134" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K134" s="120" t="s">
+      <c r="K134" s="96" t="s">
         <v>605</v>
       </c>
-      <c r="L134" s="121" t="s">
+      <c r="L134" s="97" t="s">
         <v>621</v>
       </c>
       <c r="M134" t="s">
@@ -10748,7 +10753,7 @@
         <f t="shared" si="10"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0088-SHS.png</v>
       </c>
-      <c r="O134" s="136" t="str">
+      <c r="O134" s="110" t="str">
         <f t="shared" si="11"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0088-SHS.png</v>
       </c>
@@ -10760,37 +10765,37 @@
       <c r="A135" s="4" t="s">
         <v>342</v>
       </c>
-      <c r="B135" s="53" t="s">
+      <c r="B135" s="43" t="s">
         <v>343</v>
       </c>
       <c r="C135" s="3" t="s">
         <v>796</v>
       </c>
-      <c r="D135" s="157">
+      <c r="D135" s="124">
         <v>36892</v>
       </c>
-      <c r="E135" s="81">
+      <c r="E135" s="138">
         <v>213111004326</v>
       </c>
-      <c r="F135" s="86">
+      <c r="F135" s="159">
         <v>44055</v>
       </c>
-      <c r="G135" s="87" t="s">
+      <c r="G135" s="67" t="s">
         <v>82</v>
       </c>
-      <c r="H135" s="65" t="s">
+      <c r="H135" s="55" t="s">
         <v>497</v>
       </c>
-      <c r="I135" s="100" t="s">
+      <c r="I135" s="76" t="s">
         <v>498</v>
       </c>
-      <c r="J135" s="128" t="s">
+      <c r="J135" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K135" s="120" t="s">
+      <c r="K135" s="96" t="s">
         <v>605</v>
       </c>
-      <c r="L135" s="121" t="s">
+      <c r="L135" s="97" t="s">
         <v>622</v>
       </c>
       <c r="M135" t="s">
@@ -10800,7 +10805,7 @@
         <f t="shared" si="10"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0089-SHS.png</v>
       </c>
-      <c r="O135" s="136" t="str">
+      <c r="O135" s="110" t="str">
         <f t="shared" si="11"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0089-SHS.png</v>
       </c>
@@ -10812,37 +10817,37 @@
       <c r="A136" s="4" t="s">
         <v>344</v>
       </c>
-      <c r="B136" s="53" t="s">
+      <c r="B136" s="43" t="s">
         <v>345</v>
       </c>
       <c r="C136" s="3" t="s">
         <v>795</v>
       </c>
-      <c r="D136" s="151">
+      <c r="D136" s="121">
         <v>38353</v>
       </c>
-      <c r="E136" s="81">
+      <c r="E136" s="138">
         <v>213491009575</v>
       </c>
-      <c r="F136" s="85">
+      <c r="F136" s="158">
         <v>44966</v>
       </c>
-      <c r="G136" s="55" t="s">
+      <c r="G136" s="45" t="s">
         <v>82</v>
       </c>
-      <c r="H136" s="66" t="s">
+      <c r="H136" s="56" t="s">
         <v>431</v>
       </c>
-      <c r="I136" s="100" t="s">
+      <c r="I136" s="76" t="s">
         <v>499</v>
       </c>
-      <c r="J136" s="128" t="s">
+      <c r="J136" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K136" s="120" t="s">
+      <c r="K136" s="96" t="s">
         <v>605</v>
       </c>
-      <c r="L136" s="121" t="s">
+      <c r="L136" s="97" t="s">
         <v>623</v>
       </c>
       <c r="M136" t="s">
@@ -10852,7 +10857,7 @@
         <f t="shared" si="10"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0090-SHS.png</v>
       </c>
-      <c r="O136" s="136" t="str">
+      <c r="O136" s="110" t="str">
         <f t="shared" si="11"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0090-SHS.png</v>
       </c>
@@ -10864,37 +10869,37 @@
       <c r="A137" s="4" t="s">
         <v>346</v>
       </c>
-      <c r="B137" s="53" t="s">
+      <c r="B137" s="43" t="s">
         <v>347</v>
       </c>
       <c r="C137" s="3" t="s">
         <v>794</v>
       </c>
-      <c r="D137" s="61">
+      <c r="D137" s="51">
         <v>36998</v>
       </c>
-      <c r="E137" s="81">
+      <c r="E137" s="138">
         <v>213012036258</v>
       </c>
-      <c r="F137" s="85">
+      <c r="F137" s="158">
         <v>44209</v>
       </c>
-      <c r="G137" s="55" t="s">
+      <c r="G137" s="45" t="s">
         <v>82</v>
       </c>
-      <c r="H137" s="66" t="s">
+      <c r="H137" s="56" t="s">
         <v>500</v>
       </c>
-      <c r="I137" s="100" t="s">
+      <c r="I137" s="76" t="s">
         <v>501</v>
       </c>
-      <c r="J137" s="128" t="s">
+      <c r="J137" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K137" s="120" t="s">
+      <c r="K137" s="96" t="s">
         <v>605</v>
       </c>
-      <c r="L137" s="121" t="s">
+      <c r="L137" s="97" t="s">
         <v>624</v>
       </c>
       <c r="M137" t="s">
@@ -10904,7 +10909,7 @@
         <f t="shared" si="10"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0091-SHS.png</v>
       </c>
-      <c r="O137" s="136" t="str">
+      <c r="O137" s="110" t="str">
         <f t="shared" si="11"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0091-SHS.png</v>
       </c>
@@ -10916,35 +10921,35 @@
       <c r="A138" s="4" t="s">
         <v>348</v>
       </c>
-      <c r="B138" s="53"/>
+      <c r="B138" s="43"/>
       <c r="C138" s="3" t="s">
         <v>793</v>
       </c>
-      <c r="D138" s="61">
+      <c r="D138" s="51">
         <v>37585</v>
       </c>
-      <c r="E138" s="81">
+      <c r="E138" s="138">
         <v>217012017616</v>
       </c>
-      <c r="F138" s="85">
+      <c r="F138" s="158">
         <v>44281</v>
       </c>
-      <c r="G138" s="55" t="s">
+      <c r="G138" s="45" t="s">
         <v>84</v>
       </c>
-      <c r="H138" s="66" t="s">
+      <c r="H138" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="I138" s="100" t="s">
+      <c r="I138" s="76" t="s">
         <v>502</v>
       </c>
-      <c r="J138" s="128" t="s">
+      <c r="J138" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K138" s="120" t="s">
+      <c r="K138" s="96" t="s">
         <v>605</v>
       </c>
-      <c r="L138" s="121" t="s">
+      <c r="L138" s="97" t="s">
         <v>625</v>
       </c>
       <c r="M138" t="s">
@@ -10954,7 +10959,7 @@
         <f t="shared" si="10"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0092-SHS.png</v>
       </c>
-      <c r="O138" s="136" t="str">
+      <c r="O138" s="110" t="str">
         <f t="shared" si="11"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0092-SHS.png</v>
       </c>
@@ -10966,37 +10971,37 @@
       <c r="A139" s="4" t="s">
         <v>349</v>
       </c>
-      <c r="B139" s="53" t="s">
+      <c r="B139" s="43" t="s">
         <v>350</v>
       </c>
       <c r="C139" s="3" t="s">
         <v>792</v>
       </c>
-      <c r="D139" s="61">
+      <c r="D139" s="51">
         <v>36543</v>
       </c>
-      <c r="E139" s="81">
+      <c r="E139" s="138">
         <v>213012037529</v>
       </c>
-      <c r="F139" s="85">
+      <c r="F139" s="158">
         <v>44553</v>
       </c>
-      <c r="G139" s="55" t="s">
+      <c r="G139" s="45" t="s">
         <v>82</v>
       </c>
-      <c r="H139" s="66" t="s">
+      <c r="H139" s="56" t="s">
         <v>503</v>
       </c>
-      <c r="I139" s="100" t="s">
+      <c r="I139" s="76" t="s">
         <v>504</v>
       </c>
-      <c r="J139" s="128" t="s">
+      <c r="J139" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K139" s="120" t="s">
+      <c r="K139" s="96" t="s">
         <v>605</v>
       </c>
-      <c r="L139" s="123" t="s">
+      <c r="L139" s="99" t="s">
         <v>626</v>
       </c>
       <c r="M139" t="s">
@@ -11006,7 +11011,7 @@
         <f t="shared" si="10"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0093-SHS.png</v>
       </c>
-      <c r="O139" s="136" t="str">
+      <c r="O139" s="110" t="str">
         <f t="shared" si="11"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0093-SHS.png</v>
       </c>
@@ -11018,35 +11023,35 @@
       <c r="A140" s="8" t="s">
         <v>351</v>
       </c>
-      <c r="B140" s="55"/>
+      <c r="B140" s="45"/>
       <c r="C140" s="3" t="s">
         <v>791</v>
       </c>
-      <c r="D140" s="143">
+      <c r="D140" s="117">
         <v>36161</v>
       </c>
-      <c r="E140" s="81">
+      <c r="E140" s="138">
         <v>213231002841</v>
       </c>
-      <c r="F140" s="85">
+      <c r="F140" s="158">
         <v>42896</v>
       </c>
-      <c r="G140" s="55" t="s">
+      <c r="G140" s="45" t="s">
         <v>82</v>
       </c>
-      <c r="H140" s="67" t="s">
+      <c r="H140" s="57" t="s">
         <v>431</v>
       </c>
-      <c r="I140" s="102" t="s">
+      <c r="I140" s="78" t="s">
         <v>505</v>
       </c>
-      <c r="J140" s="128" t="s">
+      <c r="J140" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K140" s="120" t="s">
+      <c r="K140" s="96" t="s">
         <v>605</v>
       </c>
-      <c r="L140" s="124" t="s">
+      <c r="L140" s="100" t="s">
         <v>627</v>
       </c>
       <c r="M140" t="s">
@@ -11056,7 +11061,7 @@
         <f t="shared" si="10"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0094-SHS.png</v>
       </c>
-      <c r="O140" s="136" t="str">
+      <c r="O140" s="110" t="str">
         <f t="shared" si="11"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0094-SHS.png</v>
       </c>
@@ -11068,37 +11073,37 @@
       <c r="A141" s="8" t="s">
         <v>352</v>
       </c>
-      <c r="B141" s="55" t="s">
+      <c r="B141" s="45" t="s">
         <v>353</v>
       </c>
       <c r="C141" s="3" t="s">
         <v>790</v>
       </c>
-      <c r="D141" s="68">
+      <c r="D141" s="58">
         <v>37012</v>
       </c>
-      <c r="E141" s="81">
+      <c r="E141" s="138">
         <v>213012035890</v>
       </c>
-      <c r="F141" s="85">
+      <c r="F141" s="158">
         <v>44109</v>
       </c>
-      <c r="G141" s="55" t="s">
+      <c r="G141" s="45" t="s">
         <v>82</v>
       </c>
-      <c r="H141" s="67" t="s">
+      <c r="H141" s="57" t="s">
         <v>98</v>
       </c>
-      <c r="I141" s="102" t="s">
+      <c r="I141" s="78" t="s">
         <v>506</v>
       </c>
-      <c r="J141" s="128" t="s">
+      <c r="J141" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K141" s="120" t="s">
+      <c r="K141" s="96" t="s">
         <v>605</v>
       </c>
-      <c r="L141" s="124" t="s">
+      <c r="L141" s="100" t="s">
         <v>628</v>
       </c>
       <c r="M141" t="s">
@@ -11108,7 +11113,7 @@
         <f t="shared" si="10"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0095-SHS.png</v>
       </c>
-      <c r="O141" s="136" t="str">
+      <c r="O141" s="110" t="str">
         <f t="shared" si="11"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0095-SHS.png</v>
       </c>
@@ -11117,7 +11122,7 @@
       </c>
     </row>
     <row r="142" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A142" s="49" t="s">
+      <c r="A142" s="39" t="s">
         <v>354</v>
       </c>
       <c r="B142" s="9" t="s">
@@ -11129,28 +11134,28 @@
       <c r="D142" s="13">
         <v>35466</v>
       </c>
-      <c r="E142" s="88">
+      <c r="E142" s="140">
         <v>213011030478</v>
       </c>
-      <c r="F142" s="72">
+      <c r="F142" s="145">
         <v>42796</v>
       </c>
-      <c r="G142" s="55" t="s">
+      <c r="G142" s="45" t="s">
         <v>82</v>
       </c>
       <c r="H142" s="14" t="s">
         <v>507</v>
       </c>
-      <c r="I142" s="34" t="s">
+      <c r="I142" s="24" t="s">
         <v>508</v>
       </c>
-      <c r="J142" s="128" t="s">
+      <c r="J142" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K142" s="120" t="s">
+      <c r="K142" s="96" t="s">
         <v>605</v>
       </c>
-      <c r="L142" s="125" t="s">
+      <c r="L142" s="101" t="s">
         <v>629</v>
       </c>
       <c r="M142" t="s">
@@ -11160,7 +11165,7 @@
         <f t="shared" si="10"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0096-SHS.png</v>
       </c>
-      <c r="O142" s="136" t="str">
+      <c r="O142" s="110" t="str">
         <f t="shared" si="11"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0096-SHS.png</v>
       </c>
@@ -11169,40 +11174,40 @@
       </c>
     </row>
     <row r="143" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A143" s="49" t="s">
+      <c r="A143" s="39" t="s">
         <v>356</v>
       </c>
-      <c r="B143" s="55" t="s">
+      <c r="B143" s="45" t="s">
         <v>357</v>
       </c>
       <c r="C143" s="3" t="s">
         <v>788</v>
       </c>
-      <c r="D143" s="68">
+      <c r="D143" s="58">
         <v>38924</v>
       </c>
-      <c r="E143" s="81">
+      <c r="E143" s="138">
         <v>213011042935</v>
       </c>
-      <c r="F143" s="85">
+      <c r="F143" s="158">
         <v>45517</v>
       </c>
-      <c r="G143" s="55" t="s">
+      <c r="G143" s="45" t="s">
         <v>82</v>
       </c>
-      <c r="H143" s="67" t="s">
+      <c r="H143" s="57" t="s">
         <v>89</v>
       </c>
-      <c r="I143" s="102" t="s">
+      <c r="I143" s="78" t="s">
         <v>509</v>
       </c>
-      <c r="J143" s="128" t="s">
+      <c r="J143" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K143" s="120" t="s">
+      <c r="K143" s="96" t="s">
         <v>605</v>
       </c>
-      <c r="L143" s="124" t="s">
+      <c r="L143" s="100" t="s">
         <v>630</v>
       </c>
       <c r="M143" t="s">
@@ -11212,7 +11217,7 @@
         <f t="shared" si="10"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0097-SHS.png</v>
       </c>
-      <c r="O143" s="136" t="str">
+      <c r="O143" s="110" t="str">
         <f t="shared" si="11"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0097-SHS.png</v>
       </c>
@@ -11221,40 +11226,40 @@
       </c>
     </row>
     <row r="144" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A144" s="49" t="s">
+      <c r="A144" s="39" t="s">
         <v>358</v>
       </c>
-      <c r="B144" s="55" t="s">
+      <c r="B144" s="45" t="s">
         <v>359</v>
       </c>
       <c r="C144" s="3" t="s">
         <v>787</v>
       </c>
-      <c r="D144" s="143">
+      <c r="D144" s="117">
         <v>30803</v>
       </c>
-      <c r="E144" s="81" t="s">
+      <c r="E144" s="138" t="s">
         <v>393</v>
       </c>
-      <c r="F144" s="85">
+      <c r="F144" s="158">
         <v>38216</v>
       </c>
-      <c r="G144" s="55" t="s">
+      <c r="G144" s="45" t="s">
         <v>82</v>
       </c>
-      <c r="H144" s="67" t="s">
+      <c r="H144" s="57" t="s">
         <v>497</v>
       </c>
-      <c r="I144" s="102" t="s">
+      <c r="I144" s="78" t="s">
         <v>510</v>
       </c>
-      <c r="J144" s="128" t="s">
+      <c r="J144" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K144" s="120" t="s">
+      <c r="K144" s="96" t="s">
         <v>605</v>
       </c>
-      <c r="L144" s="124" t="s">
+      <c r="L144" s="100" t="s">
         <v>631</v>
       </c>
       <c r="M144" t="s">
@@ -11264,7 +11269,7 @@
         <f t="shared" si="10"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0098-SHS.png</v>
       </c>
-      <c r="O144" s="136" t="str">
+      <c r="O144" s="110" t="str">
         <f t="shared" si="11"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0098-SHS.png</v>
       </c>
@@ -11273,40 +11278,40 @@
       </c>
     </row>
     <row r="145" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A145" s="49" t="s">
+      <c r="A145" s="39" t="s">
         <v>360</v>
       </c>
-      <c r="B145" s="55" t="s">
+      <c r="B145" s="45" t="s">
         <v>361</v>
       </c>
       <c r="C145" s="3" t="s">
         <v>786</v>
       </c>
-      <c r="D145" s="68">
+      <c r="D145" s="58">
         <v>38888</v>
       </c>
-      <c r="E145" s="81">
+      <c r="E145" s="138">
         <v>213052010658</v>
       </c>
-      <c r="F145" s="85">
+      <c r="F145" s="158">
         <v>45482</v>
       </c>
-      <c r="G145" s="55" t="s">
+      <c r="G145" s="45" t="s">
         <v>82</v>
       </c>
-      <c r="H145" s="67" t="s">
+      <c r="H145" s="57" t="s">
         <v>92</v>
       </c>
-      <c r="I145" s="102" t="s">
+      <c r="I145" s="78" t="s">
         <v>511</v>
       </c>
-      <c r="J145" s="128" t="s">
+      <c r="J145" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K145" s="120" t="s">
+      <c r="K145" s="96" t="s">
         <v>605</v>
       </c>
-      <c r="L145" s="124" t="s">
+      <c r="L145" s="100" t="s">
         <v>632</v>
       </c>
       <c r="M145" t="s">
@@ -11316,7 +11321,7 @@
         <f t="shared" si="10"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0099-SHS.png</v>
       </c>
-      <c r="O145" s="136" t="str">
+      <c r="O145" s="110" t="str">
         <f t="shared" si="11"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0099-SHS.png</v>
       </c>
@@ -11328,37 +11333,37 @@
       <c r="A146" s="8" t="s">
         <v>272</v>
       </c>
-      <c r="B146" s="140" t="s">
+      <c r="B146" s="114" t="s">
         <v>721</v>
       </c>
       <c r="C146" s="3" t="s">
         <v>785</v>
       </c>
-      <c r="D146" s="68">
+      <c r="D146" s="58">
         <v>38840</v>
       </c>
-      <c r="E146" s="81">
+      <c r="E146" s="138">
         <v>214012118931</v>
       </c>
-      <c r="F146" s="85">
+      <c r="F146" s="158">
         <v>45426</v>
       </c>
-      <c r="G146" s="55" t="s">
+      <c r="G146" s="45" t="s">
         <v>83</v>
       </c>
-      <c r="H146" s="67" t="s">
+      <c r="H146" s="57" t="s">
         <v>100</v>
       </c>
-      <c r="I146" s="102" t="s">
+      <c r="I146" s="78" t="s">
         <v>512</v>
       </c>
-      <c r="J146" s="128" t="s">
+      <c r="J146" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K146" s="120" t="s">
+      <c r="K146" s="96" t="s">
         <v>605</v>
       </c>
-      <c r="L146" s="126" t="s">
+      <c r="L146" s="102" t="s">
         <v>633</v>
       </c>
       <c r="M146" t="s">
@@ -11368,7 +11373,7 @@
         <f t="shared" si="10"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0100-SHS.png</v>
       </c>
-      <c r="O146" s="136" t="str">
+      <c r="O146" s="110" t="str">
         <f t="shared" si="11"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0100-SHS.png</v>
       </c>
@@ -11380,37 +11385,37 @@
       <c r="A147" s="8" t="s">
         <v>362</v>
       </c>
-      <c r="B147" s="55" t="s">
+      <c r="B147" s="45" t="s">
         <v>363</v>
       </c>
       <c r="C147" s="3" t="s">
         <v>784</v>
       </c>
-      <c r="D147" s="68">
+      <c r="D147" s="58">
         <v>38381</v>
       </c>
-      <c r="E147" s="81">
+      <c r="E147" s="138">
         <v>214012117454</v>
       </c>
-      <c r="F147" s="85">
+      <c r="F147" s="158">
         <v>44988</v>
       </c>
-      <c r="G147" s="55" t="s">
+      <c r="G147" s="45" t="s">
         <v>83</v>
       </c>
-      <c r="H147" s="67" t="s">
+      <c r="H147" s="57" t="s">
         <v>86</v>
       </c>
-      <c r="I147" s="102" t="s">
+      <c r="I147" s="78" t="s">
         <v>513</v>
       </c>
-      <c r="J147" s="128" t="s">
+      <c r="J147" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K147" s="120" t="s">
+      <c r="K147" s="96" t="s">
         <v>605</v>
       </c>
-      <c r="L147" s="124" t="s">
+      <c r="L147" s="100" t="s">
         <v>634</v>
       </c>
       <c r="M147" t="s">
@@ -11420,7 +11425,7 @@
         <f t="shared" si="10"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0101-SHS.png</v>
       </c>
-      <c r="O147" s="136" t="str">
+      <c r="O147" s="110" t="str">
         <f t="shared" si="11"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0101-SHS.png</v>
       </c>
@@ -11432,37 +11437,37 @@
       <c r="A148" s="8" t="s">
         <v>364</v>
       </c>
-      <c r="B148" s="55" t="s">
+      <c r="B148" s="45" t="s">
         <v>365</v>
       </c>
       <c r="C148" s="3" t="s">
         <v>783</v>
       </c>
-      <c r="D148" s="69">
+      <c r="D148" s="59">
         <v>37359</v>
       </c>
-      <c r="E148" s="81">
+      <c r="E148" s="138">
         <v>213011035620</v>
       </c>
-      <c r="F148" s="89">
+      <c r="F148" s="160">
         <v>44035</v>
       </c>
-      <c r="G148" s="90" t="s">
+      <c r="G148" s="69" t="s">
         <v>82</v>
       </c>
-      <c r="H148" s="103" t="s">
+      <c r="H148" s="79" t="s">
         <v>503</v>
       </c>
-      <c r="I148" s="102" t="s">
+      <c r="I148" s="78" t="s">
         <v>514</v>
       </c>
-      <c r="J148" s="128" t="s">
+      <c r="J148" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K148" s="120" t="s">
+      <c r="K148" s="96" t="s">
         <v>605</v>
       </c>
-      <c r="L148" s="124" t="s">
+      <c r="L148" s="100" t="s">
         <v>569</v>
       </c>
       <c r="M148" t="s">
@@ -11472,7 +11477,7 @@
         <f t="shared" si="10"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0102-SHS.png</v>
       </c>
-      <c r="O148" s="136" t="str">
+      <c r="O148" s="110" t="str">
         <f t="shared" si="11"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0102-SHS.png</v>
       </c>
@@ -11484,37 +11489,37 @@
       <c r="A149" s="8" t="s">
         <v>366</v>
       </c>
-      <c r="B149" s="55" t="s">
+      <c r="B149" s="45" t="s">
         <v>367</v>
       </c>
       <c r="C149" s="3" t="s">
         <v>782</v>
       </c>
-      <c r="D149" s="69">
+      <c r="D149" s="59">
         <v>35257</v>
       </c>
-      <c r="E149" s="81">
+      <c r="E149" s="138">
         <v>217011016100</v>
       </c>
-      <c r="F149" s="86">
+      <c r="F149" s="159">
         <v>43559</v>
       </c>
-      <c r="G149" s="87" t="s">
+      <c r="G149" s="67" t="s">
         <v>82</v>
       </c>
-      <c r="H149" s="103" t="s">
+      <c r="H149" s="79" t="s">
         <v>431</v>
       </c>
-      <c r="I149" s="102" t="s">
+      <c r="I149" s="78" t="s">
         <v>515</v>
       </c>
-      <c r="J149" s="128" t="s">
+      <c r="J149" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K149" s="120" t="s">
+      <c r="K149" s="96" t="s">
         <v>605</v>
       </c>
-      <c r="L149" s="124" t="s">
+      <c r="L149" s="100" t="s">
         <v>635</v>
       </c>
       <c r="M149" t="s">
@@ -11524,7 +11529,7 @@
         <f t="shared" si="10"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0103-SHS.png</v>
       </c>
-      <c r="O149" s="136" t="str">
+      <c r="O149" s="110" t="str">
         <f t="shared" si="11"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0103-SHS.png</v>
       </c>
@@ -11536,37 +11541,37 @@
       <c r="A150" s="8" t="s">
         <v>368</v>
       </c>
-      <c r="B150" s="55" t="s">
+      <c r="B150" s="45" t="s">
         <v>369</v>
       </c>
       <c r="C150" s="3" t="s">
         <v>781</v>
       </c>
-      <c r="D150" s="68">
+      <c r="D150" s="58">
         <v>37265</v>
       </c>
-      <c r="E150" s="81">
+      <c r="E150" s="138">
         <v>213011035029</v>
       </c>
-      <c r="F150" s="85">
+      <c r="F150" s="158">
         <v>43880</v>
       </c>
-      <c r="G150" s="55" t="s">
+      <c r="G150" s="45" t="s">
         <v>82</v>
       </c>
-      <c r="H150" s="103" t="s">
+      <c r="H150" s="79" t="s">
         <v>87</v>
       </c>
-      <c r="I150" s="102" t="s">
+      <c r="I150" s="78" t="s">
         <v>516</v>
       </c>
-      <c r="J150" s="128" t="s">
+      <c r="J150" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K150" s="120" t="s">
+      <c r="K150" s="96" t="s">
         <v>605</v>
       </c>
-      <c r="L150" s="124" t="s">
+      <c r="L150" s="100" t="s">
         <v>636</v>
       </c>
       <c r="M150" t="s">
@@ -11576,7 +11581,7 @@
         <f t="shared" si="10"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0104-SHS.png</v>
       </c>
-      <c r="O150" s="136" t="str">
+      <c r="O150" s="110" t="str">
         <f t="shared" si="11"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0104-SHS.png</v>
       </c>
@@ -11588,35 +11593,35 @@
       <c r="A151" s="8" t="s">
         <v>370</v>
       </c>
-      <c r="B151" s="55"/>
+      <c r="B151" s="45"/>
       <c r="C151" s="3" t="s">
         <v>780</v>
       </c>
-      <c r="D151" s="68">
+      <c r="D151" s="58">
         <v>37018</v>
       </c>
-      <c r="E151" s="81">
+      <c r="E151" s="138">
         <v>213291003505</v>
       </c>
-      <c r="F151" s="85">
+      <c r="F151" s="158">
         <v>44810</v>
       </c>
-      <c r="G151" s="55" t="s">
+      <c r="G151" s="45" t="s">
         <v>82</v>
       </c>
-      <c r="H151" s="67" t="s">
+      <c r="H151" s="57" t="s">
         <v>517</v>
       </c>
-      <c r="I151" s="102" t="s">
+      <c r="I151" s="78" t="s">
         <v>518</v>
       </c>
-      <c r="J151" s="128" t="s">
+      <c r="J151" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K151" s="120" t="s">
+      <c r="K151" s="96" t="s">
         <v>605</v>
       </c>
-      <c r="L151" s="124" t="s">
+      <c r="L151" s="100" t="s">
         <v>637</v>
       </c>
       <c r="M151" t="s">
@@ -11626,7 +11631,7 @@
         <f t="shared" si="10"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0105-SHS.png</v>
       </c>
-      <c r="O151" s="136" t="str">
+      <c r="O151" s="110" t="str">
         <f t="shared" si="11"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0105-SHS.png</v>
       </c>
@@ -11638,37 +11643,37 @@
       <c r="A152" s="8" t="s">
         <v>371</v>
       </c>
-      <c r="B152" s="55" t="s">
+      <c r="B152" s="45" t="s">
         <v>372</v>
       </c>
       <c r="C152" s="3" t="s">
         <v>779</v>
       </c>
-      <c r="D152" s="68">
+      <c r="D152" s="58">
         <v>39290</v>
       </c>
-      <c r="E152" s="81">
+      <c r="E152" s="138">
         <v>213012044433</v>
       </c>
-      <c r="F152" s="85">
+      <c r="F152" s="158">
         <v>45866</v>
       </c>
-      <c r="G152" s="55" t="s">
+      <c r="G152" s="45" t="s">
         <v>82</v>
       </c>
-      <c r="H152" s="67" t="s">
+      <c r="H152" s="57" t="s">
         <v>92</v>
       </c>
-      <c r="I152" s="102" t="s">
+      <c r="I152" s="78" t="s">
         <v>519</v>
       </c>
-      <c r="J152" s="128" t="s">
+      <c r="J152" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K152" s="120" t="s">
+      <c r="K152" s="96" t="s">
         <v>605</v>
       </c>
-      <c r="L152" s="124" t="s">
+      <c r="L152" s="100" t="s">
         <v>554</v>
       </c>
       <c r="M152" t="s">
@@ -11678,7 +11683,7 @@
         <f t="shared" si="10"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0106-SHS.png</v>
       </c>
-      <c r="O152" s="136" t="str">
+      <c r="O152" s="110" t="str">
         <f t="shared" si="11"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0106-SHS.png</v>
       </c>
@@ -11690,37 +11695,37 @@
       <c r="A153" s="8" t="s">
         <v>373</v>
       </c>
-      <c r="B153" s="56" t="s">
+      <c r="B153" s="46" t="s">
         <v>374</v>
       </c>
       <c r="C153" s="3" t="s">
         <v>778</v>
       </c>
-      <c r="D153" s="70">
+      <c r="D153" s="60">
         <v>38716</v>
       </c>
-      <c r="E153" s="91">
+      <c r="E153" s="141">
         <v>216012034889</v>
       </c>
-      <c r="F153" s="92">
+      <c r="F153" s="161">
         <v>45295</v>
       </c>
-      <c r="G153" s="56" t="s">
+      <c r="G153" s="46" t="s">
         <v>905</v>
       </c>
-      <c r="H153" s="104" t="s">
+      <c r="H153" s="80" t="s">
         <v>92</v>
       </c>
-      <c r="I153" s="105" t="s">
+      <c r="I153" s="81" t="s">
         <v>520</v>
       </c>
-      <c r="J153" s="128" t="s">
+      <c r="J153" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K153" s="120" t="s">
+      <c r="K153" s="96" t="s">
         <v>605</v>
       </c>
-      <c r="L153" s="127" t="s">
+      <c r="L153" s="103" t="s">
         <v>638</v>
       </c>
       <c r="M153" t="s">
@@ -11730,7 +11735,7 @@
         <f t="shared" si="10"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0107-SHS.png</v>
       </c>
-      <c r="O153" s="136" t="str">
+      <c r="O153" s="110" t="str">
         <f t="shared" si="11"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0107-SHS.png</v>
       </c>
@@ -11742,37 +11747,37 @@
       <c r="A154" s="8" t="s">
         <v>375</v>
       </c>
-      <c r="B154" s="55" t="s">
+      <c r="B154" s="45" t="s">
         <v>376</v>
       </c>
       <c r="C154" s="3" t="s">
         <v>777</v>
       </c>
-      <c r="D154" s="68">
+      <c r="D154" s="58">
         <v>36006</v>
       </c>
-      <c r="E154" s="93">
+      <c r="E154" s="142">
         <v>213111004230</v>
       </c>
-      <c r="F154" s="85">
+      <c r="F154" s="158">
         <v>43622</v>
       </c>
-      <c r="G154" s="55" t="s">
+      <c r="G154" s="45" t="s">
         <v>82</v>
       </c>
-      <c r="H154" s="67" t="s">
+      <c r="H154" s="57" t="s">
         <v>93</v>
       </c>
-      <c r="I154" s="102" t="s">
+      <c r="I154" s="78" t="s">
         <v>521</v>
       </c>
-      <c r="J154" s="128" t="s">
+      <c r="J154" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K154" s="120" t="s">
+      <c r="K154" s="96" t="s">
         <v>605</v>
       </c>
-      <c r="L154" s="124" t="s">
+      <c r="L154" s="100" t="s">
         <v>639</v>
       </c>
       <c r="M154" t="s">
@@ -11782,7 +11787,7 @@
         <f t="shared" si="10"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0108-SHS.png</v>
       </c>
-      <c r="O154" s="136" t="str">
+      <c r="O154" s="110" t="str">
         <f t="shared" si="11"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0108-SHS.png</v>
       </c>
@@ -11794,35 +11799,35 @@
       <c r="A155" s="8" t="s">
         <v>377</v>
       </c>
-      <c r="B155" s="55"/>
+      <c r="B155" s="45"/>
       <c r="C155" s="3" t="s">
         <v>776</v>
       </c>
-      <c r="D155" s="143">
+      <c r="D155" s="117">
         <v>37257</v>
       </c>
-      <c r="E155" s="93">
+      <c r="E155" s="142">
         <v>213571008476</v>
       </c>
-      <c r="F155" s="85">
+      <c r="F155" s="158">
         <v>44697</v>
       </c>
-      <c r="G155" s="55" t="s">
+      <c r="G155" s="45" t="s">
         <v>82</v>
       </c>
-      <c r="H155" s="67" t="s">
+      <c r="H155" s="57" t="s">
         <v>394</v>
       </c>
-      <c r="I155" s="102" t="s">
+      <c r="I155" s="78" t="s">
         <v>522</v>
       </c>
-      <c r="J155" s="128" t="s">
+      <c r="J155" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K155" s="120" t="s">
+      <c r="K155" s="96" t="s">
         <v>605</v>
       </c>
-      <c r="L155" s="124" t="s">
+      <c r="L155" s="100" t="s">
         <v>640</v>
       </c>
       <c r="M155" t="s">
@@ -11832,7 +11837,7 @@
         <f t="shared" si="10"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0109-SHS.png</v>
       </c>
-      <c r="O155" s="136" t="str">
+      <c r="O155" s="110" t="str">
         <f t="shared" si="11"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0109-SHS.png</v>
       </c>
@@ -11844,37 +11849,37 @@
       <c r="A156" s="8" t="s">
         <v>285</v>
       </c>
-      <c r="B156" s="55" t="s">
+      <c r="B156" s="45" t="s">
         <v>378</v>
       </c>
       <c r="C156" s="3" t="s">
         <v>775</v>
       </c>
-      <c r="D156" s="68">
+      <c r="D156" s="58">
         <v>38139</v>
       </c>
-      <c r="E156" s="93">
+      <c r="E156" s="142">
         <v>213571008632</v>
       </c>
-      <c r="F156" s="85">
+      <c r="F156" s="158">
         <v>44750</v>
       </c>
-      <c r="G156" s="55" t="s">
+      <c r="G156" s="45" t="s">
         <v>82</v>
       </c>
-      <c r="H156" s="67" t="s">
+      <c r="H156" s="57" t="s">
         <v>97</v>
       </c>
-      <c r="I156" s="102" t="s">
+      <c r="I156" s="78" t="s">
         <v>523</v>
       </c>
-      <c r="J156" s="128" t="s">
+      <c r="J156" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K156" s="120" t="s">
+      <c r="K156" s="96" t="s">
         <v>605</v>
       </c>
-      <c r="L156" s="124" t="s">
+      <c r="L156" s="100" t="s">
         <v>641</v>
       </c>
       <c r="M156" t="s">
@@ -11884,7 +11889,7 @@
         <f t="shared" si="10"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0110-SHS.png</v>
       </c>
-      <c r="O156" s="136" t="str">
+      <c r="O156" s="110" t="str">
         <f t="shared" si="11"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0110-SHS.png</v>
       </c>
@@ -11896,37 +11901,37 @@
       <c r="A157" s="8" t="s">
         <v>379</v>
       </c>
-      <c r="B157" s="55" t="s">
+      <c r="B157" s="45" t="s">
         <v>380</v>
       </c>
       <c r="C157" s="3" t="s">
         <v>774</v>
       </c>
-      <c r="D157" s="68">
+      <c r="D157" s="58">
         <v>37251</v>
       </c>
-      <c r="E157" s="93">
+      <c r="E157" s="142">
         <v>213372006836</v>
       </c>
-      <c r="F157" s="85">
+      <c r="F157" s="158">
         <v>43914</v>
       </c>
-      <c r="G157" s="55" t="s">
+      <c r="G157" s="45" t="s">
         <v>82</v>
       </c>
-      <c r="H157" s="67" t="s">
+      <c r="H157" s="57" t="s">
         <v>100</v>
       </c>
-      <c r="I157" s="102" t="s">
+      <c r="I157" s="78" t="s">
         <v>524</v>
       </c>
-      <c r="J157" s="128" t="s">
+      <c r="J157" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K157" s="120" t="s">
+      <c r="K157" s="96" t="s">
         <v>605</v>
       </c>
-      <c r="L157" s="124" t="s">
+      <c r="L157" s="100" t="s">
         <v>642</v>
       </c>
       <c r="M157" t="s">
@@ -11936,7 +11941,7 @@
         <f t="shared" si="10"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0111-SHS.png</v>
       </c>
-      <c r="O157" s="136" t="str">
+      <c r="O157" s="110" t="str">
         <f t="shared" si="11"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0111-SHS.png</v>
       </c>
@@ -11948,37 +11953,37 @@
       <c r="A158" s="8" t="s">
         <v>381</v>
       </c>
-      <c r="B158" s="55" t="s">
+      <c r="B158" s="45" t="s">
         <v>382</v>
       </c>
       <c r="C158" s="3" t="s">
         <v>773</v>
       </c>
-      <c r="D158" s="68">
+      <c r="D158" s="58">
         <v>38124</v>
       </c>
-      <c r="E158" s="93">
+      <c r="E158" s="142">
         <v>213011039879</v>
       </c>
-      <c r="F158" s="85">
+      <c r="F158" s="158">
         <v>44922</v>
       </c>
-      <c r="G158" s="55" t="s">
+      <c r="G158" s="45" t="s">
         <v>82</v>
       </c>
-      <c r="H158" s="67" t="s">
+      <c r="H158" s="57" t="s">
         <v>86</v>
       </c>
-      <c r="I158" s="102" t="s">
+      <c r="I158" s="78" t="s">
         <v>525</v>
       </c>
-      <c r="J158" s="128" t="s">
+      <c r="J158" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K158" s="120" t="s">
+      <c r="K158" s="96" t="s">
         <v>605</v>
       </c>
-      <c r="L158" s="124" t="s">
+      <c r="L158" s="100" t="s">
         <v>643</v>
       </c>
       <c r="M158" t="s">
@@ -11988,7 +11993,7 @@
         <f t="shared" si="10"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0112-SHS.png</v>
       </c>
-      <c r="O158" s="136" t="str">
+      <c r="O158" s="110" t="str">
         <f t="shared" si="11"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0112-SHS.png</v>
       </c>
@@ -12000,37 +12005,37 @@
       <c r="A159" s="8" t="s">
         <v>383</v>
       </c>
-      <c r="B159" s="55" t="s">
+      <c r="B159" s="45" t="s">
         <v>384</v>
       </c>
       <c r="C159" s="3" t="s">
         <v>772</v>
       </c>
-      <c r="D159" s="68">
+      <c r="D159" s="58">
         <v>38343</v>
       </c>
-      <c r="E159" s="93">
+      <c r="E159" s="142">
         <v>213012040029</v>
       </c>
-      <c r="F159" s="85">
+      <c r="F159" s="158">
         <v>44945</v>
       </c>
-      <c r="G159" s="55" t="s">
+      <c r="G159" s="45" t="s">
         <v>82</v>
       </c>
-      <c r="H159" s="67" t="s">
+      <c r="H159" s="57" t="s">
         <v>103</v>
       </c>
-      <c r="I159" s="102" t="s">
+      <c r="I159" s="78" t="s">
         <v>526</v>
       </c>
-      <c r="J159" s="128" t="s">
+      <c r="J159" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K159" s="120" t="s">
+      <c r="K159" s="96" t="s">
         <v>605</v>
       </c>
-      <c r="L159" s="124" t="s">
+      <c r="L159" s="100" t="s">
         <v>644</v>
       </c>
       <c r="M159" t="s">
@@ -12040,7 +12045,7 @@
         <f t="shared" si="10"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0113-SHS.png</v>
       </c>
-      <c r="O159" s="136" t="str">
+      <c r="O159" s="110" t="str">
         <f t="shared" si="11"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0113-SHS.png</v>
       </c>
@@ -12052,37 +12057,37 @@
       <c r="A160" s="8" t="s">
         <v>385</v>
       </c>
-      <c r="B160" s="140" t="s">
+      <c r="B160" s="114" t="s">
         <v>698</v>
       </c>
       <c r="C160" s="3" t="s">
         <v>771</v>
       </c>
-      <c r="D160" s="68">
+      <c r="D160" s="58">
         <v>35989</v>
       </c>
-      <c r="E160" s="93">
+      <c r="E160" s="142">
         <v>213012029650</v>
       </c>
-      <c r="F160" s="85">
+      <c r="F160" s="158">
         <v>42584</v>
       </c>
-      <c r="G160" s="55" t="s">
+      <c r="G160" s="45" t="s">
         <v>82</v>
       </c>
-      <c r="H160" s="67" t="s">
+      <c r="H160" s="57" t="s">
         <v>95</v>
       </c>
-      <c r="I160" s="102" t="s">
+      <c r="I160" s="78" t="s">
         <v>527</v>
       </c>
-      <c r="J160" s="128" t="s">
+      <c r="J160" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K160" s="120" t="s">
+      <c r="K160" s="96" t="s">
         <v>605</v>
       </c>
-      <c r="L160" s="124" t="s">
+      <c r="L160" s="100" t="s">
         <v>645</v>
       </c>
       <c r="M160" t="s">
@@ -12092,7 +12097,7 @@
         <f t="shared" si="10"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0114-SHS.png</v>
       </c>
-      <c r="O160" s="136" t="str">
+      <c r="O160" s="110" t="str">
         <f t="shared" si="11"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0114-SHS.png</v>
       </c>
@@ -12104,37 +12109,37 @@
       <c r="A161" s="8" t="s">
         <v>386</v>
       </c>
-      <c r="B161" s="55" t="s">
+      <c r="B161" s="45" t="s">
         <v>387</v>
       </c>
       <c r="C161" s="3" t="s">
         <v>770</v>
       </c>
-      <c r="D161" s="68">
+      <c r="D161" s="58">
         <v>38141</v>
       </c>
-      <c r="E161" s="93">
+      <c r="E161" s="142">
         <v>213012040356</v>
       </c>
-      <c r="F161" s="85">
+      <c r="F161" s="158">
         <v>44946</v>
       </c>
-      <c r="G161" s="55" t="s">
+      <c r="G161" s="45" t="s">
         <v>82</v>
       </c>
-      <c r="H161" s="67" t="s">
+      <c r="H161" s="57" t="s">
         <v>103</v>
       </c>
-      <c r="I161" s="102" t="s">
+      <c r="I161" s="78" t="s">
         <v>528</v>
       </c>
-      <c r="J161" s="128" t="s">
+      <c r="J161" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K161" s="120" t="s">
+      <c r="K161" s="96" t="s">
         <v>605</v>
       </c>
-      <c r="L161" s="124" t="s">
+      <c r="L161" s="100" t="s">
         <v>646</v>
       </c>
       <c r="M161" t="s">
@@ -12144,7 +12149,7 @@
         <f t="shared" si="10"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0115-SHS.png</v>
       </c>
-      <c r="O161" s="136" t="str">
+      <c r="O161" s="110" t="str">
         <f t="shared" si="11"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0115-SHS.png</v>
       </c>
@@ -12156,37 +12161,37 @@
       <c r="A162" s="8" t="s">
         <v>388</v>
       </c>
-      <c r="B162" s="55" t="s">
+      <c r="B162" s="45" t="s">
         <v>389</v>
       </c>
       <c r="C162" s="3" t="s">
         <v>769</v>
       </c>
-      <c r="D162" s="68">
+      <c r="D162" s="58">
         <v>36239</v>
       </c>
-      <c r="E162" s="93">
+      <c r="E162" s="142">
         <v>213011034309</v>
       </c>
-      <c r="F162" s="85">
+      <c r="F162" s="158">
         <v>43693</v>
       </c>
-      <c r="G162" s="55" t="s">
+      <c r="G162" s="45" t="s">
         <v>82</v>
       </c>
-      <c r="H162" s="67" t="s">
+      <c r="H162" s="57" t="s">
         <v>101</v>
       </c>
-      <c r="I162" s="102" t="s">
+      <c r="I162" s="78" t="s">
         <v>529</v>
       </c>
-      <c r="J162" s="128" t="s">
+      <c r="J162" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K162" s="120" t="s">
+      <c r="K162" s="96" t="s">
         <v>605</v>
       </c>
-      <c r="L162" s="124" t="s">
+      <c r="L162" s="100" t="s">
         <v>647</v>
       </c>
       <c r="M162" t="s">
@@ -12196,7 +12201,7 @@
         <f t="shared" si="10"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0116-SHS.png</v>
       </c>
-      <c r="O162" s="136" t="str">
+      <c r="O162" s="110" t="str">
         <f t="shared" si="11"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0116-SHS.png</v>
       </c>
@@ -12208,35 +12213,35 @@
       <c r="A163" s="8" t="s">
         <v>390</v>
       </c>
-      <c r="B163" s="55"/>
+      <c r="B163" s="45"/>
       <c r="C163" s="3" t="s">
         <v>768</v>
       </c>
-      <c r="D163" s="68">
+      <c r="D163" s="58">
         <v>37268</v>
       </c>
-      <c r="E163" s="93">
+      <c r="E163" s="142">
         <v>213012036833</v>
       </c>
-      <c r="F163" s="85">
+      <c r="F163" s="158">
         <v>44326</v>
       </c>
-      <c r="G163" s="55" t="s">
+      <c r="G163" s="45" t="s">
         <v>82</v>
       </c>
-      <c r="H163" s="67" t="s">
+      <c r="H163" s="57" t="s">
         <v>92</v>
       </c>
-      <c r="I163" s="102" t="s">
+      <c r="I163" s="78" t="s">
         <v>530</v>
       </c>
-      <c r="J163" s="128" t="s">
+      <c r="J163" s="104" t="s">
         <v>907</v>
       </c>
-      <c r="K163" s="120" t="s">
+      <c r="K163" s="96" t="s">
         <v>605</v>
       </c>
-      <c r="L163" s="124" t="s">
+      <c r="L163" s="100" t="s">
         <v>648</v>
       </c>
       <c r="M163" t="s">
@@ -12246,7 +12251,7 @@
         <f t="shared" si="10"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0117-SHS.png</v>
       </c>
-      <c r="O163" s="136" t="str">
+      <c r="O163" s="110" t="str">
         <f t="shared" si="11"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0117-SHS.png</v>
       </c>
@@ -12255,38 +12260,38 @@
       </c>
     </row>
     <row r="164" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A164" s="53" t="s">
+      <c r="A164" s="43" t="s">
         <v>649</v>
       </c>
-      <c r="B164" s="53"/>
+      <c r="B164" s="43"/>
       <c r="C164" s="3" t="s">
         <v>885</v>
       </c>
-      <c r="D164" s="64">
+      <c r="D164" s="54">
         <v>38847</v>
       </c>
-      <c r="E164" s="81">
+      <c r="E164" s="138">
         <v>213011042714</v>
       </c>
-      <c r="F164" s="158">
+      <c r="F164" s="162">
         <v>45477</v>
       </c>
-      <c r="G164" s="87" t="s">
+      <c r="G164" s="67" t="s">
         <v>82</v>
       </c>
-      <c r="H164" s="65" t="s">
+      <c r="H164" s="55" t="s">
         <v>104</v>
       </c>
-      <c r="I164" s="100" t="s">
+      <c r="I164" s="76" t="s">
         <v>666</v>
       </c>
-      <c r="J164" s="133" t="s">
+      <c r="J164" s="108" t="s">
         <v>695</v>
       </c>
-      <c r="K164" s="107" t="s">
+      <c r="K164" s="83" t="s">
         <v>592</v>
       </c>
-      <c r="L164" s="121" t="s">
+      <c r="L164" s="97" t="s">
         <v>679</v>
       </c>
       <c r="M164" t="s">
@@ -12296,7 +12301,7 @@
         <f t="shared" ref="N164:N174" si="12">"https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/" &amp; C164 &amp; ".png"</f>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0001-SV.png</v>
       </c>
-      <c r="O164" s="136" t="str">
+      <c r="O164" s="110" t="str">
         <f t="shared" ref="O164:O174" si="13">"https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/" &amp; C164 &amp; ".png"</f>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0001-SV.png</v>
       </c>
@@ -12305,40 +12310,40 @@
       </c>
     </row>
     <row r="165" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A165" s="53" t="s">
+      <c r="A165" s="43" t="s">
         <v>650</v>
       </c>
-      <c r="B165" s="53" t="s">
+      <c r="B165" s="43" t="s">
         <v>651</v>
       </c>
       <c r="C165" s="3" t="s">
         <v>886</v>
       </c>
-      <c r="D165" s="64">
+      <c r="D165" s="54">
         <v>37537</v>
       </c>
-      <c r="E165" s="81">
+      <c r="E165" s="138">
         <v>212012014973</v>
       </c>
-      <c r="F165" s="75">
+      <c r="F165" s="155">
         <v>44620</v>
       </c>
-      <c r="G165" s="87" t="s">
+      <c r="G165" s="67" t="s">
         <v>901</v>
       </c>
-      <c r="H165" s="65" t="s">
+      <c r="H165" s="55" t="s">
         <v>667</v>
       </c>
-      <c r="I165" s="100" t="s">
+      <c r="I165" s="76" t="s">
         <v>668</v>
       </c>
-      <c r="J165" s="133" t="s">
+      <c r="J165" s="108" t="s">
         <v>695</v>
       </c>
-      <c r="K165" s="107" t="s">
+      <c r="K165" s="83" t="s">
         <v>592</v>
       </c>
-      <c r="L165" s="121" t="s">
+      <c r="L165" s="97" t="s">
         <v>680</v>
       </c>
       <c r="M165" t="s">
@@ -12348,7 +12353,7 @@
         <f t="shared" si="12"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0002-SV.png</v>
       </c>
-      <c r="O165" s="136" t="str">
+      <c r="O165" s="110" t="str">
         <f t="shared" si="13"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0002-SV.png</v>
       </c>
@@ -12357,40 +12362,40 @@
       </c>
     </row>
     <row r="166" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A166" s="53" t="s">
+      <c r="A166" s="43" t="s">
         <v>267</v>
       </c>
-      <c r="B166" s="53" t="s">
+      <c r="B166" s="43" t="s">
         <v>652</v>
       </c>
       <c r="C166" s="3" t="s">
         <v>887</v>
       </c>
-      <c r="D166" s="157">
+      <c r="D166" s="124">
         <v>37257</v>
       </c>
-      <c r="E166" s="81">
+      <c r="E166" s="138">
         <v>213011036991</v>
       </c>
-      <c r="F166" s="75">
+      <c r="F166" s="155">
         <v>44377</v>
       </c>
-      <c r="G166" s="87" t="s">
+      <c r="G166" s="67" t="s">
         <v>82</v>
       </c>
-      <c r="H166" s="65" t="s">
+      <c r="H166" s="55" t="s">
         <v>95</v>
       </c>
-      <c r="I166" s="100" t="s">
+      <c r="I166" s="76" t="s">
         <v>669</v>
       </c>
-      <c r="J166" s="133" t="s">
+      <c r="J166" s="108" t="s">
         <v>695</v>
       </c>
-      <c r="K166" s="107" t="s">
+      <c r="K166" s="83" t="s">
         <v>592</v>
       </c>
-      <c r="L166" s="121" t="s">
+      <c r="L166" s="97" t="s">
         <v>681</v>
       </c>
       <c r="M166" t="s">
@@ -12400,7 +12405,7 @@
         <f t="shared" si="12"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0003-SV.png</v>
       </c>
-      <c r="O166" s="136" t="str">
+      <c r="O166" s="110" t="str">
         <f t="shared" si="13"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0003-SV.png</v>
       </c>
@@ -12412,37 +12417,37 @@
       <c r="A167" s="4" t="s">
         <v>653</v>
       </c>
-      <c r="B167" s="53" t="s">
+      <c r="B167" s="43" t="s">
         <v>654</v>
       </c>
       <c r="C167" s="3" t="s">
         <v>888</v>
       </c>
-      <c r="D167" s="64">
+      <c r="D167" s="54">
         <v>37335</v>
       </c>
-      <c r="E167" s="159">
+      <c r="E167" s="139">
         <v>101222151928</v>
       </c>
-      <c r="F167" s="74">
+      <c r="F167" s="150">
         <v>44992</v>
       </c>
-      <c r="G167" s="131" t="s">
+      <c r="G167" s="106" t="s">
         <v>906</v>
       </c>
-      <c r="H167" s="65" t="s">
+      <c r="H167" s="55" t="s">
         <v>670</v>
       </c>
-      <c r="I167" s="132" t="s">
+      <c r="I167" s="107" t="s">
         <v>671</v>
       </c>
-      <c r="J167" s="133" t="s">
+      <c r="J167" s="108" t="s">
         <v>695</v>
       </c>
-      <c r="K167" s="107" t="s">
+      <c r="K167" s="83" t="s">
         <v>605</v>
       </c>
-      <c r="L167" s="134" t="s">
+      <c r="L167" s="109" t="s">
         <v>682</v>
       </c>
       <c r="M167" t="s">
@@ -12452,7 +12457,7 @@
         <f t="shared" si="12"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0004-SV.png</v>
       </c>
-      <c r="O167" s="136" t="str">
+      <c r="O167" s="110" t="str">
         <f t="shared" si="13"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0004-SV.png</v>
       </c>
@@ -12464,37 +12469,37 @@
       <c r="A168" s="4" t="s">
         <v>655</v>
       </c>
-      <c r="B168" s="53" t="s">
+      <c r="B168" s="43" t="s">
         <v>656</v>
       </c>
       <c r="C168" s="3" t="s">
         <v>889</v>
       </c>
-      <c r="D168" s="61">
+      <c r="D168" s="51">
         <v>37212</v>
       </c>
-      <c r="E168" s="130">
+      <c r="E168" s="138">
         <v>213011036639</v>
       </c>
-      <c r="F168" s="72">
+      <c r="F168" s="145">
         <v>44295</v>
       </c>
-      <c r="G168" s="78" t="s">
+      <c r="G168" s="65" t="s">
         <v>82</v>
       </c>
-      <c r="H168" s="66" t="s">
+      <c r="H168" s="56" t="s">
         <v>102</v>
       </c>
-      <c r="I168" s="132" t="s">
+      <c r="I168" s="107" t="s">
         <v>672</v>
       </c>
-      <c r="J168" s="133" t="s">
+      <c r="J168" s="108" t="s">
         <v>695</v>
       </c>
-      <c r="K168" s="107" t="s">
+      <c r="K168" s="83" t="s">
         <v>605</v>
       </c>
-      <c r="L168" s="134" t="s">
+      <c r="L168" s="109" t="s">
         <v>683</v>
       </c>
       <c r="M168" t="s">
@@ -12504,7 +12509,7 @@
         <f t="shared" si="12"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0005-SV.png</v>
       </c>
-      <c r="O168" s="136" t="str">
+      <c r="O168" s="110" t="str">
         <f t="shared" si="13"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0005-SV.png</v>
       </c>
@@ -12516,35 +12521,35 @@
       <c r="A169" s="4" t="s">
         <v>657</v>
       </c>
-      <c r="B169" s="53"/>
+      <c r="B169" s="43"/>
       <c r="C169" s="3" t="s">
         <v>890</v>
       </c>
-      <c r="D169" s="61">
+      <c r="D169" s="51">
         <v>37876</v>
       </c>
-      <c r="E169" s="130">
+      <c r="E169" s="138">
         <v>214031101476</v>
       </c>
-      <c r="F169" s="72">
+      <c r="F169" s="145">
         <v>44525</v>
       </c>
-      <c r="G169" s="78" t="s">
+      <c r="G169" s="65" t="s">
         <v>83</v>
       </c>
-      <c r="H169" s="66" t="s">
+      <c r="H169" s="56" t="s">
         <v>86</v>
       </c>
-      <c r="I169" s="132" t="s">
+      <c r="I169" s="107" t="s">
         <v>673</v>
       </c>
-      <c r="J169" s="133" t="s">
+      <c r="J169" s="108" t="s">
         <v>695</v>
       </c>
-      <c r="K169" s="107" t="s">
+      <c r="K169" s="83" t="s">
         <v>605</v>
       </c>
-      <c r="L169" s="134" t="s">
+      <c r="L169" s="109" t="s">
         <v>684</v>
       </c>
       <c r="M169" t="s">
@@ -12554,7 +12559,7 @@
         <f t="shared" si="12"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0006-SV.png</v>
       </c>
-      <c r="O169" s="136" t="str">
+      <c r="O169" s="110" t="str">
         <f t="shared" si="13"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0006-SV.png</v>
       </c>
@@ -12566,37 +12571,37 @@
       <c r="A170" s="4" t="s">
         <v>658</v>
       </c>
-      <c r="B170" s="53" t="s">
+      <c r="B170" s="43" t="s">
         <v>659</v>
       </c>
       <c r="C170" s="3" t="s">
         <v>891</v>
       </c>
-      <c r="D170" s="64">
+      <c r="D170" s="54">
         <v>36710</v>
       </c>
-      <c r="E170" s="130">
+      <c r="E170" s="138">
         <v>213011035527</v>
       </c>
-      <c r="F170" s="89">
+      <c r="F170" s="160">
         <v>44012</v>
       </c>
-      <c r="G170" s="89" t="s">
+      <c r="G170" s="68" t="s">
         <v>82</v>
       </c>
-      <c r="H170" s="65" t="s">
+      <c r="H170" s="55" t="s">
         <v>99</v>
       </c>
-      <c r="I170" s="132" t="s">
+      <c r="I170" s="107" t="s">
         <v>674</v>
       </c>
-      <c r="J170" s="133" t="s">
+      <c r="J170" s="108" t="s">
         <v>695</v>
       </c>
-      <c r="K170" s="107" t="s">
+      <c r="K170" s="83" t="s">
         <v>605</v>
       </c>
-      <c r="L170" s="134" t="s">
+      <c r="L170" s="109" t="s">
         <v>685</v>
       </c>
       <c r="M170" t="s">
@@ -12606,7 +12611,7 @@
         <f t="shared" si="12"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0007-SV.png</v>
       </c>
-      <c r="O170" s="136" t="str">
+      <c r="O170" s="110" t="str">
         <f t="shared" si="13"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0007-SV.png</v>
       </c>
@@ -12618,37 +12623,37 @@
       <c r="A171" s="4" t="s">
         <v>660</v>
       </c>
-      <c r="B171" s="53" t="s">
+      <c r="B171" s="43" t="s">
         <v>661</v>
       </c>
       <c r="C171" s="3" t="s">
         <v>892</v>
       </c>
-      <c r="D171" s="64">
+      <c r="D171" s="54">
         <v>37135</v>
       </c>
-      <c r="E171" s="130">
+      <c r="E171" s="138">
         <v>213011037730</v>
       </c>
-      <c r="F171" s="74">
+      <c r="F171" s="150">
         <v>44581</v>
       </c>
-      <c r="G171" s="131" t="s">
+      <c r="G171" s="106" t="s">
         <v>82</v>
       </c>
-      <c r="H171" s="65" t="s">
+      <c r="H171" s="55" t="s">
         <v>86</v>
       </c>
-      <c r="I171" s="132" t="s">
+      <c r="I171" s="107" t="s">
         <v>675</v>
       </c>
-      <c r="J171" s="133" t="s">
+      <c r="J171" s="108" t="s">
         <v>695</v>
       </c>
-      <c r="K171" s="107" t="s">
+      <c r="K171" s="83" t="s">
         <v>605</v>
       </c>
-      <c r="L171" s="134" t="s">
+      <c r="L171" s="109" t="s">
         <v>686</v>
       </c>
       <c r="M171" t="s">
@@ -12658,7 +12663,7 @@
         <f t="shared" si="12"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0008-SV.png</v>
       </c>
-      <c r="O171" s="136" t="str">
+      <c r="O171" s="110" t="str">
         <f t="shared" si="13"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0008-SV.png</v>
       </c>
@@ -12670,37 +12675,37 @@
       <c r="A172" s="4" t="s">
         <v>662</v>
       </c>
-      <c r="B172" s="53" t="s">
+      <c r="B172" s="43" t="s">
         <v>663</v>
       </c>
       <c r="C172" s="3" t="s">
         <v>893</v>
       </c>
-      <c r="D172" s="64">
+      <c r="D172" s="54">
         <v>38626</v>
       </c>
-      <c r="E172" s="130">
+      <c r="E172" s="138">
         <v>213151003699</v>
       </c>
-      <c r="F172" s="74">
+      <c r="F172" s="150">
         <v>45301</v>
       </c>
-      <c r="G172" s="131" t="s">
+      <c r="G172" s="106" t="s">
         <v>82</v>
       </c>
-      <c r="H172" s="65" t="s">
+      <c r="H172" s="55" t="s">
         <v>91</v>
       </c>
-      <c r="I172" s="132" t="s">
+      <c r="I172" s="107" t="s">
         <v>676</v>
       </c>
-      <c r="J172" s="133" t="s">
+      <c r="J172" s="108" t="s">
         <v>695</v>
       </c>
-      <c r="K172" s="107" t="s">
+      <c r="K172" s="83" t="s">
         <v>605</v>
       </c>
-      <c r="L172" s="134" t="s">
+      <c r="L172" s="109" t="s">
         <v>687</v>
       </c>
       <c r="M172" t="s">
@@ -12710,7 +12715,7 @@
         <f t="shared" si="12"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0009-SV.png</v>
       </c>
-      <c r="O172" s="136" t="str">
+      <c r="O172" s="110" t="str">
         <f t="shared" si="13"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0009-SV.png</v>
       </c>
@@ -12719,40 +12724,40 @@
       </c>
     </row>
     <row r="173" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A173" s="138" t="s">
+      <c r="A173" s="112" t="s">
         <v>697</v>
       </c>
-      <c r="B173" s="53" t="s">
+      <c r="B173" s="43" t="s">
         <v>664</v>
       </c>
       <c r="C173" s="3" t="s">
         <v>894</v>
       </c>
-      <c r="D173" s="63">
+      <c r="D173" s="53">
         <v>38212</v>
       </c>
-      <c r="E173" s="130">
+      <c r="E173" s="138">
         <v>213011040588</v>
       </c>
-      <c r="F173" s="72">
+      <c r="F173" s="145">
         <v>44988</v>
       </c>
-      <c r="G173" s="78" t="s">
+      <c r="G173" s="65" t="s">
         <v>82</v>
       </c>
-      <c r="H173" s="65" t="s">
+      <c r="H173" s="55" t="s">
         <v>394</v>
       </c>
-      <c r="I173" s="132" t="s">
+      <c r="I173" s="107" t="s">
         <v>677</v>
       </c>
-      <c r="J173" s="133" t="s">
+      <c r="J173" s="108" t="s">
         <v>695</v>
       </c>
-      <c r="K173" s="107" t="s">
+      <c r="K173" s="83" t="s">
         <v>605</v>
       </c>
-      <c r="L173" s="134" t="s">
+      <c r="L173" s="109" t="s">
         <v>688</v>
       </c>
       <c r="M173" t="s">
@@ -12762,7 +12767,7 @@
         <f t="shared" si="12"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0010-SV.png</v>
       </c>
-      <c r="O173" s="136" t="str">
+      <c r="O173" s="110" t="str">
         <f t="shared" si="13"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0010-SV.png</v>
       </c>
@@ -12774,37 +12779,37 @@
       <c r="A174" s="4" t="s">
         <v>665</v>
       </c>
-      <c r="B174" s="142" t="s">
+      <c r="B174" s="116" t="s">
         <v>722</v>
       </c>
       <c r="C174" s="3" t="s">
         <v>895</v>
       </c>
-      <c r="D174" s="64">
+      <c r="D174" s="54">
         <v>37431</v>
       </c>
-      <c r="E174" s="130">
+      <c r="E174" s="138">
         <v>214031101129</v>
       </c>
-      <c r="F174" s="72">
+      <c r="F174" s="145">
         <v>44412</v>
       </c>
-      <c r="G174" s="78" t="s">
+      <c r="G174" s="65" t="s">
         <v>83</v>
       </c>
-      <c r="H174" s="65" t="s">
+      <c r="H174" s="55" t="s">
         <v>86</v>
       </c>
-      <c r="I174" s="132" t="s">
+      <c r="I174" s="107" t="s">
         <v>678</v>
       </c>
-      <c r="J174" s="133" t="s">
+      <c r="J174" s="108" t="s">
         <v>695</v>
       </c>
-      <c r="K174" s="107" t="s">
+      <c r="K174" s="83" t="s">
         <v>605</v>
       </c>
-      <c r="L174" s="134" t="s">
+      <c r="L174" s="109" t="s">
         <v>689</v>
       </c>
       <c r="M174" t="s">
@@ -12814,7 +12819,7 @@
         <f t="shared" si="12"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/JS/qr_etudiant/0011-SV.png</v>
       </c>
-      <c r="O174" s="136" t="str">
+      <c r="O174" s="110" t="str">
         <f t="shared" si="13"/>
         <v>https://raw.githubusercontent.com/DanysRandrianarison/Photo-univ/main/photo_etudiants/0011-SV.png</v>
       </c>
@@ -12831,16 +12836,16 @@
       <c r="A176" s="4"/>
       <c r="B176" s="5"/>
       <c r="C176" s="3"/>
-      <c r="D176" s="57"/>
-      <c r="E176" s="71"/>
-      <c r="F176" s="84"/>
-      <c r="G176" s="78"/>
-      <c r="H176" s="57"/>
-      <c r="I176" s="32"/>
-      <c r="J176" s="129"/>
-      <c r="K176" s="115"/>
-      <c r="L176" s="118"/>
-      <c r="O176" s="136"/>
+      <c r="D176" s="47"/>
+      <c r="E176" s="134"/>
+      <c r="F176" s="156"/>
+      <c r="G176" s="65"/>
+      <c r="H176" s="47"/>
+      <c r="I176" s="22"/>
+      <c r="J176" s="105"/>
+      <c r="K176" s="91"/>
+      <c r="L176" s="94"/>
+      <c r="O176" s="110"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:O176" xr:uid="{00000000-0001-0000-0000-000000000000}">

--- a/JS/liste_etudiants_v1.xlsx
+++ b/JS/liste_etudiants_v1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Stephano\Documents\TRAVAIL\Photo-univ\JS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF76291D-7FA8-432C-AAB2-6DC447A32A11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39F5E4B6-1A3C-442B-B0BB-21889F4C61CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3828,7 +3828,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:P176"/>
   <sheetFormatPr defaultColWidth="8.734375" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
@@ -3950,7 +3949,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="3" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
@@ -4054,7 +4053,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="5" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1" t="s">
         <v>16</v>
       </c>
@@ -4106,7 +4105,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="6" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="1" t="s">
         <v>18</v>
       </c>
@@ -4158,7 +4157,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="7" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="1" t="s">
         <v>20</v>
       </c>
@@ -4210,7 +4209,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="8" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="4" t="s">
         <v>22</v>
       </c>
@@ -4262,7 +4261,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="9" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="6" t="s">
         <v>23</v>
       </c>
@@ -4312,7 +4311,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="10" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="6" t="s">
         <v>24</v>
       </c>
@@ -4416,7 +4415,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="12" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="8" t="s">
         <v>27</v>
       </c>
@@ -4468,7 +4467,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="13" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="8" t="s">
         <v>29</v>
       </c>
@@ -4520,7 +4519,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="14" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="8" t="s">
         <v>31</v>
       </c>
@@ -4572,7 +4571,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="15" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="6" t="s">
         <v>33</v>
       </c>
@@ -4676,7 +4675,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="17" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="8" t="s">
         <v>37</v>
       </c>
@@ -4728,7 +4727,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="18" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="6" t="s">
         <v>39</v>
       </c>
@@ -4780,7 +4779,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="19" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="6" t="s">
         <v>41</v>
       </c>
@@ -4832,7 +4831,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="20" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="6" t="s">
         <v>43</v>
       </c>
@@ -4884,7 +4883,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="21" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="8" t="s">
         <v>45</v>
       </c>
@@ -4988,7 +4987,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="23" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="6" t="s">
         <v>49</v>
       </c>
@@ -5092,7 +5091,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="25" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="8" t="s">
         <v>52</v>
       </c>
@@ -5144,7 +5143,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="26" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="6" t="s">
         <v>54</v>
       </c>
@@ -5196,7 +5195,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="27" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="6" t="s">
         <v>56</v>
       </c>
@@ -5246,7 +5245,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="28" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="6" t="s">
         <v>57</v>
       </c>
@@ -5298,7 +5297,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="29" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="6" t="s">
         <v>59</v>
       </c>
@@ -5350,7 +5349,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="30" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="6" t="s">
         <v>61</v>
       </c>
@@ -5402,7 +5401,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="31" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="6" t="s">
         <v>62</v>
       </c>
@@ -5454,7 +5453,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="32" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="8" t="s">
         <v>63</v>
       </c>
@@ -5506,7 +5505,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="33" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="6" t="s">
         <v>65</v>
       </c>
@@ -5556,7 +5555,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="34" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="6" t="s">
         <v>66</v>
       </c>
@@ -5606,7 +5605,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="35" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="105" t="s">
         <v>708</v>
       </c>
@@ -5658,7 +5657,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="36" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="8" t="s">
         <v>67</v>
       </c>
@@ -5814,7 +5813,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="39" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="6" t="s">
         <v>71</v>
       </c>
@@ -5866,7 +5865,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="40" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="6" t="s">
         <v>73</v>
       </c>
@@ -5966,7 +5965,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="42" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="6" t="s">
         <v>75</v>
       </c>
@@ -6120,7 +6119,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="45" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="6" t="s">
         <v>80</v>
       </c>
@@ -6170,7 +6169,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="46" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="8" t="s">
         <v>81</v>
       </c>
@@ -6220,7 +6219,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="47" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="4" t="s">
         <v>196</v>
       </c>
@@ -6324,7 +6323,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="49" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" s="4" t="s">
         <v>200</v>
       </c>
@@ -6376,7 +6375,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="50" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" s="4" t="s">
         <v>202</v>
       </c>
@@ -6428,7 +6427,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="51" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" s="4" t="s">
         <v>203</v>
       </c>
@@ -6480,7 +6479,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="52" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" s="4" t="s">
         <v>205</v>
       </c>
@@ -6530,7 +6529,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="53" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" s="4" t="s">
         <v>206</v>
       </c>
@@ -6582,7 +6581,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="54" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" s="4" t="s">
         <v>208</v>
       </c>
@@ -6634,7 +6633,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="55" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" s="4" t="s">
         <v>210</v>
       </c>
@@ -6684,7 +6683,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="56" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" s="4" t="s">
         <v>211</v>
       </c>
@@ -6736,7 +6735,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="57" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" s="4" t="s">
         <v>213</v>
       </c>
@@ -6840,7 +6839,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="59" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" s="4" t="s">
         <v>217</v>
       </c>
@@ -6892,7 +6891,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="60" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" s="8" t="s">
         <v>219</v>
       </c>
@@ -6944,7 +6943,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="61" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" s="8" t="s">
         <v>221</v>
       </c>
@@ -7096,7 +7095,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="64" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="64" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" s="35" t="s">
         <v>225</v>
       </c>
@@ -7198,7 +7197,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="66" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" s="8" t="s">
         <v>228</v>
       </c>
@@ -7250,7 +7249,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="67" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" s="8" t="s">
         <v>230</v>
       </c>
@@ -7300,7 +7299,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="68" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" s="8" t="s">
         <v>231</v>
       </c>
@@ -7404,7 +7403,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="70" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" s="8" t="s">
         <v>234</v>
       </c>
@@ -7508,7 +7507,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="72" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="72" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" s="8" t="s">
         <v>238</v>
       </c>
@@ -7610,7 +7609,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="74" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="74" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" s="8" t="s">
         <v>242</v>
       </c>
@@ -7662,7 +7661,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="75" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="75" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" s="8" t="s">
         <v>244</v>
       </c>
@@ -7816,7 +7815,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="78" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="78" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" s="8" t="s">
         <v>248</v>
       </c>
@@ -8076,7 +8075,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="83" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="83" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A83" s="8" t="s">
         <v>258</v>
       </c>
@@ -8180,7 +8179,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="85" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="85" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A85" s="8" t="s">
         <v>262</v>
       </c>
@@ -8232,7 +8231,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="86" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="86" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A86" s="8" t="s">
         <v>264</v>
       </c>
@@ -8336,7 +8335,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="88" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="88" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" s="8" t="s">
         <v>267</v>
       </c>
@@ -8386,7 +8385,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="89" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="89" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A89" s="8" t="s">
         <v>268</v>
       </c>
@@ -8438,7 +8437,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="90" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="90" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A90" s="8" t="s">
         <v>269</v>
       </c>
@@ -8490,7 +8489,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="91" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="91" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A91" s="8" t="s">
         <v>271</v>
       </c>
@@ -8594,7 +8593,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="93" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="93" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A93" s="8" t="s">
         <v>274</v>
       </c>
@@ -8646,7 +8645,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="94" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="94" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A94" s="8" t="s">
         <v>276</v>
       </c>
@@ -8750,7 +8749,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="96" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="96" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A96" s="8" t="s">
         <v>279</v>
       </c>
@@ -8802,7 +8801,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="97" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="97" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A97" s="8" t="s">
         <v>281</v>
       </c>
@@ -8906,7 +8905,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="99" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="99" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A99" s="36" t="s">
         <v>285</v>
       </c>
@@ -9010,7 +9009,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="101" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="101" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A101" s="8" t="s">
         <v>289</v>
       </c>
@@ -9062,7 +9061,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="102" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="102" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A102" s="8" t="s">
         <v>290</v>
       </c>
@@ -9166,7 +9165,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="104" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="104" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A104" s="8" t="s">
         <v>294</v>
       </c>
@@ -9218,7 +9217,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="105" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="105" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A105" s="8" t="s">
         <v>296</v>
       </c>
@@ -9322,7 +9321,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="107" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="107" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A107" s="38" t="s">
         <v>300</v>
       </c>
@@ -9426,7 +9425,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="109" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="109" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A109" s="4" t="s">
         <v>304</v>
       </c>
@@ -9476,7 +9475,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="110" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="110" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A110" s="4" t="s">
         <v>305</v>
       </c>
@@ -9734,7 +9733,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="115" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="115" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A115" s="4" t="s">
         <v>314</v>
       </c>
@@ -9786,7 +9785,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="116" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="116" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A116" s="4" t="s">
         <v>316</v>
       </c>
@@ -9838,7 +9837,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="117" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="117" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A117" s="4" t="s">
         <v>258</v>
       </c>
@@ -9890,7 +9889,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="118" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="118" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A118" s="4" t="s">
         <v>318</v>
       </c>
@@ -9994,7 +9993,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="120" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="120" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A120" s="4" t="s">
         <v>321</v>
       </c>
@@ -10046,7 +10045,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="121" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="121" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A121" s="4" t="s">
         <v>322</v>
       </c>
@@ -10098,7 +10097,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="122" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="122" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A122" s="8" t="s">
         <v>323</v>
       </c>
@@ -10150,7 +10149,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="123" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="123" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A123" s="8" t="s">
         <v>324</v>
       </c>
@@ -10252,7 +10251,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="125" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="125" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A125" s="4" t="s">
         <v>327</v>
       </c>
@@ -10304,7 +10303,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="126" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="126" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A126" s="4" t="s">
         <v>328</v>
       </c>
@@ -10356,7 +10355,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="127" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="127" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A127" s="100" t="s">
         <v>696</v>
       </c>
@@ -10406,7 +10405,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="128" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="128" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A128" s="4" t="s">
         <v>330</v>
       </c>
@@ -10456,7 +10455,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="129" spans="1:16" ht="15.6" hidden="1" x14ac:dyDescent="0.6">
+    <row r="129" spans="1:16" ht="15.6" x14ac:dyDescent="0.6">
       <c r="A129" s="40" t="s">
         <v>331</v>
       </c>
@@ -10612,7 +10611,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="132" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="132" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A132" s="4" t="s">
         <v>337</v>
       </c>
@@ -10664,7 +10663,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="133" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="133" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A133" s="4" t="s">
         <v>339</v>
       </c>
@@ -10714,7 +10713,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="134" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="134" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A134" s="4" t="s">
         <v>340</v>
       </c>
@@ -10766,7 +10765,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="135" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="135" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A135" s="4" t="s">
         <v>342</v>
       </c>
@@ -10818,7 +10817,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="136" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="136" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A136" s="4" t="s">
         <v>344</v>
       </c>
@@ -10870,7 +10869,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="137" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="137" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A137" s="4" t="s">
         <v>346</v>
       </c>
@@ -10922,7 +10921,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="138" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="138" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A138" s="4" t="s">
         <v>348</v>
       </c>
@@ -10972,7 +10971,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="139" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="139" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A139" s="4" t="s">
         <v>349</v>
       </c>
@@ -11024,7 +11023,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="140" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="140" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A140" s="8" t="s">
         <v>351</v>
       </c>
@@ -11074,7 +11073,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="141" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="141" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A141" s="8" t="s">
         <v>352</v>
       </c>
@@ -11178,7 +11177,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="143" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="143" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A143" s="35" t="s">
         <v>356</v>
       </c>
@@ -11230,7 +11229,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="144" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="144" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A144" s="35" t="s">
         <v>358</v>
       </c>
@@ -11334,7 +11333,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="146" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="146" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A146" s="8" t="s">
         <v>272</v>
       </c>
@@ -11386,7 +11385,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="147" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="147" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A147" s="8" t="s">
         <v>362</v>
       </c>
@@ -11490,7 +11489,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="149" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="149" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A149" s="8" t="s">
         <v>366</v>
       </c>
@@ -11542,7 +11541,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="150" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="150" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A150" s="8" t="s">
         <v>368</v>
       </c>
@@ -11594,7 +11593,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="151" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="151" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A151" s="8" t="s">
         <v>370</v>
       </c>
@@ -11696,7 +11695,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="153" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="153" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A153" s="8" t="s">
         <v>373</v>
       </c>
@@ -11800,7 +11799,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="155" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="155" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A155" s="8" t="s">
         <v>377</v>
       </c>
@@ -11850,7 +11849,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="156" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="156" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A156" s="8" t="s">
         <v>285</v>
       </c>
@@ -11954,7 +11953,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="158" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="158" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A158" s="8" t="s">
         <v>381</v>
       </c>
@@ -12058,7 +12057,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="160" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="160" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A160" s="8" t="s">
         <v>385</v>
       </c>
@@ -12264,7 +12263,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="164" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="164" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A164" s="39" t="s">
         <v>649</v>
       </c>
@@ -12314,7 +12313,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="165" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="165" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A165" s="39" t="s">
         <v>650</v>
       </c>
@@ -12366,7 +12365,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="166" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="166" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A166" s="39" t="s">
         <v>267</v>
       </c>
@@ -12418,7 +12417,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="167" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="167" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A167" s="4" t="s">
         <v>653</v>
       </c>
@@ -12470,7 +12469,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="168" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="168" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A168" s="4" t="s">
         <v>655</v>
       </c>
@@ -12522,7 +12521,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="169" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="169" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A169" s="4" t="s">
         <v>657</v>
       </c>
@@ -12624,7 +12623,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="171" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="171" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A171" s="4" t="s">
         <v>660</v>
       </c>
@@ -12676,7 +12675,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="172" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="172" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A172" s="4" t="s">
         <v>662</v>
       </c>
@@ -12728,7 +12727,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="173" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="173" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A173" s="99" t="s">
         <v>697</v>
       </c>
@@ -12832,12 +12831,12 @@
         <v>911</v>
       </c>
     </row>
-    <row r="175" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="175" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A175" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="176" spans="1:16" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="176" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A176" s="4"/>
       <c r="B176" s="5"/>
       <c r="C176" s="3"/>
@@ -12853,13 +12852,6 @@
       <c r="O176" s="97"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P176" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="12">
-      <filters>
-        <filter val="Pas de photo"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
   <conditionalFormatting sqref="A127">
     <cfRule type="colorScale" priority="3">
       <colorScale>
